--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-381.455</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.4007e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.575</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06951318462215825</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5363639417591418</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.685119683448859</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.017854888966721</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.26870929552174</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.7226039646996</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 25.145x + -12822.028</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>449.6745171879671</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42554130.69681846</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.835511574532325e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9582779782550677</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-329.179</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.39345e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.97499999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1857790428966435</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.403151162066192</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.306504634640369</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39.39030896110042</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.94837269523504</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 27.915x + -13557.950</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>438.4540737227541</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>246431000.570932</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.763430389738114e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9635870822507515</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-304.09</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.38986e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.126</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1204578768004475</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8531209395630199</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.409483768391679</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.991770979476339</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43.17298880949703</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.17854880117901</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 31.446x + -15147.335</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>433.2248310180203</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>25393117.07049244</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.732865694075292e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9658671588310183</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-294.957</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.38786e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.22199999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2926918352227469</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.574525573621481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.376592971047289</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44.50083534249696</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.16927968497635</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 31.286x + -14808.520</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>428.8137887709896</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>467768447.6888936</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.718479741523072e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9669316818352978</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-281.806</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38667e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.29300000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2932953736593257</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.129286132015484</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.335199387803538</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.158662694983656</v>
+      </c>
+      <c r="J6" t="n">
+        <v>47.07913007936292</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.32880186537525</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 34.275x + -16171.688</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>408.1742188563638</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7009.65058287773</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.919311721271531e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8718001307299609</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-274.538</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.38581e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.366</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2266073247084026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.048968602297025</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.19063086677084</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.030853283879326</v>
+      </c>
+      <c r="J7" t="n">
+        <v>48.58405553382573</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.33883013400482</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 34.482x + -16045.389</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>420.4195331226477</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>25072149.92516794</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.692610012807808e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9690307847277694</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-269.574</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.38516e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.405</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4764653158754314</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.365963224073554</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.44405821296238</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.214491632564211</v>
+      </c>
+      <c r="J8" t="n">
+        <v>49.08386415821636</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.41648753791699</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 36.174x + -16726.776</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>397.3689196272579</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3410.637819077788</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.318479908176496e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7233618543659136</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-267.9109999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.38474e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.447</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2613070317529992</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.019715664328673</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.383543495839679</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.151513710767172</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49.76593931152152</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.38809614662625</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 35.536x + -16205.029</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>395.4983703746601</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3382.47338464426</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.679114916044387e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7403640421130188</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-261.2500000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.38429e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.489</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8044593626129941</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.492624284211407</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.713240074058787</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.169981521747506</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50.31281525164443</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.48458316352</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 37.800x + -17172.754</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>409.177831085275</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>446354202.0403723</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.676641170578329e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9703243491872734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-258.436</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.38354e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.532</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5791586716262803</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.440439675494955</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.373385300900581</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.003763990569142</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50.96133026838996</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.4780430744419</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 37.637x + -16898.737</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>409.0010012465469</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10607.0661543138</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.560644274500548e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9998899481272274</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-257.948</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.38316e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.56399999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2497183156415834</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9244531947223121</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.118351436617805</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.680211136750347</v>
+      </c>
+      <c r="J12" t="n">
+        <v>51.05797370567237</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.43660816401631</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 36.639x + -16228.824</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>400.011940678606</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6002.323577819623</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.522591193554731e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9116645710089836</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-254.417</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.38329e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1119905121092186</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6749111709089382</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.868492427981709</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.527776893446886</v>
+      </c>
+      <c r="J13" t="n">
+        <v>51.54947364743479</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.42629967368011</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 36.399x + -15942.187</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>389.3982734493844</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6314.678051446853</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.299234505709092e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7948567441408684</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-248.977</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.38237e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.639</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5666007078452291</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.368839178456682</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.575457526474617</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.179732958503439</v>
+      </c>
+      <c r="J14" t="n">
+        <v>53.3794124102861</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.52159239249009</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 38.746x + -16936.366</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>396.5011400072781</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>435210888.7657615</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.655031488858451e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9721055695092801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-246.5700000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.38212e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2858519373528463</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.341616894250423</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.328221694878474</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.035690631854864</v>
+      </c>
+      <c r="J15" t="n">
+        <v>53.94822747558594</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.51125202708421</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 38.477x + -16643.303</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>393.5601479490324</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>214651657.0973744</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.650238820506533e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9725220223827753</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-243.208</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.38169e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.705</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5598743303363515</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.271683280521099</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.460845748870019</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.356380541812865</v>
+      </c>
+      <c r="J16" t="n">
+        <v>55.1614172491581</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.53887902477388</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 39.205x + -16846.483</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>378.0915880934682</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3200.021776007199</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.959794187255251e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6744048381305533</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-241.561</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.38151e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.73399999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4036996126499637</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.141671879699344</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.706236060701364</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.220401319932065</v>
+      </c>
+      <c r="J17" t="n">
+        <v>55.39694693217127</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.55207436504415</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 39.563x + -16857.019</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>376.0505910099079</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3175.754908420079</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.546383489236969e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6872385930589926</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-238.047</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.38102e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.759</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6923233787622027</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.724408025851523</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.950560058139958</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.887422707736175</v>
+      </c>
+      <c r="J18" t="n">
+        <v>56.29815725534894</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.60092914736765</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 40.945x + -17362.770</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>374.0487902565378</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3150.450023124124</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.344126717681031e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.6676270672898907</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-238.684</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.38053e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.78100000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4171271437730372</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.219041978718328</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.567569745415884</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.343598890053027</v>
+      </c>
+      <c r="J19" t="n">
+        <v>56.03853610797679</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.57576865845618</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 40.221x + -16876.748</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>372.049145487165</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3127.323934210941</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.972757512800434e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.6708147596189596</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-237.926</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.38014e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.80800000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5137708234577403</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.079343671455127</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.418460919227589</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.9658695451593</v>
+      </c>
+      <c r="J20" t="n">
+        <v>56.30510536327489</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.55961358739191</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 39.770x + -16516.712</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>370.0793780290469</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3102.817741932373</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.487402432016493e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.6644198362484501</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-233.692</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.38002e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.84099999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2807535285702525</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.141952169131998</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.160260717261922</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.291795020231753</v>
+      </c>
+      <c r="J21" t="n">
+        <v>56.89884287006748</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.59781360725368</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 40.854x + -16857.079</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>368.1090043012</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3080.740831432381</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.742969046266379e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.629966183956977</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-233.659</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.37988e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.86499999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1969564037566486</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9283398958539635</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.190472682701644</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.716488146449735</v>
+      </c>
+      <c r="J22" t="n">
+        <v>56.54821189176041</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.57623627401499</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 40.234x + -16423.914</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>366.0718103345478</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3057.675703850157</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.641388053161204e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6335974516160547</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-963.5230000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.37996e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.717</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07202664845586355</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3407518282098369</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.057552668873019</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.207857261436747</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.53329474445022</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.00061494428905</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.431x + -5808.303</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>433.3319892882081</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>702664727.5205411</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.255714864846592e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9252792117604457</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-726.0170000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.39236e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.15000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.325413406432366</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9309109630611319</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.165840018206571</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.704236939535567</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.32678534541973</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.2671391483667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.327x + -6796.954</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>400.0097735964395</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>219781828.8455609</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.01060832395525e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9438294914318545</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-598.255</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.37508e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.934</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5546009352384351</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.376137804329235</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.32355230040416</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.144426345681668</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.24050676807615</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.95152604535487</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.777x + -8069.113</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>391.0170644581005</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>853377689.1218193</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.869888689413641e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9528630097236869</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-521.946</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.35982e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.404</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5035980585291561</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.209575112493277</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.467511956597355</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.727991680058426</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.61596604441922</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.35950003177355</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 21.683x + -9173.940</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>391.3346221138735</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10048.54031388172</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.899640745121579e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9366583218875678</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-474.7139999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.34835e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.71599999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1670621641700335</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.025381259487446</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.247211907482951</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.035977715278665</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.5414218030699</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.58101973264372</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 23.672x + -9838.252</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>381.2705759157993</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>103637606.8395346</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.728071967764566e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9618181348573558</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-438.241</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.33972e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.934</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6360304182257815</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.559712439582444</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.726317347346814</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.325319664595901</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.92231094358374</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.80078017159987</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 26.040x + -10743.070</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>366.6528996274645</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3081.494744177717</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.803486606084007e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6802984333547296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-413.741</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.33379e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.107</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3494459330198162</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.143709976938647</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.247426052613434</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.970932618799004</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.97096447634449</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.90012402087255</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 27.273x + -11053.071</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>363.6376069962431</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3043.814780033557</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.373673087624089e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6610404364971576</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-395.441</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.32873e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.24299999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2441439194917761</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9203981111752455</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.139796798558371</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.847991671378964</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.66946247606383</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.97993307133902</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 28.352x + -11312.335</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>369.9873394758301</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9104.316546793854</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.947415348728371e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9492814755227535</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-378.204</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.3251e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.348</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5438541769385348</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.395037510540678</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.669971821702061</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.555414939046712</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.30801522795542</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.09190839973874</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 30.017x + -11874.333</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>358.0187008381943</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2969.661359649142</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.772476471591856e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6223964790633304</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-368.8920000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.3222e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.438</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08604405244194629</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9206334549081292</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.02555026674533</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.992569253427723</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.50439815262592</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.1037037525636</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 30.204x + -11736.963</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>360.5142991971231</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5922.624533486918</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.456784505355195e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7586072186923243</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-500.3539999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.35036e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.182</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1505760818234145</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7731531203910154</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.003276334300212</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.426320137566016</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.32937160508418</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.40998884539238</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 22.107x + -11058.032</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>428.2258639481237</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>18372.7964795937</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.708124901436907e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9997735852864446</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-417.432</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.33679e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.688</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2668031236871934</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.036357425760383</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.260546567795348</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.132888692699387</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.31094508839436</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.82907848491389</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 26.380x + -12887.855</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>436.2390868813392</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>714857312.7649179</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.731094755667596e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9601272681503946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-377.727</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.32952e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.928</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4074312951661168</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.166027180025574</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.297374894743989</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.103697649702061</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.88634803430541</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.03561727392091</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 29.156x + -14096.625</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>392.2418228770213</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14347.69680565677</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.853974146356537e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9999894978399823</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-356.744</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.32425e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.074</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3703446100547459</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.151329383402778</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.262260490881905</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.127728620695996</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.50820903873145</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.12590844652591</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 30.562x + -14593.081</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>428.1113247978005</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>36588883.84992374</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.659933458259396e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9650895641874155</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-335.6950000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.32104e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.20699999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5392592258844723</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.216380074690692</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.582132698625078</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.068490608082332</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39.92667146314594</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.23523104501101</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 32.456x + -15346.342</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>423.9579095881203</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>27559905.67447949</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.63809084954019e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9667384858624685</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-329.619</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.31841e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.26900000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3302634351417134</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.056692112141867</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.248625915727059</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.195651648485865</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.02196851584197</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.26574326382118</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 33.028x + -15431.406</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>419.9025313780976</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22813193.89138057</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6255153529867e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9676225195725283</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-316.491</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.31663e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.35299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.523344728445956</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.395018904351595</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.641916884218028</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.484531077848667</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.75112478166474</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.34692519291823</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 34.651x + -16062.703</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>400.5301560943147</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6874.129375918969</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.464919215754058e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8680630262029891</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-309.5690000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3149e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.41800000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4395876874386115</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.125274954028687</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.622288051572982</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.223500220678886</v>
+      </c>
+      <c r="J9" t="n">
+        <v>44.01821102558331</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.36326173207384</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 34.997x + -16030.590</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>412.4537415775835</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>901410856.1699787</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.605921673503404e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9690636093497924</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-306.232</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.31353e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.477</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.602417523596386</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.758099486164819</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.732414377827308</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44.73671880310231</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.3117973395633</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 33.929x + -15278.701</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>390.4344537883035</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3351.606138140507</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.70935487095687e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6719996310187298</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-297.874</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.31225e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.524</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3112519479575973</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.025498442330901</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.282487752170091</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.140815682987528</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46.01200420898316</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.40333634760319</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 35.875x + -16101.650</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>388.2930548595324</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3322.798733853723</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.929434986793159e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6988673094316408</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-292.782</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.31102e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.56999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7196881972102216</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.063632674220548</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.56447398656038</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.499453464676784</v>
+      </c>
+      <c r="J12" t="n">
+        <v>47.05323594021765</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.43765963813895</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 36.664x + -16319.707</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>402.5482859389144</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>219749421.0854972</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.582254998207532e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.970889300678743</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-285.513</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.30994e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.616</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6110153446980167</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.447276985514313</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.601835562909352</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.565616618225262</v>
+      </c>
+      <c r="J13" t="n">
+        <v>47.99606500840096</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.48952368140284</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 37.923x + -16775.684</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>399.4362182370824</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>217884101.4122648</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.575533681273246e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9714148345587645</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-284.0509999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.30901e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.661</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7264555301297773</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.954872516341676</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.974146109871869</v>
+      </c>
+      <c r="J14" t="n">
+        <v>48.74698283605987</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.43843403923236</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 36.682x + -15978.477</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>387.243572223659</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6087.355515252417</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.750494667108169e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8229604772147875</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-283.2789999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.30828e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.685</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3734413719913721</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8495422301089434</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.105468811064588</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.137639649043462</v>
+      </c>
+      <c r="J15" t="n">
+        <v>48.92735939463357</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.4520607038823</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 37.005x + -15986.150</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>385.0033597714138</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5817.856239181757</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.269584952541309e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8579401766700118</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-277.4930000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.30739e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.727</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1985363731329773</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8775760946296537</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.177528453694789</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.029089573463846</v>
+      </c>
+      <c r="J16" t="n">
+        <v>49.85561175722484</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.50172950716394</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 38.233x + -16410.358</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>390.1298533925001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>424906154.8144028</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.559476524407433e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9726902902154484</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-273.061</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.30682e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.76300000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3370459563957311</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9745183409478436</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.284271464930761</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.910655098021333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>50.35514553467614</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.53229054254551</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 39.029x + -16628.039</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>387.0645065547251</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>527789415.7056388</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.554655332137557e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9730985830748725</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-269.231</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.30609e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.79600000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2820905077459882</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.068162640978397</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.485315090007098</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.29380758574157</v>
+      </c>
+      <c r="J18" t="n">
+        <v>51.20198023007158</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.56643024143784</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 39.959x + -16898.867</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>384.0055298146076</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>209938966.7393761</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.549660193808371e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9735088282034376</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-264.191</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.30585e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.84</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2720796036774977</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.135012512533163</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.499184462509821</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.536873695252218</v>
+      </c>
+      <c r="J19" t="n">
+        <v>52.47150482237888</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.5755622336933</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 40.215x + -16834.996</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>369.914785747864</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3117.64811257039</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.150379421065077e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.6717996693984944</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-261.0170000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.30541e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.87</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6979595335423836</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.015345194688437</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.342801621416547</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.151741334015781</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52.77130604888472</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.60138341235772</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 40.958x + -17014.745</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>367.7615643634669</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3092.98069709524</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.719243108953146e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.6581273213961258</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-263.503</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.30485e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.896</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6572037844327163</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.723410416429102</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.808567272961701</v>
+      </c>
+      <c r="J21" t="n">
+        <v>52.85430080487623</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.52127905446127</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 38.738x + -15826.615</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>365.6442421361662</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3065.105472682255</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.50856728064152e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.6589229649273686</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-252.7429999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.30452e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.934</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8279753148514126</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.718800916485976</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.789910803388504</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.094896364935551</v>
+      </c>
+      <c r="J22" t="n">
+        <v>54.40523652964323</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.67967253573478</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 43.387x + -17783.630</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>363.5401248831968</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3041.305824953865</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.226150934124446e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6244279840078788</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1025.074</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.42364e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.172</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1475317172455076</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5491065251219244</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.299768982330636</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.490451348572728</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.23641004851777</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.5734836262973</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.527x + -5264.725</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>430.7569450103838</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>233728674.5132036</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.415788474583415e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9197166466712509</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-761.4280000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.42039e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.833</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3951801674856225</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.004075919106236</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.028514809940817</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.629600561539606</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.17888372248058</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.0032009398027</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.312x + -6368.239</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>403.081108882269</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>26865526.29293975</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.09475894374022e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9406702993587325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-613.395</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.39813e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.73399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.244805505050918</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.778309896176582</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.875108049534948</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.231455458527977</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.29681133932474</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.84456018329087</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.139x + -7917.759</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>395.4896485780671</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>216046876.3848027</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.927812295393479e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9507651565317236</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-531.818</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.37992e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.26300000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5304552065887045</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.234395001242919</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.347352391313667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.164562404650361</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.89828902638913</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.2567462518365</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.870x + -8929.433</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>396.1013078597147</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9899.950515235945</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.690383414507065e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9979303241153106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-473.7760000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.36703e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5904198919995903</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.151603432549296</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.358905446866916</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.064990056643957</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.14229911344584</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.55762539885507</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 23.445x + -9911.451</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>386.7729435961884</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>947233320.0759394</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.763108932738833e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9608585626297973</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-440.054</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3576e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.85599999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1796670358858117</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.142429341888751</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.150578729279332</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.837279147388965</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.52055018265381</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.71961191690619</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 25.112x + -10457.326</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>382.5174943840916</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>209577946.5805859</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.720373641015596e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9635320430160704</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-407.7500000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.35109e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.051</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7027325452828443</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.463907646666737</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.440647435841053</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.178167468120908</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.0887744243484</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.89886347394258</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 27.257x + -11245.434</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>368.5942465753271</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3091.854779228136</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.253836186046018e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6884210375358281</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-392.219</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.34609e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.187</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1546566482363866</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6326767915943524</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.905116921374161</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.402519992793956</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.6449759772661</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.9207469114542</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 27.544x + -11125.368</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>365.5545231100253</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3055.342962976627</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.187563762829413e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6659380877268782</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-370.448</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.3425e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.31399999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5001385020331462</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.185976331440435</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.510807797859341</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.154664958529194</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.8906087303131</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.06866440834293</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 29.655x + -11897.308</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>362.7931590103153</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3019.408839757034</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.576046445387152e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6345541794673513</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-354.895</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.33984e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.413</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9346006582115417</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.422164254515464</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.724357026499066</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.066108846378718</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.31008441041866</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.1680233395651</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 31.265x + -12434.172</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>360.276349917771</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2987.28400260335</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.804308553158765e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6229805346753083</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-638.0010000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.4003e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.227</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1904481742290459</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.854818698938966</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.871087436611262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.448882625495529</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.96094924565681</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.61199063625102</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.892x + -8686.133</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>452.35668962881</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>247438428.0794368</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.035226843614756e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9426902992629592</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-452.424</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.36711e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.384</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2287152286706374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.299399411249475</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.317115546426677</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.043411297611991</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.91021216558055</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.61820935853832</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.042x + -11896.576</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>441.236970068914</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>125079789.1509634</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.809083805034442e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9568502772434311</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-392.71</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.35447e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.762</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2740149499731916</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.030147439665586</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.379578587893013</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.098711081818809</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.047796442997</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.90968108703846</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 27.398x + -13325.243</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>436.0491753386115</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>387987452.8781702</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.738985204231838e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9614436847749341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-359.264</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.34813e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.95999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8424748988119065</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.41646158147149</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.665065823210168</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.581421301036349</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.30255578874856</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.10998604028869</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 30.304x + -14629.671</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>431.8986589084778</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>31910299.39771348</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.700756659347028e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9641181272402682</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-346.229</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.34414e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.09099999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08693528301623969</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6254812080830131</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.053056163950485</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.571902884236613</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.16372192538996</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.09375167779901</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 30.046x + -14209.247</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>428.0160598089331</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>467629884.2441313</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.68002551100011e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9655398689829168</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-334.555</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.34128e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.19799999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04398044082441644</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.090750417036863</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.940398891385464</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39.47167640342165</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.06670532332714</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 29.625x + -13763.947</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>424.1785264245281</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>125545190.288765</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.66198345384196e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9668629723079419</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-318.557</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.33927e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.264</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.510513439407238</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.368924675205588</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.545661225637498</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.17491193090753</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.65046854068598</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.29492502434373</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 33.593x + -15682.860</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>413.3510388804626</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>15685.6440730381</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.77094109916298e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9999999860989168</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-311.059</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.33729e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.334</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4587350122262122</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.053150148941244</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.191575198893802</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.969298016130145</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42.90602094757921</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.31178839547577</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 33.929x + -15651.295</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>416.7702582982151</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>909589822.4757632</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.639971929839753e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.968447875621587</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-304.948</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.33595e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.220447407081307</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.372259963094892</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.782693991537857</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43.76940997105598</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.33982469682809</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 34.502x + -15764.342</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>412.4253798300946</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7686.457886692357</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.662815190856792e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8534223755056346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-299.026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.33485e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.437</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1778411172250179</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.037918207206718</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.317968621508405</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.924217298201902</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44.64645579013533</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.37191918054657</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 35.183x + -15934.396</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.1903711043747</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3362.49531787377</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.561791301832183e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7126031676005499</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-293.3960000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.33389e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.482</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4390828994100324</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.296116317949674</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.516227724758624</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.497620027677549</v>
+      </c>
+      <c r="J12" t="n">
+        <v>46.02124065458372</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.41432945599126</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 36.124x + -16252.516</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>406.5696251295084</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7562.536343381692</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.033533860087458e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8329837228778508</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-288.478</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.33293e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.535</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1981368519938238</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8998556832980953</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.304146116114672</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.947471979252967</v>
+      </c>
+      <c r="J13" t="n">
+        <v>46.74603020550754</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.41061103453872</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 36.040x + -16028.722</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>403.8964437003165</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>220028077.1227835</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.609640843267215e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9708052774873611</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-283.853</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.33203e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.57299999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2867986388771034</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.069348375307753</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.125654236682709</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.900370958588094</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47.47885178218676</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.43327254477968</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 36.561x + -16130.076</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>391.4139537918428</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6274.182893957601</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.838704087528576e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8185845910639955</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-287.0189999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.33143e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1084767012000819</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.187834329476276</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.156482962352657</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.93553120817976</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.30164900253993</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 33.726x + -14594.952</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>397.9808730092059</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>216786082.4330912</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.59908970498482e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9716433820751113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-273.194</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.33054e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.655</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5561334322968206</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.379764212327423</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.554965450624795</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.157139765297166</v>
+      </c>
+      <c r="J16" t="n">
+        <v>49.63030921717826</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.51491342104781</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 38.572x + -16806.840</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>386.1011873896881</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6152.843472120463</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.338106733968226e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.7868989511233535</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-271.648</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.33038e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.68300000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4350936473064957</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.280935521500277</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.56340135305993</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.666020172977758</v>
+      </c>
+      <c r="J17" t="n">
+        <v>50.19868416358441</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.5165870612917</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 38.616x + -16665.981</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>392.1617665167183</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>108141571.6773528</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.588498537872321e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9725387417697915</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-265.635</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.32974e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.72199999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9344358162724209</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.57352195341097</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.653464789645653</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.168356644033553</v>
+      </c>
+      <c r="J18" t="n">
+        <v>50.78203327005826</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.56988028413464</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 40.055x + -17201.665</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>389.2228096335514</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>423823252.9383525</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.583740140481801e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.972928666034528</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-264.2040000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.32936e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.754</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4581996164536785</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.081457603830237</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.059235308547056</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.950474385472732</v>
+      </c>
+      <c r="J19" t="n">
+        <v>51.08267860844081</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.54107988918297</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 39.264x + -16648.479</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>386.3321753760547</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>421642121.2288289</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.579302543440558e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9733164792989136</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-253.407</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.32884e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.78700000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.724817634640487</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.782594133650997</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.000965509988829</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.864705141533984</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52.5309502095397</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.7222515776574</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 44.834x + -19179.413</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>372.524350903414</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3137.765914510968</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.80558198294671e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.6814004971198239</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-262.4709999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.32834e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.821</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3518807705337629</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.587347054985503</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.304062021941724</v>
+      </c>
+      <c r="J21" t="n">
+        <v>51.7077246709522</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.46246401890861</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 37.256x + -15400.264</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>370.3841944268697</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3110.482970582952</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.060048837761327e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.6459859786199874</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-249.913</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.32818e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.851</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.640291974051946</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.129090198646517</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.335943161282973</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.084502388976164</v>
+      </c>
+      <c r="J22" t="n">
+        <v>53.63909919572608</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.69849085206897</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 44.015x + -18393.186</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>368.3066786447217</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3088.221134289601</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.946012337124171e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6733042551582672</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1020.75</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.45121e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.01300000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2875363148956713</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7839386182584485</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.526556016009936</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.882158004050137</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.08523423968417</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.49918395916609</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.384x + -5250.953</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>428.2332462765251</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>176854762.310507</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.503146688684804e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9172624204141567</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-727.758</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.44345e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.952</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2273951028380678</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8561023301699239</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.078115871711116</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.770837372650904</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.70977465012022</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.10331232512375</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.681x + -6428.418</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>378.5659046197014</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3251.976403630118</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.638314156025119e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7310016366530891</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-574.908</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.41798e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.92100000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.432100356170089</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.15918510012084</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.292750016909542</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.918568256018977</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.49111343701817</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.95039915777241</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.770x + -7975.321</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>387.4135014371778</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5878.512002361233</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.027754898540164e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9368114480869567</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-486.778</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.39885e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.47199999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4695339054831082</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.179566746522168</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.276852005340013</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.735652831965993</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.75600408426212</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.43536910256242</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 22.326x + -9362.085</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>383.8299045016033</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>419254175.9051671</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.82381194019089e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.95922540528931</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-428.646</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38618e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.825</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8368184598070096</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.434652697637291</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.530023157173491</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.152210999246645</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.62084430887329</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.7556883062751</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 25.516x + -10601.220</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>368.8728782930354</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3105.746169602751</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.379624438924234e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6917026197940417</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-388.851</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.37709e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.06100000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.689863731115181</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.046000611455014</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.454590031108722</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.244487200646617</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.92102320706093</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.99494859295974</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 28.564x + -11797.636</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>366.1889323686365</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3069.469555446921</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.354806899301846e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6608962418854819</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-363.164</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.37161e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.25700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4290091167837713</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.187548516452249</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.116201812707581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.880991108345968</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.70392156141912</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.06013333914801</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 29.525x + -11910.999</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>363.3927720476658</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3029.728417792315</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.595083832219959e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6335036539685892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-344.14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.36684e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.39100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2734043755488413</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.345784003941734</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.459635923457063</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.182853234655018</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36.99664937929808</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.16340468963088</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 31.186x + -12423.381</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>365.6700232995036</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4894.766165784499</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.110762989935804e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8035245279410367</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-329.702</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.36418e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.488</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9045724190484686</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.465495990064886</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.597983352973499</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.178081958715279</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.6125616181471</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.24712784817928</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 32.677x + -12879.701</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>362.3122293056554</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>393741041.4451929</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.648926069873349e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9707232710836597</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-315.8560000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.36178e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.587</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7892208974391008</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.370849447281564</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.386909576465692</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.15630253813424</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40.54521353049856</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.32050250286623</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 34.105x + -13285.898</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>358.4391175287689</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>33422879.31864697</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.632150073337587e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.972014366512766</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-608.9560000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.43565e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.29300000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4959055670420575</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.586756815320366</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.150004120034919</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.34016829248513</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.65441705284117</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 17.106x + -8593.638</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>445.7947041603194</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>244050227.6888387</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.071748836608976e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9437716666932277</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-444.6999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.40363e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.313</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8280253555913717</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.617647183996894</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.399626816114479</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.950347170866386</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.48379038793594</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.62321067557258</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.093x + -11840.649</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>436.9700326005391</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>341020120.6648586</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.865560298812348e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9561961947193215</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-383.852</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.39069e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.717</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2116383013726481</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9582943207768206</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.227577819866553</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.913504955135797</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.9633118811969</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.88393660932623</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 27.064x + -13041.572</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>432.5868409983169</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>27750175.75858851</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.787540813147449e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9612695288223025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-351.7339999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.38452e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.922</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2189114680642494</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.180223357025625</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.304662586000497</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.011265600275663</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.4376246988161</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.04612989654245</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.313x + -13975.832</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>428.6187214448487</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>234348620.6758281</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.752994282087224e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9635642570370346</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-337.012</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38064e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.051</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5022086359909113</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.73828235454599</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.661496002131329</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.48364080755779</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.05673054153104</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 29.473x + -13808.292</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>424.5595634917665</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>128756446.3089024</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.729583716904129e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9651903461022434</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-316.075</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.37826e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.15600000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7874010170535384</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.631564961163769</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.663010046563074</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.460722732002552</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40.93285349340482</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.27044688663949</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 33.117x + -15532.443</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>420.4315652067328</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>118615617.0548192</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.712206307714624e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9664686563307822</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-310.097</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.37642e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.235</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6242231188623198</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9676343193172794</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.442593355943094</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.007705508736649</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.31264864052041</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.24290423031162</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 32.598x + -15019.597</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>416.3770116231983</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>454588972.0921235</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.699571050475663e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9673986967322421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-301.028</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.37501e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.306</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4620594521889791</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.068804789065058</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.312750144623849</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.036746361847698</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.69460385081167</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.29186155096993</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 33.533x + -15295.800</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>393.7922482824788</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3380.332953377035</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.299760744514844e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7206784422406334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-293.661</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.37379e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.36799999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.354721607336536</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.19145251376467</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.204583051530835</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.22585319527408</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44.96742248647183</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.33010779802876</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 34.301x + -15496.521</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>393.3558551742232</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3350.947418589739</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.133772204584533e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7969682207860459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-285.8539999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.37277e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.416</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9147051797277438</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.428852187994655</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.618215573143581</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.167444174510042</v>
+      </c>
+      <c r="J11" t="n">
+        <v>45.64887252385711</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.40474625744268</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 35.907x + -16136.333</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>405.6987242050351</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>223496760.40505</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.671143237273648e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9695690665259259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-287.692</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.37214e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.462</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3598668737548246</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.411012730276602</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.128593992565151</v>
+      </c>
+      <c r="J12" t="n">
+        <v>45.40441804939214</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.2793501247301</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 33.289x + -14647.019</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>406.6718598625063</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10426.34676195086</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.626741760332304e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9983495940900967</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-278.355</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.37122e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.508</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1209527387684319</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.010424950348922</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.248906958226849</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.814085383256018</v>
+      </c>
+      <c r="J13" t="n">
+        <v>47.14611154018428</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.40617885970838</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 35.939x + -15797.921</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>399.4162991703378</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>123994034.9297559</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.657267705748101e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9706750895791072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-278.026</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.3706e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.545</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4638370498212119</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.910052324553353</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.75981163317594</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47.84135482975276</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.35504712138336</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 34.822x + -15094.628</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>400.2324335157696</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10470.88867216568</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.269943740968406e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.961358022299325</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-269.083</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.36985e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.587</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5052179703890171</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.019529494491963</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.334090789504904</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.088039535229215</v>
+      </c>
+      <c r="J15" t="n">
+        <v>48.96615506324409</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.47903605119467</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 37.662x + -16328.454</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>393.4107771894506</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>107723215.7499345</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.645584611816782e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9716049016418253</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-264.576</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.36958e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.63</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3247480507861498</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.142872454857702</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.521556784898553</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.382739632121032</v>
+      </c>
+      <c r="J16" t="n">
+        <v>50.20702195728759</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.49065533624402</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 37.952x + -16298.552</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>390.4918075518529</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>217876328.0257168</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.640303864404856e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9720715638424783</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-266.073</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.36887e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.65300000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07873981263444427</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.749340141456708</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.050301209771286</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.894760236396851</v>
+      </c>
+      <c r="J17" t="n">
+        <v>49.89027451049957</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.44194140277973</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 36.765x + -15585.799</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>375.5062330050512</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3172.946271935872</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.241315651755685e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6669372147365985</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-258.6390000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.36843e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.694</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3920910056521773</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.352871154610726</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.582126968586413</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.541963158896137</v>
+      </c>
+      <c r="J18" t="n">
+        <v>51.44471404856569</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.53242985999732</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 39.033x + -16502.586</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>373.3998191523149</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3149.076553888359</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.07087961023799e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.7032503934952897</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-255.449</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.36822e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.726</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4164622445740868</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.336789869355909</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.314026562672537</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.071243381509586</v>
+      </c>
+      <c r="J19" t="n">
+        <v>51.5547216193296</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.55674945260151</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 39.691x + -16651.589</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>371.3188852355273</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3123.663719967379</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.18720346893616e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.6730752126117748</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-251.033</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.36795e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.762</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8120121246553947</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.33117745829463</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.674237639603463</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.263904964532949</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52.58921192846201</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.58473711769085</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 40.476x + -16851.461</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>369.2982471975364</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3099.302276693664</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.942202739543038e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.6557105089339925</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-250.662</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.36769e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.78400000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5884355961336842</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.31437535523234</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.607131094079043</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.48620913669718</v>
+      </c>
+      <c r="J21" t="n">
+        <v>52.84353422473711</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.60130208001813</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 40.956x + -16913.710</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>367.1860219749532</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3075.127425408357</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.907859228920702e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.6277294533940498</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-247.7919999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.36741e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.816</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5711502675243449</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.452995813698131</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.593207236360604</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.732259849175275</v>
+      </c>
+      <c r="J22" t="n">
+        <v>53.64127473272201</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.60453112993389</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 41.050x + -16789.938</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>365.2080411536498</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3048.036387501885</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.649870250503162e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6333881973766845</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-894.4929999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.47798e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.81100000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1858786897697501</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5761232361937542</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.529415065979131</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.823728616810431</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.4743140759348</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.07196918455699</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.598x + -5304.874</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>401.1043403775762</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>108907247.952289</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.373384584861524e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.927957716770761</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-550.8199999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.43856e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.01900000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2573476385916386</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9328062405032042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.977705808995471</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.714843158946661</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.23427694191831</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.01464537540696</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 19.175x + -8006.075</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>381.3629202390516</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9439.87884057199</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.658933688911196e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9982084002033405</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-426.4520000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.41636e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.785</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5806117957601437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.080142564586975</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.424196426777212</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.2015206332408</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.40958958227861</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.67743692957593</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 24.656x + -10066.136</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>364.5311168886443</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3058.22627779957</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.609211404066198e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6804409056036921</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-361.5520000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.40476e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.152</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.058351096808554</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.293269559505159</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.386080398305476</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.336142077774697</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.92955917781334</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.08235552617823</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.867x + -12164.623</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>361.9718251685001</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3015.894685735782</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.520239378837497e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6358179121648219</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-333.287</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.39867e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.372</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5934631493476684</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.309336792618772</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.649505525886763</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.341852520538622</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.71109840772913</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.1532222126736</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 31.014x + -12301.637</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>364.3538657862861</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>105464050.9517256</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.705058324283315e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9694094793004953</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-313.081</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.39524e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.52</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.57956578892743</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.051516293240645</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.410154555136514</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.870976057397392</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40.33624523028612</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.22827363210166</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 32.329x + -12591.555</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>359.2365938796329</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>30867463.59770979</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.680696565424466e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9712306144011446</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-297.344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.39352e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.397431760239812</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.135820687024798</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.395714627381376</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.932596252622725</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.43705322646479</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.32155903305907</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 34.127x + -13108.619</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>354.16747354124</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>289119563.5671461</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.667270538946964e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9722673321817167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-284.604</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.39268e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.721</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6985055427113006</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.364938252202912</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.608947491879248</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.494867310999511</v>
+      </c>
+      <c r="J9" t="n">
+        <v>44.86456903002861</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.39740103072994</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 35.742x + -13545.505</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>349.3739113736689</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>474103179.0063043</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.655311809901298e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9732739305007284</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-277.068</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.39238e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.786</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5014500573245739</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.282092939337125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.393934140188522</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2465681211706</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45.94419276144426</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.4311182282699</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 36.511x + -13638.588</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>345.0101471185797</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>187649832.029548</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.646770464454235e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9740325991615326</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-272.275</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.39217e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.843</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2567589030461178</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.04250996156246</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.315056953784954</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.802228242451729</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46.79584937436223</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.41999804012282</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 36.254x + -13312.564</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>333.1721359161679</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5602.47840505856</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.840085250934307e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7588072773552623</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-485.686</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.31074e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.252</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1778819964779912</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.089293153795504</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.104313179905942</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.644722639784622</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.16490610903331</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.53951509543693</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 23.272x + -12344.378</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12344.37768874648</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>467.6570940016832</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>485.686</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.765856924959165e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9540645597205092</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-439.384</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.30011e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.554</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2434583226533332</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.18347198914152</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.30569155616504</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.145201308606906</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.66138098204909</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.78614871101689</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 25.868x + -13489.038</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13489.03786423497</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>460.842479074512</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>439.384</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.708017582691505e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9578916680277162</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-411.664</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.29335e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.758</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04569425672340185</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8119325738219176</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.926368514225424</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.58083555817284</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.93832620350692</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.89029421361499</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 27.146x + -13863.965</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13863.96538051371</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>436.8494436332582</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>411.664</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.661877335263083e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9997456135185345</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-386.404</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.28864e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.914</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4123040942772812</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.360741545056794</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.649670122709811</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.992624364730559</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.19159774703152</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.05805267390988</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 29.493x + -14903.051</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14903.05133271452</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>448.7462546299487</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>386.404</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.642305570667434e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9625287614976732</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-376.839</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.28581e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.015</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2810135135290894</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9020318354828287</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.155598522010069</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.892903409406919</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.536222586957</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.07866841055484</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 29.810x + -14783.958</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14783.95811005138</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>443.3097998353818</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>376.839</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.624525978720059e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9638636810929061</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-365.185</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.28356e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.111</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7510205601316173</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.82519493579781</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.647561951245311</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.73494990865267</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.10811613630992</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 30.274x + -14768.774</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14768.77376278749</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>438.1425064061951</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>365.185</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.608399886353592e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9651172059383819</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-353.241</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.28196e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.19199999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3635042131552154</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.086408653935847</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.399689138944258</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.154290207897681</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.26199052860405</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.20335717492929</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 31.880x + -15407.875</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15407.87487417757</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>379.6747431750197</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>353.241</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88059960962276e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9995785702830648</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-341.3070000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.27971e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.279</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.379843483238768</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.076706323494596</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.368862333224177</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.995516242664121</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.48026260911331</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.27073029357051</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 33.123x + -15823.338</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15823.33750516756</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>428.0859084856359</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>341.3070000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.582859134618542e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.967108551661319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-336.863</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.27854e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.349</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1190157201801389</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4004532187446726</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.803182124567867</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.468701286382921</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.22627154855961</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.22851940606468</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 32.333x + -15136.251</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15136.25084606659</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>423.2099813772927</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>336.863</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.57251038502611e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9679733493192154</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-328.858</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.2773e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.407</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08883564878249696</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7851116347003053</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.926636331827337</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.508426057602019</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42.23913891192351</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.29013535664943</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 33.499x + -15531.253</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15531.25305697876</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>418.6770996582599</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>328.858</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.563857707125518e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9686732710935785</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>87.7226039646996</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 25.145x + -12822.028</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12822.02778880958</v>
       </c>
       <c r="Y2" t="n">
         <v>449.6745171879671</v>
       </c>
       <c r="Z2" t="n">
-        <v>42554130.69681846</v>
+        <v>381.455</v>
       </c>
       <c r="AA2" t="n">
         <v>1.835511574532325e-07</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>87.94837269523504</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 27.915x + -13557.950</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13557.94999070565</v>
       </c>
       <c r="Y3" t="n">
         <v>438.4540737227541</v>
       </c>
       <c r="Z3" t="n">
-        <v>246431000.570932</v>
+        <v>329.179</v>
       </c>
       <c r="AA3" t="n">
         <v>1.763430389738114e-07</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>88.17854880117901</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 31.446x + -15147.335</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15147.33515707951</v>
       </c>
       <c r="Y4" t="n">
         <v>433.2248310180203</v>
       </c>
       <c r="Z4" t="n">
-        <v>25393117.07049244</v>
+        <v>304.09</v>
       </c>
       <c r="AA4" t="n">
         <v>1.732865694075292e-07</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>88.16927968497635</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 31.286x + -14808.520</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14808.5196472664</v>
       </c>
       <c r="Y5" t="n">
         <v>428.8137887709896</v>
       </c>
       <c r="Z5" t="n">
-        <v>467768447.6888936</v>
+        <v>294.957</v>
       </c>
       <c r="AA5" t="n">
         <v>1.718479741523072e-07</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>88.32880186537525</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 34.275x + -16171.688</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16171.68798660787</v>
       </c>
       <c r="Y6" t="n">
         <v>408.1742188563638</v>
       </c>
       <c r="Z6" t="n">
-        <v>7009.65058287773</v>
+        <v>281.806</v>
       </c>
       <c r="AA6" t="n">
         <v>6.919311721271531e-07</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>88.33883013400482</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 34.482x + -16045.389</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16045.38937363871</v>
       </c>
       <c r="Y7" t="n">
         <v>420.4195331226477</v>
       </c>
       <c r="Z7" t="n">
-        <v>25072149.92516794</v>
+        <v>274.538</v>
       </c>
       <c r="AA7" t="n">
         <v>1.692610012807808e-07</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>88.41648753791699</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 36.174x + -16726.776</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16726.77627878552</v>
       </c>
       <c r="Y8" t="n">
         <v>397.3689196272579</v>
       </c>
       <c r="Z8" t="n">
-        <v>3410.637819077788</v>
+        <v>269.574</v>
       </c>
       <c r="AA8" t="n">
         <v>3.318479908176496e-06</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>88.38809614662625</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 35.536x + -16205.029</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-16205.02873704155</v>
       </c>
       <c r="Y9" t="n">
         <v>395.4983703746601</v>
       </c>
       <c r="Z9" t="n">
-        <v>3382.47338464426</v>
+        <v>267.9109999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>2.679114916044387e-06</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>88.48458316352</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 37.800x + -17172.754</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-17172.75378590349</v>
       </c>
       <c r="Y10" t="n">
         <v>409.177831085275</v>
       </c>
       <c r="Z10" t="n">
-        <v>446354202.0403723</v>
+        <v>261.2500000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.676641170578329e-07</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>88.4780430744419</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 37.637x + -16898.737</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16898.73726182366</v>
       </c>
       <c r="Y11" t="n">
         <v>409.0010012465469</v>
       </c>
       <c r="Z11" t="n">
-        <v>10607.0661543138</v>
+        <v>258.436</v>
       </c>
       <c r="AA11" t="n">
         <v>2.560644274500548e-07</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>88.43660816401631</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 36.639x + -16228.824</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-16228.82403837326</v>
       </c>
       <c r="Y12" t="n">
         <v>400.011940678606</v>
       </c>
       <c r="Z12" t="n">
-        <v>6002.323577819623</v>
+        <v>257.948</v>
       </c>
       <c r="AA12" t="n">
         <v>4.522591193554731e-07</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>88.42629967368011</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 36.399x + -15942.187</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15942.18692873509</v>
       </c>
       <c r="Y13" t="n">
         <v>389.3982734493844</v>
       </c>
       <c r="Z13" t="n">
-        <v>6314.678051446853</v>
+        <v>254.417</v>
       </c>
       <c r="AA13" t="n">
         <v>1.299234505709092e-06</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>88.52159239249009</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 38.746x + -16936.366</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16936.36643620468</v>
       </c>
       <c r="Y14" t="n">
         <v>396.5011400072781</v>
       </c>
       <c r="Z14" t="n">
-        <v>435210888.7657615</v>
+        <v>248.977</v>
       </c>
       <c r="AA14" t="n">
         <v>1.655031488858451e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>88.51125202708421</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 38.477x + -16643.303</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-16643.30296134172</v>
       </c>
       <c r="Y15" t="n">
         <v>393.5601479490324</v>
       </c>
       <c r="Z15" t="n">
-        <v>214651657.0973744</v>
+        <v>246.5700000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.650238820506533e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>88.53887902477388</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 39.205x + -16846.483</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16846.48349964605</v>
       </c>
       <c r="Y16" t="n">
         <v>378.0915880934682</v>
       </c>
       <c r="Z16" t="n">
-        <v>3200.021776007199</v>
+        <v>243.208</v>
       </c>
       <c r="AA16" t="n">
         <v>3.959794187255251e-06</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>88.55207436504415</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 39.563x + -16857.019</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-16857.01893624054</v>
       </c>
       <c r="Y17" t="n">
         <v>376.0505910099079</v>
       </c>
       <c r="Z17" t="n">
-        <v>3175.754908420079</v>
+        <v>241.561</v>
       </c>
       <c r="AA17" t="n">
         <v>3.546383489236969e-06</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>88.60092914736765</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 40.945x + -17362.770</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-17362.76992330362</v>
       </c>
       <c r="Y18" t="n">
         <v>374.0487902565378</v>
       </c>
       <c r="Z18" t="n">
-        <v>3150.450023124124</v>
+        <v>238.047</v>
       </c>
       <c r="AA18" t="n">
         <v>4.344126717681031e-06</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>88.57576865845618</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 40.221x + -16876.748</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-16876.74777693363</v>
       </c>
       <c r="Y19" t="n">
         <v>372.049145487165</v>
       </c>
       <c r="Z19" t="n">
-        <v>3127.323934210941</v>
+        <v>238.684</v>
       </c>
       <c r="AA19" t="n">
         <v>3.972757512800434e-06</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>88.55961358739191</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 39.770x + -16516.712</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16516.71193339312</v>
       </c>
       <c r="Y20" t="n">
         <v>370.0793780290469</v>
       </c>
       <c r="Z20" t="n">
-        <v>3102.817741932373</v>
+        <v>237.926</v>
       </c>
       <c r="AA20" t="n">
         <v>4.487402432016493e-06</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>88.59781360725368</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 40.854x + -16857.079</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16857.07896105192</v>
       </c>
       <c r="Y21" t="n">
         <v>368.1090043012</v>
       </c>
       <c r="Z21" t="n">
-        <v>3080.740831432381</v>
+        <v>233.692</v>
       </c>
       <c r="AA21" t="n">
         <v>5.742969046266379e-06</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>88.57623627401499</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 40.234x + -16423.914</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-16423.9140367922</v>
       </c>
       <c r="Y22" t="n">
         <v>366.0718103345478</v>
       </c>
       <c r="Z22" t="n">
-        <v>3057.675703850157</v>
+        <v>233.659</v>
       </c>
       <c r="AA22" t="n">
         <v>5.641388053161204e-06</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-492.792</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.31411e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.224</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2961497334859802</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.07438005711279</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.054143240335374</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.670752362614413</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.84920750777166</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.50473203768817</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 22.947x + -12123.842</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12123.84202056224</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>460.6238995794369</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>492.792</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.774403400401903e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9537545230038583</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-390.406</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.29962e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.854</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3309961804814279</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.039111332003842</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.229773506922785</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.920709881674654</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.750027546527</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.99565485570862</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 28.574x + -14481.426</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14481.42614730383</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>450.2200509822064</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>390.406</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.664567588103265e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9617656197504765</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-357.253</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.29233e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.074</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1543690342366548</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9733287695844106</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.208858162951442</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.91952451678127</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.57456074028052</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.1359397460767</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 30.726x + -15304.821</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15304.82075703165</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>445.3684382892027</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>357.253</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.625654406343331e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9645147577009645</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-338.177</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.28793e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.202</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1946287545114478</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.274834238332939</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.583886807502353</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.269524906896642</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.34846520139183</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.24226566809949</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 32.586x + -16064.317</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16064.31660664211</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>441.057126885874</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>338.177</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.603182105650482e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9661200428420953</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-326.828</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.28431e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09234270436945416</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8258924627126107</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.130121393416192</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.680446529196132</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42.938189124065</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.2628309136518</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 32.972x + -16013.826</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16013.82608106867</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>381.922818856085</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>326.828</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.834295378082544e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9992569699770993</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-317.366</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.28143e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.373</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1967073806402147</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.815595440953068</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.198568194472012</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.961068635430331</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44.41427469034488</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.31719934723067</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 34.038x + -16357.287</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16357.28705731489</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>385.6662286725656</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>317.366</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.052840766674812e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9984004369077244</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-310.542</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27985e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.42700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3298480835679606</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.06503664367744</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.526562412118118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.271625341513504</v>
+      </c>
+      <c r="J8" t="n">
+        <v>45.41190804409871</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.3812777923025</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 35.386x + -16865.195</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16865.19531556046</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>428.163097075322</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>310.542</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.561360683189014e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.969208184793075</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-303.485</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.27862e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.491</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2213273545414763</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.12739830906719</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.237339269896657</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.794782410509471</v>
+      </c>
+      <c r="J9" t="n">
+        <v>46.34316522544032</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.40152683659176</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 35.835x + -16874.717</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-16874.71697691734</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>424.128099526301</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>303.485</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.55284447976298e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9698970314107124</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-297.688</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.27761e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.539</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3705906724996814</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.245483978466519</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.314626774374533</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.486040202824595</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.67165537552716</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.44911893954631</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 36.935x + -17247.439</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-17247.43865135637</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>420.2519489761569</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>297.688</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.548064645108504e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9702547271893177</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-295.909</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.2767e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.571</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3248178927093877</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.078967413326492</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.199718146763056</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.867271217500068</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.50616115459507</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.44835247916954</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 36.917x + -17040.174</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-17040.17357784339</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>398.7846648972076</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>295.909</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.954473502611596e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9090186399210735</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-290.691</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.27615e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.61799999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4218268456143988</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.322658430585799</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.386570487346716</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.321862086952069</v>
+      </c>
+      <c r="J12" t="n">
+        <v>48.99489222910123</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.47074562688456</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 37.458x + -17120.126</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-17120.1256064699</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>412.9498010680853</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>290.691</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.536621899455083e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9712161772557483</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-282.789</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.27526e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.66500000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6978565979983411</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.726468905081745</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.90767348351091</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.741659562188315</v>
+      </c>
+      <c r="J13" t="n">
+        <v>50.16899455770158</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.55210595611571</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 39.563x + -18003.740</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-18003.73978618631</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>409.9714713688827</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>282.789</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.586148895956666e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8540159320136745</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-281.032</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.27443e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.699</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3415276741666914</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.329998498487884</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.649623799320877</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.381282807868472</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50.41225208985558</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.53771951488943</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 39.174x + -17610.987</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-17610.9871134212</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>388.8352672729376</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>281.032</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.882408580975925e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7002968364637472</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-279.723</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.27374e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.73399999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3862141369690649</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.06533420302879</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.211085945044229</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.899309230510733</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50.74319243120775</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.52154558342484</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 38.745x + -17208.489</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-17208.48884818449</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>402.6533208395448</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>279.723</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.520169188990871e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9725820696212756</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-274.514</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.27307e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.774</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5381187430298392</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.131387712789768</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.34469632957035</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.071291082847563</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51.80401881796762</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.55344098214188</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 39.600x + -17441.158</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17441.15762665463</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>399.2866874166169</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>274.514</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.514899248952161e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9730381413063854</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-272.915</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.27252e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.80500000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2647621442549637</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.184836442130321</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.262599557443147</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.214651173076095</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.26071364266095</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.55258391024402</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 39.576x + -17243.047</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-17243.04685903747</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>387.4502664951513</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>272.915</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.468984113764074e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.775440283898572</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-268.489</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.27191e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.833</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7661997557540706</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.326766979481069</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.564710195922419</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.529908175628724</v>
+      </c>
+      <c r="J18" t="n">
+        <v>52.74241802735012</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.6153973402204</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 41.373x + -17944.371</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-17944.37131442848</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>385.231271717932</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>268.489</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.079634136156786e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.808120242059553</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-262.977</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.27144e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.878</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7546145028248559</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.356954440799032</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.478819333185493</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.499086673610129</v>
+      </c>
+      <c r="J19" t="n">
+        <v>53.99092940782302</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.64204818525057</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 42.185x + -18135.465</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-18135.46509163999</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>389.4181073657846</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>262.977</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.500804209514123e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9742734114328043</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-262.783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.27113e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.90000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6706463919858338</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.422353147362363</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.632001414651894</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.179724261530192</v>
+      </c>
+      <c r="J20" t="n">
+        <v>53.83046628810909</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.64241017521204</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 42.196x + -17958.525</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-17958.52544821114</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>386.1429010916787</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>262.783</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.498408751587341e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9744883841235749</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-258.266</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.2708e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.94</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5683809482985607</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.369701716363486</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.687698510528306</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.507433663685586</v>
+      </c>
+      <c r="J21" t="n">
+        <v>55.17276114244543</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.65490644638726</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 42.588x + -17946.064</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-17946.06409079452</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>382.9088097882289</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>258.266</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.49375746343324e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9749254236154548</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-258.143</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.27013e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.96299999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3873089029219532</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.124209568982395</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.409891270046687</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.160184330058309</v>
+      </c>
+      <c r="J22" t="n">
+        <v>54.91244908678262</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.65396118956778</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 42.558x + -17744.220</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-17744.21970502623</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>369.4545041984531</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>258.143</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.502592419324417e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6565823734997837</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>85.00061494428905</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.431x + -5808.303</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5808.302779513925</v>
       </c>
       <c r="Y2" t="n">
         <v>433.3319892882081</v>
       </c>
       <c r="Z2" t="n">
-        <v>702664727.5205411</v>
+        <v>963.5230000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.255714864846592e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.2671391483667</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.327x + -6796.954</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6796.953724562959</v>
       </c>
       <c r="Y3" t="n">
         <v>400.0097735964395</v>
       </c>
       <c r="Z3" t="n">
-        <v>219781828.8455609</v>
+        <v>726.0170000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.01060832395525e-07</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.95152604535487</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.777x + -8069.113</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8069.112609432689</v>
       </c>
       <c r="Y4" t="n">
         <v>391.0170644581005</v>
       </c>
       <c r="Z4" t="n">
-        <v>853377689.1218193</v>
+        <v>598.255</v>
       </c>
       <c r="AA4" t="n">
         <v>1.869888689413641e-07</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>87.35950003177355</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 21.683x + -9173.940</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9173.939713338897</v>
       </c>
       <c r="Y5" t="n">
         <v>391.3346221138735</v>
       </c>
       <c r="Z5" t="n">
-        <v>10048.54031388172</v>
+        <v>521.946</v>
       </c>
       <c r="AA5" t="n">
         <v>3.899640745121579e-07</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>87.58101973264372</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.672x + -9838.252</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9838.252048670225</v>
       </c>
       <c r="Y6" t="n">
         <v>381.2705759157993</v>
       </c>
       <c r="Z6" t="n">
-        <v>103637606.8395346</v>
+        <v>474.7139999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.728071967764566e-07</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>87.80078017159987</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 26.040x + -10743.070</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10743.07042555574</v>
       </c>
       <c r="Y7" t="n">
         <v>366.6528996274645</v>
       </c>
       <c r="Z7" t="n">
-        <v>3081.494744177717</v>
+        <v>438.241</v>
       </c>
       <c r="AA7" t="n">
         <v>3.803486606084007e-06</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>87.90012402087255</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 27.273x + -11053.071</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11053.07098521811</v>
       </c>
       <c r="Y8" t="n">
         <v>363.6376069962431</v>
       </c>
       <c r="Z8" t="n">
-        <v>3043.814780033557</v>
+        <v>413.741</v>
       </c>
       <c r="AA8" t="n">
         <v>4.373673087624089e-06</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>87.97993307133902</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 28.352x + -11312.335</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11312.33455660986</v>
       </c>
       <c r="Y9" t="n">
         <v>369.9873394758301</v>
       </c>
       <c r="Z9" t="n">
-        <v>9104.316546793854</v>
+        <v>395.441</v>
       </c>
       <c r="AA9" t="n">
         <v>2.947415348728371e-07</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>88.09190839973874</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 30.017x + -11874.333</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11874.33313082993</v>
       </c>
       <c r="Y10" t="n">
         <v>358.0187008381943</v>
       </c>
       <c r="Z10" t="n">
-        <v>2969.661359649142</v>
+        <v>378.204</v>
       </c>
       <c r="AA10" t="n">
         <v>6.772476471591856e-06</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>88.1037037525636</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 30.204x + -11736.963</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11736.96339846924</v>
       </c>
       <c r="Y11" t="n">
         <v>360.5142991971231</v>
       </c>
       <c r="Z11" t="n">
-        <v>5922.624533486918</v>
+        <v>368.8920000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.456784505355195e-06</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>87.40998884539238</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 22.107x + -11058.032</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11058.03164845512</v>
       </c>
       <c r="Y2" t="n">
         <v>428.2258639481237</v>
       </c>
       <c r="Z2" t="n">
-        <v>18372.7964795937</v>
+        <v>500.3539999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.708124901436907e-07</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>87.82907848491389</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 26.380x + -12887.855</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-12887.85470734534</v>
       </c>
       <c r="Y3" t="n">
         <v>436.2390868813392</v>
       </c>
       <c r="Z3" t="n">
-        <v>714857312.7649179</v>
+        <v>417.432</v>
       </c>
       <c r="AA3" t="n">
         <v>1.731094755667596e-07</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>88.03561727392091</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 29.156x + -14096.625</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14096.6253668565</v>
       </c>
       <c r="Y4" t="n">
         <v>392.2418228770213</v>
       </c>
       <c r="Z4" t="n">
-        <v>14347.69680565677</v>
+        <v>377.727</v>
       </c>
       <c r="AA4" t="n">
         <v>1.853974146356537e-07</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>88.12590844652591</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 30.562x + -14593.081</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14593.08078356724</v>
       </c>
       <c r="Y5" t="n">
         <v>428.1113247978005</v>
       </c>
       <c r="Z5" t="n">
-        <v>36588883.84992374</v>
+        <v>356.744</v>
       </c>
       <c r="AA5" t="n">
         <v>1.659933458259396e-07</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>88.23523104501101</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 32.456x + -15346.342</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15346.34184152871</v>
       </c>
       <c r="Y6" t="n">
         <v>423.9579095881203</v>
       </c>
       <c r="Z6" t="n">
-        <v>27559905.67447949</v>
+        <v>335.6950000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.63809084954019e-07</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>88.26574326382118</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 33.028x + -15431.406</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-15431.40644278099</v>
       </c>
       <c r="Y7" t="n">
         <v>419.9025313780976</v>
       </c>
       <c r="Z7" t="n">
-        <v>22813193.89138057</v>
+        <v>329.619</v>
       </c>
       <c r="AA7" t="n">
         <v>1.6255153529867e-07</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>88.34692519291823</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 34.651x + -16062.703</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16062.70326834718</v>
       </c>
       <c r="Y8" t="n">
         <v>400.5301560943147</v>
       </c>
       <c r="Z8" t="n">
-        <v>6874.129375918969</v>
+        <v>316.491</v>
       </c>
       <c r="AA8" t="n">
         <v>7.464919215754058e-07</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>88.36326173207384</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 34.997x + -16030.590</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-16030.59039215619</v>
       </c>
       <c r="Y9" t="n">
         <v>412.4537415775835</v>
       </c>
       <c r="Z9" t="n">
-        <v>901410856.1699787</v>
+        <v>309.5690000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.605921673503404e-07</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>88.3117973395633</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 33.929x + -15278.701</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15278.70072850319</v>
       </c>
       <c r="Y10" t="n">
         <v>390.4344537883035</v>
       </c>
       <c r="Z10" t="n">
-        <v>3351.606138140507</v>
+        <v>306.232</v>
       </c>
       <c r="AA10" t="n">
         <v>3.70935487095687e-06</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>88.40333634760319</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 35.875x + -16101.650</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16101.64984084333</v>
       </c>
       <c r="Y11" t="n">
         <v>388.2930548595324</v>
       </c>
       <c r="Z11" t="n">
-        <v>3322.798733853723</v>
+        <v>297.874</v>
       </c>
       <c r="AA11" t="n">
         <v>2.929434986793159e-06</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>88.43765963813895</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 36.664x + -16319.707</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-16319.70746934681</v>
       </c>
       <c r="Y12" t="n">
         <v>402.5482859389144</v>
       </c>
       <c r="Z12" t="n">
-        <v>219749421.0854972</v>
+        <v>292.782</v>
       </c>
       <c r="AA12" t="n">
         <v>1.582254998207532e-07</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>88.48952368140284</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 37.923x + -16775.684</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16775.68393520089</v>
       </c>
       <c r="Y13" t="n">
         <v>399.4362182370824</v>
       </c>
       <c r="Z13" t="n">
-        <v>217884101.4122648</v>
+        <v>285.513</v>
       </c>
       <c r="AA13" t="n">
         <v>1.575533681273246e-07</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>88.43843403923236</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 36.682x + -15978.477</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15978.47705867695</v>
       </c>
       <c r="Y14" t="n">
         <v>387.243572223659</v>
       </c>
       <c r="Z14" t="n">
-        <v>6087.355515252417</v>
+        <v>284.0509999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>8.750494667108169e-07</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>88.4520607038823</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 37.005x + -15986.150</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-15986.14978403234</v>
       </c>
       <c r="Y15" t="n">
         <v>385.0033597714138</v>
       </c>
       <c r="Z15" t="n">
-        <v>5817.856239181757</v>
+        <v>283.2789999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>8.269584952541309e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>88.50172950716394</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 38.233x + -16410.358</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16410.35807759123</v>
       </c>
       <c r="Y16" t="n">
         <v>390.1298533925001</v>
       </c>
       <c r="Z16" t="n">
-        <v>424906154.8144028</v>
+        <v>277.4930000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.559476524407433e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>88.53229054254551</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 39.029x + -16628.039</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-16628.03869600047</v>
       </c>
       <c r="Y17" t="n">
         <v>387.0645065547251</v>
       </c>
       <c r="Z17" t="n">
-        <v>527789415.7056388</v>
+        <v>273.061</v>
       </c>
       <c r="AA17" t="n">
         <v>1.554655332137557e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>88.56643024143784</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 39.959x + -16898.867</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-16898.86726804942</v>
       </c>
       <c r="Y18" t="n">
         <v>384.0055298146076</v>
       </c>
       <c r="Z18" t="n">
-        <v>209938966.7393761</v>
+        <v>269.231</v>
       </c>
       <c r="AA18" t="n">
         <v>1.549660193808371e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>88.5755622336933</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 40.215x + -16834.996</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-16834.99572961427</v>
       </c>
       <c r="Y19" t="n">
         <v>369.914785747864</v>
       </c>
       <c r="Z19" t="n">
-        <v>3117.64811257039</v>
+        <v>264.191</v>
       </c>
       <c r="AA19" t="n">
         <v>4.150379421065077e-06</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>88.60138341235772</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 40.958x + -17014.745</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-17014.7453676991</v>
       </c>
       <c r="Y20" t="n">
         <v>367.7615643634669</v>
       </c>
       <c r="Z20" t="n">
-        <v>3092.98069709524</v>
+        <v>261.0170000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>4.719243108953146e-06</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>88.52127905446127</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 38.738x + -15826.615</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15826.61462063316</v>
       </c>
       <c r="Y21" t="n">
         <v>365.6442421361662</v>
       </c>
       <c r="Z21" t="n">
-        <v>3065.105472682255</v>
+        <v>263.503</v>
       </c>
       <c r="AA21" t="n">
         <v>4.50856728064152e-06</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>88.67967253573478</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 43.387x + -17783.630</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-17783.62994468227</v>
       </c>
       <c r="Y22" t="n">
         <v>363.5401248831968</v>
       </c>
       <c r="Z22" t="n">
-        <v>3041.305824953865</v>
+        <v>252.7429999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>6.226150934124446e-06</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.5734836262973</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.527x + -5264.725</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5264.72458753714</v>
       </c>
       <c r="Y2" t="n">
         <v>430.7569450103838</v>
       </c>
       <c r="Z2" t="n">
-        <v>233728674.5132036</v>
+        <v>1025.074</v>
       </c>
       <c r="AA2" t="n">
         <v>2.415788474583415e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>86.0032009398027</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.312x + -6368.239</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6368.238706289995</v>
       </c>
       <c r="Y3" t="n">
         <v>403.081108882269</v>
       </c>
       <c r="Z3" t="n">
-        <v>26865526.29293975</v>
+        <v>761.4280000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.09475894374022e-07</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.84456018329087</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.139x + -7917.759</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7917.759453026883</v>
       </c>
       <c r="Y4" t="n">
         <v>395.4896485780671</v>
       </c>
       <c r="Z4" t="n">
-        <v>216046876.3848027</v>
+        <v>613.395</v>
       </c>
       <c r="AA4" t="n">
         <v>1.927812295393479e-07</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>87.2567462518365</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.870x + -8929.433</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8929.433037612014</v>
       </c>
       <c r="Y5" t="n">
         <v>396.1013078597147</v>
       </c>
       <c r="Z5" t="n">
-        <v>9899.950515235945</v>
+        <v>531.818</v>
       </c>
       <c r="AA5" t="n">
         <v>2.690383414507065e-07</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>87.55762539885507</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.445x + -9911.451</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9911.451398944964</v>
       </c>
       <c r="Y6" t="n">
         <v>386.7729435961884</v>
       </c>
       <c r="Z6" t="n">
-        <v>947233320.0759394</v>
+        <v>473.7760000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.763108932738833e-07</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>87.71961191690619</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 25.112x + -10457.326</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10457.32644871787</v>
       </c>
       <c r="Y7" t="n">
         <v>382.5174943840916</v>
       </c>
       <c r="Z7" t="n">
-        <v>209577946.5805859</v>
+        <v>440.054</v>
       </c>
       <c r="AA7" t="n">
         <v>1.720373641015596e-07</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>87.89886347394258</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 27.257x + -11245.434</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11245.43405165313</v>
       </c>
       <c r="Y8" t="n">
         <v>368.5942465753271</v>
       </c>
       <c r="Z8" t="n">
-        <v>3091.854779228136</v>
+        <v>407.7500000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>4.253836186046018e-06</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>87.9207469114542</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 27.544x + -11125.368</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11125.36763713648</v>
       </c>
       <c r="Y9" t="n">
         <v>365.5545231100253</v>
       </c>
       <c r="Z9" t="n">
-        <v>3055.342962976627</v>
+        <v>392.219</v>
       </c>
       <c r="AA9" t="n">
         <v>4.187563762829413e-06</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>88.06866440834293</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 29.655x + -11897.308</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11897.30801714758</v>
       </c>
       <c r="Y10" t="n">
         <v>362.7931590103153</v>
       </c>
       <c r="Z10" t="n">
-        <v>3019.408839757034</v>
+        <v>370.448</v>
       </c>
       <c r="AA10" t="n">
         <v>5.576046445387152e-06</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>88.1680233395651</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 31.265x + -12434.172</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12434.17226967321</v>
       </c>
       <c r="Y11" t="n">
         <v>360.276349917771</v>
       </c>
       <c r="Z11" t="n">
-        <v>2987.28400260335</v>
+        <v>354.895</v>
       </c>
       <c r="AA11" t="n">
         <v>6.804308553158765e-06</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>86.61199063625102</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.892x + -8686.133</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8686.133135867789</v>
       </c>
       <c r="Y2" t="n">
         <v>452.35668962881</v>
       </c>
       <c r="Z2" t="n">
-        <v>247438428.0794368</v>
+        <v>638.0010000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.035226843614756e-07</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>87.61820935853832</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.042x + -11896.576</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11896.57602459269</v>
       </c>
       <c r="Y3" t="n">
         <v>441.236970068914</v>
       </c>
       <c r="Z3" t="n">
-        <v>125079789.1509634</v>
+        <v>452.424</v>
       </c>
       <c r="AA3" t="n">
         <v>1.809083805034442e-07</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.90968108703846</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 27.398x + -13325.243</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13325.24316002457</v>
       </c>
       <c r="Y4" t="n">
         <v>436.0491753386115</v>
       </c>
       <c r="Z4" t="n">
-        <v>387987452.8781702</v>
+        <v>392.71</v>
       </c>
       <c r="AA4" t="n">
         <v>1.738985204231838e-07</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>88.10998604028869</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 30.304x + -14629.671</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14629.67131829655</v>
       </c>
       <c r="Y5" t="n">
         <v>431.8986589084778</v>
       </c>
       <c r="Z5" t="n">
-        <v>31910299.39771348</v>
+        <v>359.264</v>
       </c>
       <c r="AA5" t="n">
         <v>1.700756659347028e-07</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>88.09375167779901</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 30.046x + -14209.247</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14209.24727128199</v>
       </c>
       <c r="Y6" t="n">
         <v>428.0160598089331</v>
       </c>
       <c r="Z6" t="n">
-        <v>467629884.2441313</v>
+        <v>346.229</v>
       </c>
       <c r="AA6" t="n">
         <v>1.68002551100011e-07</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>88.06670532332714</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 29.625x + -13763.947</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13763.94748817758</v>
       </c>
       <c r="Y7" t="n">
         <v>424.1785264245281</v>
       </c>
       <c r="Z7" t="n">
-        <v>125545190.288765</v>
+        <v>334.555</v>
       </c>
       <c r="AA7" t="n">
         <v>1.66198345384196e-07</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>88.29492502434373</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 33.593x + -15682.860</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15682.86009572078</v>
       </c>
       <c r="Y8" t="n">
         <v>413.3510388804626</v>
       </c>
       <c r="Z8" t="n">
-        <v>15685.6440730381</v>
+        <v>318.557</v>
       </c>
       <c r="AA8" t="n">
         <v>1.77094109916298e-07</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>88.31178839547577</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 33.929x + -15651.295</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15651.29473670315</v>
       </c>
       <c r="Y9" t="n">
         <v>416.7702582982151</v>
       </c>
       <c r="Z9" t="n">
-        <v>909589822.4757632</v>
+        <v>311.059</v>
       </c>
       <c r="AA9" t="n">
         <v>1.639971929839753e-07</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>88.33982469682809</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 34.502x + -15764.342</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15764.34154710978</v>
       </c>
       <c r="Y10" t="n">
         <v>412.4253798300946</v>
       </c>
       <c r="Z10" t="n">
-        <v>7686.457886692357</v>
+        <v>304.948</v>
       </c>
       <c r="AA10" t="n">
         <v>7.662815190856792e-07</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>88.37191918054657</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 35.183x + -15934.396</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15934.39619045957</v>
       </c>
       <c r="Y11" t="n">
         <v>392.1903711043747</v>
       </c>
       <c r="Z11" t="n">
-        <v>3362.49531787377</v>
+        <v>299.026</v>
       </c>
       <c r="AA11" t="n">
         <v>2.561791301832183e-06</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>88.41432945599126</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 36.124x + -16252.516</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-16252.51595046164</v>
       </c>
       <c r="Y12" t="n">
         <v>406.5696251295084</v>
       </c>
       <c r="Z12" t="n">
-        <v>7562.536343381692</v>
+        <v>293.3960000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.033533860087458e-06</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>88.41061103453872</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 36.040x + -16028.722</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16028.72150931268</v>
       </c>
       <c r="Y13" t="n">
         <v>403.8964437003165</v>
       </c>
       <c r="Z13" t="n">
-        <v>220028077.1227835</v>
+        <v>288.478</v>
       </c>
       <c r="AA13" t="n">
         <v>1.609640843267215e-07</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>88.43327254477968</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 36.561x + -16130.076</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16130.07587172526</v>
       </c>
       <c r="Y14" t="n">
         <v>391.4139537918428</v>
       </c>
       <c r="Z14" t="n">
-        <v>6274.182893957601</v>
+        <v>283.853</v>
       </c>
       <c r="AA14" t="n">
         <v>8.838704087528576e-07</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>88.30164900253993</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 33.726x + -14594.952</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14594.95151907926</v>
       </c>
       <c r="Y15" t="n">
         <v>397.9808730092059</v>
       </c>
       <c r="Z15" t="n">
-        <v>216786082.4330912</v>
+        <v>287.0189999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.59908970498482e-07</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>88.51491342104781</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 38.572x + -16806.840</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16806.83966202478</v>
       </c>
       <c r="Y16" t="n">
         <v>386.1011873896881</v>
       </c>
       <c r="Z16" t="n">
-        <v>6152.843472120463</v>
+        <v>273.194</v>
       </c>
       <c r="AA16" t="n">
         <v>1.338106733968226e-06</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>88.5165870612917</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 38.616x + -16665.981</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-16665.98065748631</v>
       </c>
       <c r="Y17" t="n">
         <v>392.1617665167183</v>
       </c>
       <c r="Z17" t="n">
-        <v>108141571.6773528</v>
+        <v>271.648</v>
       </c>
       <c r="AA17" t="n">
         <v>1.588498537872321e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>88.56988028413464</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 40.055x + -17201.665</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-17201.66456970658</v>
       </c>
       <c r="Y18" t="n">
         <v>389.2228096335514</v>
       </c>
       <c r="Z18" t="n">
-        <v>423823252.9383525</v>
+        <v>265.635</v>
       </c>
       <c r="AA18" t="n">
         <v>1.583740140481801e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>88.54107988918297</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 39.264x + -16648.479</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-16648.47850029673</v>
       </c>
       <c r="Y19" t="n">
         <v>386.3321753760547</v>
       </c>
       <c r="Z19" t="n">
-        <v>421642121.2288289</v>
+        <v>264.2040000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.579302543440558e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>88.7222515776574</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 44.834x + -19179.413</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-19179.41293714672</v>
       </c>
       <c r="Y20" t="n">
         <v>372.524350903414</v>
       </c>
       <c r="Z20" t="n">
-        <v>3137.765914510968</v>
+        <v>253.407</v>
       </c>
       <c r="AA20" t="n">
         <v>3.80558198294671e-06</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>88.46246401890861</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 37.256x + -15400.264</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15400.26373223274</v>
       </c>
       <c r="Y21" t="n">
         <v>370.3841944268697</v>
       </c>
       <c r="Z21" t="n">
-        <v>3110.482970582952</v>
+        <v>262.4709999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>5.060048837761327e-06</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>88.69849085206897</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 44.015x + -18393.186</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-18393.18569421029</v>
       </c>
       <c r="Y22" t="n">
         <v>368.3066786447217</v>
       </c>
       <c r="Z22" t="n">
-        <v>3088.221134289601</v>
+        <v>249.913</v>
       </c>
       <c r="AA22" t="n">
         <v>3.946012337124171e-06</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.49918395916609</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.384x + -5250.953</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5250.953486006958</v>
       </c>
       <c r="Y2" t="n">
         <v>428.2332462765251</v>
       </c>
       <c r="Z2" t="n">
-        <v>176854762.310507</v>
+        <v>1020.75</v>
       </c>
       <c r="AA2" t="n">
         <v>2.503146688684804e-07</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>86.10331232512375</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.681x + -6428.418</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6428.417618295207</v>
       </c>
       <c r="Y3" t="n">
         <v>378.5659046197014</v>
       </c>
       <c r="Z3" t="n">
-        <v>3251.976403630118</v>
+        <v>727.758</v>
       </c>
       <c r="AA3" t="n">
         <v>2.638314156025119e-06</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.95039915777241</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.770x + -7975.321</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7975.320502822983</v>
       </c>
       <c r="Y4" t="n">
         <v>387.4135014371778</v>
       </c>
       <c r="Z4" t="n">
-        <v>5878.512002361233</v>
+        <v>574.908</v>
       </c>
       <c r="AA4" t="n">
         <v>6.027754898540164e-07</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>87.43536910256242</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.326x + -9362.085</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9362.084669412065</v>
       </c>
       <c r="Y5" t="n">
         <v>383.8299045016033</v>
       </c>
       <c r="Z5" t="n">
-        <v>419254175.9051671</v>
+        <v>486.778</v>
       </c>
       <c r="AA5" t="n">
         <v>1.82381194019089e-07</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.7556883062751</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 25.516x + -10601.220</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10601.21969535638</v>
       </c>
       <c r="Y6" t="n">
         <v>368.8728782930354</v>
       </c>
       <c r="Z6" t="n">
-        <v>3105.746169602751</v>
+        <v>428.646</v>
       </c>
       <c r="AA6" t="n">
         <v>3.379624438924234e-06</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.99494859295974</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 28.564x + -11797.636</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11797.63606719903</v>
       </c>
       <c r="Y7" t="n">
         <v>366.1889323686365</v>
       </c>
       <c r="Z7" t="n">
-        <v>3069.469555446921</v>
+        <v>388.851</v>
       </c>
       <c r="AA7" t="n">
         <v>4.354806899301846e-06</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>88.06013333914801</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 29.525x + -11910.999</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11910.99916511957</v>
       </c>
       <c r="Y8" t="n">
         <v>363.3927720476658</v>
       </c>
       <c r="Z8" t="n">
-        <v>3029.728417792315</v>
+        <v>363.164</v>
       </c>
       <c r="AA8" t="n">
         <v>5.595083832219959e-06</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>88.16340468963088</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 31.186x + -12423.381</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12423.38149510681</v>
       </c>
       <c r="Y9" t="n">
         <v>365.6700232995036</v>
       </c>
       <c r="Z9" t="n">
-        <v>4894.766165784499</v>
+        <v>344.14</v>
       </c>
       <c r="AA9" t="n">
         <v>1.110762989935804e-06</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>88.24712784817928</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 32.677x + -12879.701</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12879.70078544074</v>
       </c>
       <c r="Y10" t="n">
         <v>362.3122293056554</v>
       </c>
       <c r="Z10" t="n">
-        <v>393741041.4451929</v>
+        <v>329.702</v>
       </c>
       <c r="AA10" t="n">
         <v>1.648926069873349e-07</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>88.32050250286623</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 34.105x + -13285.898</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13285.89821834282</v>
       </c>
       <c r="Y11" t="n">
         <v>358.4391175287689</v>
       </c>
       <c r="Z11" t="n">
-        <v>33422879.31864697</v>
+        <v>315.8560000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.632150073337587e-07</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.65441705284117</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 17.106x + -8593.638</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8593.638004325428</v>
       </c>
       <c r="Y2" t="n">
         <v>445.7947041603194</v>
       </c>
       <c r="Z2" t="n">
-        <v>244050227.6888387</v>
+        <v>608.9560000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.071748836608976e-07</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>87.62321067557258</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.093x + -11840.649</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11840.64945193359</v>
       </c>
       <c r="Y3" t="n">
         <v>436.9700326005391</v>
       </c>
       <c r="Z3" t="n">
-        <v>341020120.6648586</v>
+        <v>444.6999999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.865560298812348e-07</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.88393660932623</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 27.064x + -13041.572</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13041.57198786413</v>
       </c>
       <c r="Y4" t="n">
         <v>432.5868409983169</v>
       </c>
       <c r="Z4" t="n">
-        <v>27750175.75858851</v>
+        <v>383.852</v>
       </c>
       <c r="AA4" t="n">
         <v>1.787540813147449e-07</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>88.04612989654245</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.313x + -13975.832</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13975.83191713709</v>
       </c>
       <c r="Y5" t="n">
         <v>428.6187214448487</v>
       </c>
       <c r="Z5" t="n">
-        <v>234348620.6758281</v>
+        <v>351.7339999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.752994282087224e-07</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>88.05673054153104</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 29.473x + -13808.292</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13808.29235260107</v>
       </c>
       <c r="Y6" t="n">
         <v>424.5595634917665</v>
       </c>
       <c r="Z6" t="n">
-        <v>128756446.3089024</v>
+        <v>337.012</v>
       </c>
       <c r="AA6" t="n">
         <v>1.729583716904129e-07</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>88.27044688663949</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 33.117x + -15532.443</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-15532.44254583502</v>
       </c>
       <c r="Y7" t="n">
         <v>420.4315652067328</v>
       </c>
       <c r="Z7" t="n">
-        <v>118615617.0548192</v>
+        <v>316.075</v>
       </c>
       <c r="AA7" t="n">
         <v>1.712206307714624e-07</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>88.24290423031162</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 32.598x + -15019.597</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15019.59746420028</v>
       </c>
       <c r="Y8" t="n">
         <v>416.3770116231983</v>
       </c>
       <c r="Z8" t="n">
-        <v>454588972.0921235</v>
+        <v>310.097</v>
       </c>
       <c r="AA8" t="n">
         <v>1.699571050475663e-07</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>88.29186155096993</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 33.533x + -15295.800</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15295.7998640503</v>
       </c>
       <c r="Y9" t="n">
         <v>393.7922482824788</v>
       </c>
       <c r="Z9" t="n">
-        <v>3380.332953377035</v>
+        <v>301.028</v>
       </c>
       <c r="AA9" t="n">
         <v>3.299760744514844e-06</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>88.33010779802876</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 34.301x + -15496.521</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15496.52076257386</v>
       </c>
       <c r="Y10" t="n">
         <v>393.3558551742232</v>
       </c>
       <c r="Z10" t="n">
-        <v>3350.947418589739</v>
+        <v>293.661</v>
       </c>
       <c r="AA10" t="n">
         <v>2.133772204584533e-06</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>88.40474625744268</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 35.907x + -16136.333</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16136.33295058607</v>
       </c>
       <c r="Y11" t="n">
         <v>405.6987242050351</v>
       </c>
       <c r="Z11" t="n">
-        <v>223496760.40505</v>
+        <v>285.8539999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.671143237273648e-07</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>88.2793501247301</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 33.289x + -14647.019</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14647.01905829087</v>
       </c>
       <c r="Y12" t="n">
         <v>406.6718598625063</v>
       </c>
       <c r="Z12" t="n">
-        <v>10426.34676195086</v>
+        <v>287.692</v>
       </c>
       <c r="AA12" t="n">
         <v>2.626741760332304e-07</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>88.40617885970838</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 35.939x + -15797.921</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15797.92056487545</v>
       </c>
       <c r="Y13" t="n">
         <v>399.4162991703378</v>
       </c>
       <c r="Z13" t="n">
-        <v>123994034.9297559</v>
+        <v>278.355</v>
       </c>
       <c r="AA13" t="n">
         <v>1.657267705748101e-07</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>88.35504712138336</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 34.822x + -15094.628</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15094.6284375091</v>
       </c>
       <c r="Y14" t="n">
         <v>400.2324335157696</v>
       </c>
       <c r="Z14" t="n">
-        <v>10470.88867216568</v>
+        <v>278.026</v>
       </c>
       <c r="AA14" t="n">
         <v>3.269943740968406e-07</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>88.47903605119467</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 37.662x + -16328.454</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-16328.45434062075</v>
       </c>
       <c r="Y15" t="n">
         <v>393.4107771894506</v>
       </c>
       <c r="Z15" t="n">
-        <v>107723215.7499345</v>
+        <v>269.083</v>
       </c>
       <c r="AA15" t="n">
         <v>1.645584611816782e-07</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>88.49065533624402</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 37.952x + -16298.552</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16298.55191694088</v>
       </c>
       <c r="Y16" t="n">
         <v>390.4918075518529</v>
       </c>
       <c r="Z16" t="n">
-        <v>217876328.0257168</v>
+        <v>264.576</v>
       </c>
       <c r="AA16" t="n">
         <v>1.640303864404856e-07</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>88.44194140277973</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 36.765x + -15585.799</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-15585.79937136267</v>
       </c>
       <c r="Y17" t="n">
         <v>375.5062330050512</v>
       </c>
       <c r="Z17" t="n">
-        <v>3172.946271935872</v>
+        <v>266.073</v>
       </c>
       <c r="AA17" t="n">
         <v>4.241315651755685e-06</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>88.53242985999732</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 39.033x + -16502.586</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-16502.58576815755</v>
       </c>
       <c r="Y18" t="n">
         <v>373.3998191523149</v>
       </c>
       <c r="Z18" t="n">
-        <v>3149.076553888359</v>
+        <v>258.6390000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>3.07087961023799e-06</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>88.55674945260151</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 39.691x + -16651.589</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-16651.58944383805</v>
       </c>
       <c r="Y19" t="n">
         <v>371.3188852355273</v>
       </c>
       <c r="Z19" t="n">
-        <v>3123.663719967379</v>
+        <v>255.449</v>
       </c>
       <c r="AA19" t="n">
         <v>4.18720346893616e-06</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>88.58473711769085</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 40.476x + -16851.461</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16851.46139508637</v>
       </c>
       <c r="Y20" t="n">
         <v>369.2982471975364</v>
       </c>
       <c r="Z20" t="n">
-        <v>3099.302276693664</v>
+        <v>251.033</v>
       </c>
       <c r="AA20" t="n">
         <v>4.942202739543038e-06</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>88.60130208001813</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 40.956x + -16913.710</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16913.70999556211</v>
       </c>
       <c r="Y21" t="n">
         <v>367.1860219749532</v>
       </c>
       <c r="Z21" t="n">
-        <v>3075.127425408357</v>
+        <v>250.662</v>
       </c>
       <c r="AA21" t="n">
         <v>5.907859228920702e-06</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>88.60453112993389</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 41.050x + -16789.938</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-16789.93781409243</v>
       </c>
       <c r="Y22" t="n">
         <v>365.2080411536498</v>
       </c>
       <c r="Z22" t="n">
-        <v>3048.036387501885</v>
+        <v>247.7919999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>5.649870250503162e-06</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>85.07196918455699</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.598x + -5304.874</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5304.874138784559</v>
       </c>
       <c r="Y2" t="n">
         <v>401.1043403775762</v>
       </c>
       <c r="Z2" t="n">
-        <v>108907247.952289</v>
+        <v>894.4929999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>2.373384584861524e-07</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>87.01464537540696</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 19.175x + -8006.075</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8006.074614647086</v>
       </c>
       <c r="Y3" t="n">
         <v>381.3629202390516</v>
       </c>
       <c r="Z3" t="n">
-        <v>9439.87884057199</v>
+        <v>550.8199999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>2.658933688911196e-07</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.67743692957593</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 24.656x + -10066.136</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10066.13555488129</v>
       </c>
       <c r="Y4" t="n">
         <v>364.5311168886443</v>
       </c>
       <c r="Z4" t="n">
-        <v>3058.22627779957</v>
+        <v>426.4520000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>3.609211404066198e-06</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>88.08235552617823</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.867x + -12164.623</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12164.62309624022</v>
       </c>
       <c r="Y5" t="n">
         <v>361.9718251685001</v>
       </c>
       <c r="Z5" t="n">
-        <v>3015.894685735782</v>
+        <v>361.5520000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>5.520239378837497e-06</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>88.1532222126736</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 31.014x + -12301.637</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12301.63704658648</v>
       </c>
       <c r="Y6" t="n">
         <v>364.3538657862861</v>
       </c>
       <c r="Z6" t="n">
-        <v>105464050.9517256</v>
+        <v>333.287</v>
       </c>
       <c r="AA6" t="n">
         <v>1.705058324283315e-07</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>88.22827363210166</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 32.329x + -12591.555</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12591.55523584506</v>
       </c>
       <c r="Y7" t="n">
         <v>359.2365938796329</v>
       </c>
       <c r="Z7" t="n">
-        <v>30867463.59770979</v>
+        <v>313.081</v>
       </c>
       <c r="AA7" t="n">
         <v>1.680696565424466e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>88.32155903305907</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 34.127x + -13108.619</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13108.61851085418</v>
       </c>
       <c r="Y8" t="n">
         <v>354.16747354124</v>
       </c>
       <c r="Z8" t="n">
-        <v>289119563.5671461</v>
+        <v>297.344</v>
       </c>
       <c r="AA8" t="n">
         <v>1.667270538946964e-07</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>88.39740103072994</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 35.742x + -13545.505</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13545.50494930807</v>
       </c>
       <c r="Y9" t="n">
         <v>349.3739113736689</v>
       </c>
       <c r="Z9" t="n">
-        <v>474103179.0063043</v>
+        <v>284.604</v>
       </c>
       <c r="AA9" t="n">
         <v>1.655311809901298e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>88.4311182282699</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 36.511x + -13638.588</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13638.58811045589</v>
       </c>
       <c r="Y10" t="n">
         <v>345.0101471185797</v>
       </c>
       <c r="Z10" t="n">
-        <v>187649832.029548</v>
+        <v>277.068</v>
       </c>
       <c r="AA10" t="n">
         <v>1.646770464454235e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>88.41999804012282</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 36.254x + -13312.564</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13312.56357781967</v>
       </c>
       <c r="Y11" t="n">
         <v>333.1721359161679</v>
       </c>
       <c r="Z11" t="n">
-        <v>5602.47840505856</v>
+        <v>272.275</v>
       </c>
       <c r="AA11" t="n">
         <v>1.840085250934307e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>87.53951509543693</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 23.272x + -12344.378</t>
-        </is>
+      <c r="W2" t="n">
+        <v>23.27206089065146</v>
       </c>
       <c r="X2" t="n">
         <v>-12344.37768874648</v>
@@ -600,7 +598,7 @@
         <v>467.6570940016832</v>
       </c>
       <c r="Z2" t="n">
-        <v>485.686</v>
+        <v>256485948.4332564</v>
       </c>
       <c r="AA2" t="n">
         <v>1.765856924959165e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.78614871101689</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 25.868x + -13489.038</t>
-        </is>
+      <c r="W3" t="n">
+        <v>25.8677099484165</v>
       </c>
       <c r="X3" t="n">
         <v>-13489.03786423497</v>
@@ -652,7 +648,7 @@
         <v>460.842479074512</v>
       </c>
       <c r="Z3" t="n">
-        <v>439.384</v>
+        <v>630266120.0473253</v>
       </c>
       <c r="AA3" t="n">
         <v>1.708017582691505e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.89029421361499</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.146x + -13863.965</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.14590986891531</v>
       </c>
       <c r="X4" t="n">
         <v>-13863.96538051371</v>
@@ -704,7 +698,7 @@
         <v>436.8494436332582</v>
       </c>
       <c r="Z4" t="n">
-        <v>411.664</v>
+        <v>18892.58923630365</v>
       </c>
       <c r="AA4" t="n">
         <v>1.661877335263083e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>88.05805267390988</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.493x + -14903.051</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.49299259925347</v>
       </c>
       <c r="X5" t="n">
         <v>-14903.05133271452</v>
@@ -756,7 +748,7 @@
         <v>448.7462546299487</v>
       </c>
       <c r="Z5" t="n">
-        <v>386.404</v>
+        <v>491689290.2403167</v>
       </c>
       <c r="AA5" t="n">
         <v>1.642305570667434e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>88.07866841055484</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 29.810x + -14783.958</t>
-        </is>
+      <c r="W6" t="n">
+        <v>29.80969128565701</v>
       </c>
       <c r="X6" t="n">
         <v>-14783.95811005138</v>
@@ -808,7 +798,7 @@
         <v>443.3097998353818</v>
       </c>
       <c r="Z6" t="n">
-        <v>376.839</v>
+        <v>485544532.7090031</v>
       </c>
       <c r="AA6" t="n">
         <v>1.624525978720059e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>88.10811613630992</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 30.274x + -14768.774</t>
-        </is>
+      <c r="W7" t="n">
+        <v>30.27403320798036</v>
       </c>
       <c r="X7" t="n">
         <v>-14768.77376278749</v>
@@ -860,7 +848,7 @@
         <v>438.1425064061951</v>
       </c>
       <c r="Z7" t="n">
-        <v>365.185</v>
+        <v>120043184.2007365</v>
       </c>
       <c r="AA7" t="n">
         <v>1.608399886353592e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>88.20335717492929</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 31.880x + -15407.875</t>
-        </is>
+      <c r="W8" t="n">
+        <v>31.88001430985865</v>
       </c>
       <c r="X8" t="n">
         <v>-15407.87487417757</v>
@@ -912,7 +898,7 @@
         <v>379.6747431750197</v>
       </c>
       <c r="Z8" t="n">
-        <v>353.241</v>
+        <v>14352.53679729584</v>
       </c>
       <c r="AA8" t="n">
         <v>1.88059960962276e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>88.27073029357051</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 33.123x + -15823.338</t>
-        </is>
+      <c r="W9" t="n">
+        <v>33.12287317267284</v>
       </c>
       <c r="X9" t="n">
         <v>-15823.33750516756</v>
@@ -964,7 +948,7 @@
         <v>428.0859084856359</v>
       </c>
       <c r="Z9" t="n">
-        <v>341.3070000000001</v>
+        <v>934326069.9412551</v>
       </c>
       <c r="AA9" t="n">
         <v>1.582859134618542e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>88.22851940606468</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 32.333x + -15136.251</t>
-        </is>
+      <c r="W10" t="n">
+        <v>32.33313509996982</v>
       </c>
       <c r="X10" t="n">
         <v>-15136.25084606659</v>
@@ -1016,7 +998,7 @@
         <v>423.2099813772927</v>
       </c>
       <c r="Z10" t="n">
-        <v>336.863</v>
+        <v>236038914.182063</v>
       </c>
       <c r="AA10" t="n">
         <v>1.57251038502611e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>88.29013535664943</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 33.499x + -15531.253</t>
-        </is>
+      <c r="W11" t="n">
+        <v>33.49900806166463</v>
       </c>
       <c r="X11" t="n">
         <v>-15531.25305697876</v>
@@ -1068,7 +1048,7 @@
         <v>418.6770996582599</v>
       </c>
       <c r="Z11" t="n">
-        <v>328.858</v>
+        <v>344760190.966718</v>
       </c>
       <c r="AA11" t="n">
         <v>1.563857707125518e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>87.7226039646996</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 25.145x + -12822.028</t>
-        </is>
+      <c r="W2" t="n">
+        <v>25.14521032911586</v>
       </c>
       <c r="X2" t="n">
         <v>-12822.02778880958</v>
@@ -1266,7 +1244,7 @@
         <v>449.6745171879671</v>
       </c>
       <c r="Z2" t="n">
-        <v>381.455</v>
+        <v>42554130.69681846</v>
       </c>
       <c r="AA2" t="n">
         <v>1.835511574532325e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>87.94837269523504</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 27.915x + -13557.950</t>
-        </is>
+      <c r="W3" t="n">
+        <v>27.91505518640042</v>
       </c>
       <c r="X3" t="n">
         <v>-13557.94999070565</v>
@@ -1318,7 +1294,7 @@
         <v>438.4540737227541</v>
       </c>
       <c r="Z3" t="n">
-        <v>329.179</v>
+        <v>246431000.570932</v>
       </c>
       <c r="AA3" t="n">
         <v>1.763430389738114e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>88.17854880117901</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 31.446x + -15147.335</t>
-        </is>
+      <c r="W4" t="n">
+        <v>31.44551813616913</v>
       </c>
       <c r="X4" t="n">
         <v>-15147.33515707951</v>
@@ -1370,7 +1344,7 @@
         <v>433.2248310180203</v>
       </c>
       <c r="Z4" t="n">
-        <v>304.09</v>
+        <v>25393117.07049244</v>
       </c>
       <c r="AA4" t="n">
         <v>1.732865694075292e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>88.16927968497635</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 31.286x + -14808.520</t>
-        </is>
+      <c r="W5" t="n">
+        <v>31.2861988063765</v>
       </c>
       <c r="X5" t="n">
         <v>-14808.5196472664</v>
@@ -1422,7 +1394,7 @@
         <v>428.8137887709896</v>
       </c>
       <c r="Z5" t="n">
-        <v>294.957</v>
+        <v>467768447.6888936</v>
       </c>
       <c r="AA5" t="n">
         <v>1.718479741523072e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>88.32880186537525</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 34.275x + -16171.688</t>
-        </is>
+      <c r="W6" t="n">
+        <v>34.27452972360252</v>
       </c>
       <c r="X6" t="n">
         <v>-16171.68798660787</v>
@@ -1474,7 +1444,7 @@
         <v>408.1742188563638</v>
       </c>
       <c r="Z6" t="n">
-        <v>281.806</v>
+        <v>7009.65058287773</v>
       </c>
       <c r="AA6" t="n">
         <v>6.919311721271531e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>88.33883013400482</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 34.482x + -16045.389</t>
-        </is>
+      <c r="W7" t="n">
+        <v>34.48155769680275</v>
       </c>
       <c r="X7" t="n">
         <v>-16045.38937363871</v>
@@ -1526,7 +1494,7 @@
         <v>420.4195331226477</v>
       </c>
       <c r="Z7" t="n">
-        <v>274.538</v>
+        <v>25072149.92516794</v>
       </c>
       <c r="AA7" t="n">
         <v>1.692610012807808e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>88.41648753791699</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 36.174x + -16726.776</t>
-        </is>
+      <c r="W8" t="n">
+        <v>36.17350164897743</v>
       </c>
       <c r="X8" t="n">
         <v>-16726.77627878552</v>
@@ -1578,7 +1544,7 @@
         <v>397.3689196272579</v>
       </c>
       <c r="Z8" t="n">
-        <v>269.574</v>
+        <v>3410.637819077788</v>
       </c>
       <c r="AA8" t="n">
         <v>3.318479908176496e-06</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>88.38809614662625</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.536x + -16205.029</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.53602944907729</v>
       </c>
       <c r="X9" t="n">
         <v>-16205.02873704155</v>
@@ -1630,7 +1594,7 @@
         <v>395.4983703746601</v>
       </c>
       <c r="Z9" t="n">
-        <v>267.9109999999999</v>
+        <v>3382.47338464426</v>
       </c>
       <c r="AA9" t="n">
         <v>2.679114916044387e-06</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>88.48458316352</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 37.800x + -17172.754</t>
-        </is>
+      <c r="W10" t="n">
+        <v>37.79977698829273</v>
       </c>
       <c r="X10" t="n">
         <v>-17172.75378590349</v>
@@ -1682,7 +1644,7 @@
         <v>409.177831085275</v>
       </c>
       <c r="Z10" t="n">
-        <v>261.2500000000001</v>
+        <v>446354202.0403723</v>
       </c>
       <c r="AA10" t="n">
         <v>1.676641170578329e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>88.4780430744419</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 37.637x + -16898.737</t>
-        </is>
+      <c r="W11" t="n">
+        <v>37.63726944066111</v>
       </c>
       <c r="X11" t="n">
         <v>-16898.73726182366</v>
@@ -1734,7 +1694,7 @@
         <v>409.0010012465469</v>
       </c>
       <c r="Z11" t="n">
-        <v>258.436</v>
+        <v>10607.0661543138</v>
       </c>
       <c r="AA11" t="n">
         <v>2.560644274500548e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>88.43660816401631</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 36.639x + -16228.824</t>
-        </is>
+      <c r="W12" t="n">
+        <v>36.63928501116852</v>
       </c>
       <c r="X12" t="n">
         <v>-16228.82403837326</v>
@@ -1786,7 +1744,7 @@
         <v>400.011940678606</v>
       </c>
       <c r="Z12" t="n">
-        <v>257.948</v>
+        <v>6002.323577819623</v>
       </c>
       <c r="AA12" t="n">
         <v>4.522591193554731e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>88.42629967368011</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 36.399x + -15942.187</t>
-        </is>
+      <c r="W13" t="n">
+        <v>36.39916059435038</v>
       </c>
       <c r="X13" t="n">
         <v>-15942.18692873509</v>
@@ -1838,7 +1794,7 @@
         <v>389.3982734493844</v>
       </c>
       <c r="Z13" t="n">
-        <v>254.417</v>
+        <v>6314.678051446853</v>
       </c>
       <c r="AA13" t="n">
         <v>1.299234505709092e-06</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>88.52159239249009</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 38.746x + -16936.366</t>
-        </is>
+      <c r="W14" t="n">
+        <v>38.74646128319421</v>
       </c>
       <c r="X14" t="n">
         <v>-16936.36643620468</v>
@@ -1890,7 +1844,7 @@
         <v>396.5011400072781</v>
       </c>
       <c r="Z14" t="n">
-        <v>248.977</v>
+        <v>435210888.7657615</v>
       </c>
       <c r="AA14" t="n">
         <v>1.655031488858451e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>88.51125202708421</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 38.477x + -16643.303</t>
-        </is>
+      <c r="W15" t="n">
+        <v>38.47722089551421</v>
       </c>
       <c r="X15" t="n">
         <v>-16643.30296134172</v>
@@ -1942,7 +1894,7 @@
         <v>393.5601479490324</v>
       </c>
       <c r="Z15" t="n">
-        <v>246.5700000000001</v>
+        <v>214651657.0973744</v>
       </c>
       <c r="AA15" t="n">
         <v>1.650238820506533e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>88.53887902477388</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 39.205x + -16846.483</t>
-        </is>
+      <c r="W16" t="n">
+        <v>39.20507593103612</v>
       </c>
       <c r="X16" t="n">
         <v>-16846.48349964605</v>
@@ -1994,7 +1944,7 @@
         <v>378.0915880934682</v>
       </c>
       <c r="Z16" t="n">
-        <v>243.208</v>
+        <v>3200.021776007199</v>
       </c>
       <c r="AA16" t="n">
         <v>3.959794187255251e-06</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>88.55207436504415</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 39.563x + -16857.019</t>
-        </is>
+      <c r="W17" t="n">
+        <v>39.56251670272344</v>
       </c>
       <c r="X17" t="n">
         <v>-16857.01893624054</v>
@@ -2046,7 +1994,7 @@
         <v>376.0505910099079</v>
       </c>
       <c r="Z17" t="n">
-        <v>241.561</v>
+        <v>3175.754908420079</v>
       </c>
       <c r="AA17" t="n">
         <v>3.546383489236969e-06</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>88.60092914736765</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 40.945x + -17362.770</t>
-        </is>
+      <c r="W18" t="n">
+        <v>40.94459638364689</v>
       </c>
       <c r="X18" t="n">
         <v>-17362.76992330362</v>
@@ -2098,7 +2044,7 @@
         <v>374.0487902565378</v>
       </c>
       <c r="Z18" t="n">
-        <v>238.047</v>
+        <v>3150.450023124124</v>
       </c>
       <c r="AA18" t="n">
         <v>4.344126717681031e-06</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>88.57576865845618</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 40.221x + -16876.748</t>
-        </is>
+      <c r="W19" t="n">
+        <v>40.22097843238722</v>
       </c>
       <c r="X19" t="n">
         <v>-16876.74777693363</v>
@@ -2150,7 +2094,7 @@
         <v>372.049145487165</v>
       </c>
       <c r="Z19" t="n">
-        <v>238.684</v>
+        <v>3127.323934210941</v>
       </c>
       <c r="AA19" t="n">
         <v>3.972757512800434e-06</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>88.55961358739191</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 39.770x + -16516.712</t>
-        </is>
+      <c r="W20" t="n">
+        <v>39.76968146326256</v>
       </c>
       <c r="X20" t="n">
         <v>-16516.71193339312</v>
@@ -2202,7 +2144,7 @@
         <v>370.0793780290469</v>
       </c>
       <c r="Z20" t="n">
-        <v>237.926</v>
+        <v>3102.817741932373</v>
       </c>
       <c r="AA20" t="n">
         <v>4.487402432016493e-06</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>88.59781360725368</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 40.854x + -16857.079</t>
-        </is>
+      <c r="W21" t="n">
+        <v>40.85358472405958</v>
       </c>
       <c r="X21" t="n">
         <v>-16857.07896105192</v>
@@ -2254,7 +2194,7 @@
         <v>368.1090043012</v>
       </c>
       <c r="Z21" t="n">
-        <v>233.692</v>
+        <v>3080.740831432381</v>
       </c>
       <c r="AA21" t="n">
         <v>5.742969046266379e-06</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>88.57623627401499</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 40.234x + -16423.914</t>
-        </is>
+      <c r="W22" t="n">
+        <v>40.23419390030874</v>
       </c>
       <c r="X22" t="n">
         <v>-16423.9140367922</v>
@@ -2306,7 +2244,7 @@
         <v>366.0718103345478</v>
       </c>
       <c r="Z22" t="n">
-        <v>233.659</v>
+        <v>3057.675703850157</v>
       </c>
       <c r="AA22" t="n">
         <v>5.641388053161204e-06</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>87.50473203768817</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.947x + -12123.842</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.94725548113249</v>
       </c>
       <c r="X2" t="n">
         <v>-12123.84202056224</v>
@@ -2504,7 +2440,7 @@
         <v>460.6238995794369</v>
       </c>
       <c r="Z2" t="n">
-        <v>492.792</v>
+        <v>1006766927.235635</v>
       </c>
       <c r="AA2" t="n">
         <v>1.774403400401903e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>87.99565485570862</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 28.574x + -14481.426</t>
-        </is>
+      <c r="W3" t="n">
+        <v>28.57412331729682</v>
       </c>
       <c r="X3" t="n">
         <v>-14481.42614730383</v>
@@ -2556,7 +2490,7 @@
         <v>450.2200509822064</v>
       </c>
       <c r="Z3" t="n">
-        <v>390.406</v>
+        <v>184198450.6248948</v>
       </c>
       <c r="AA3" t="n">
         <v>1.664567588103265e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>88.1359397460767</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 30.726x + -15304.821</t>
-        </is>
+      <c r="W4" t="n">
+        <v>30.72624013131347</v>
       </c>
       <c r="X4" t="n">
         <v>-15304.82075703165</v>
@@ -2608,7 +2540,7 @@
         <v>445.3684382892027</v>
       </c>
       <c r="Z4" t="n">
-        <v>357.253</v>
+        <v>850327921.6281017</v>
       </c>
       <c r="AA4" t="n">
         <v>1.625654406343331e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>88.24226566809949</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 32.586x + -16064.317</t>
-        </is>
+      <c r="W5" t="n">
+        <v>32.5861551470263</v>
       </c>
       <c r="X5" t="n">
         <v>-16064.31660664211</v>
@@ -2660,7 +2590,7 @@
         <v>441.057126885874</v>
       </c>
       <c r="Z5" t="n">
-        <v>338.177</v>
+        <v>721825974.9817973</v>
       </c>
       <c r="AA5" t="n">
         <v>1.603182105650482e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>88.2628309136518</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 32.972x + -16013.826</t>
-        </is>
+      <c r="W6" t="n">
+        <v>32.97216275140337</v>
       </c>
       <c r="X6" t="n">
         <v>-16013.82608106867</v>
@@ -2712,7 +2640,7 @@
         <v>381.922818856085</v>
       </c>
       <c r="Z6" t="n">
-        <v>326.828</v>
+        <v>14479.40661746183</v>
       </c>
       <c r="AA6" t="n">
         <v>1.834295378082544e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>88.31719934723067</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 34.038x + -16357.287</t>
-        </is>
+      <c r="W7" t="n">
+        <v>34.03808028109797</v>
       </c>
       <c r="X7" t="n">
         <v>-16357.28705731489</v>
@@ -2764,7 +2690,7 @@
         <v>385.6662286725656</v>
       </c>
       <c r="Z7" t="n">
-        <v>317.366</v>
+        <v>14336.89875579788</v>
       </c>
       <c r="AA7" t="n">
         <v>2.052840766674812e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>88.3812777923025</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 35.386x + -16865.195</t>
-        </is>
+      <c r="W8" t="n">
+        <v>35.38626601000009</v>
       </c>
       <c r="X8" t="n">
         <v>-16865.19531556046</v>
@@ -2816,7 +2740,7 @@
         <v>428.163097075322</v>
       </c>
       <c r="Z8" t="n">
-        <v>310.542</v>
+        <v>23741318.15268247</v>
       </c>
       <c r="AA8" t="n">
         <v>1.561360683189014e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>88.40152683659176</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.835x + -16874.717</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.83476719408563</v>
       </c>
       <c r="X9" t="n">
         <v>-16874.71697691734</v>
@@ -2868,7 +2790,7 @@
         <v>424.128099526301</v>
       </c>
       <c r="Z9" t="n">
-        <v>303.485</v>
+        <v>29019382.78923294</v>
       </c>
       <c r="AA9" t="n">
         <v>1.55284447976298e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>88.44911893954631</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 36.935x + -17247.439</t>
-        </is>
+      <c r="W10" t="n">
+        <v>36.93499599502281</v>
       </c>
       <c r="X10" t="n">
         <v>-17247.43865135637</v>
@@ -2920,7 +2840,7 @@
         <v>420.2519489761569</v>
       </c>
       <c r="Z10" t="n">
-        <v>297.688</v>
+        <v>459212508.7763305</v>
       </c>
       <c r="AA10" t="n">
         <v>1.548064645108504e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>88.44835247916954</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 36.917x + -17040.174</t>
-        </is>
+      <c r="W11" t="n">
+        <v>36.91674246362543</v>
       </c>
       <c r="X11" t="n">
         <v>-17040.17357784339</v>
@@ -2972,7 +2890,7 @@
         <v>398.7846648972076</v>
       </c>
       <c r="Z11" t="n">
-        <v>295.909</v>
+        <v>6877.533398922906</v>
       </c>
       <c r="AA11" t="n">
         <v>5.954473502611596e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>88.47074562688456</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 37.458x + -17120.126</t>
-        </is>
+      <c r="W12" t="n">
+        <v>37.45758347364621</v>
       </c>
       <c r="X12" t="n">
         <v>-17120.1256064699</v>
@@ -3024,7 +2940,7 @@
         <v>412.9498010680853</v>
       </c>
       <c r="Z12" t="n">
-        <v>290.691</v>
+        <v>281094450.2318594</v>
       </c>
       <c r="AA12" t="n">
         <v>1.536621899455083e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>88.55210595611571</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 39.563x + -18003.740</t>
-        </is>
+      <c r="W13" t="n">
+        <v>39.56338027044617</v>
       </c>
       <c r="X13" t="n">
         <v>-18003.73978618631</v>
@@ -3076,7 +2990,7 @@
         <v>409.9714713688827</v>
       </c>
       <c r="Z13" t="n">
-        <v>282.789</v>
+        <v>7604.693690718798</v>
       </c>
       <c r="AA13" t="n">
         <v>7.586148895956666e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>88.53771951488943</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 39.174x + -17610.987</t>
-        </is>
+      <c r="W14" t="n">
+        <v>39.17397492422733</v>
       </c>
       <c r="X14" t="n">
         <v>-17610.9871134212</v>
@@ -3128,7 +3040,7 @@
         <v>388.8352672729376</v>
       </c>
       <c r="Z14" t="n">
-        <v>281.032</v>
+        <v>3324.365182566327</v>
       </c>
       <c r="AA14" t="n">
         <v>2.882408580975925e-06</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>88.52154558342484</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 38.745x + -17208.489</t>
-        </is>
+      <c r="W15" t="n">
+        <v>38.74523399413439</v>
       </c>
       <c r="X15" t="n">
         <v>-17208.48884818449</v>
@@ -3180,7 +3090,7 @@
         <v>402.6533208395448</v>
       </c>
       <c r="Z15" t="n">
-        <v>279.723</v>
+        <v>438452594.0219834</v>
       </c>
       <c r="AA15" t="n">
         <v>1.520169188990871e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>88.55344098214188</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 39.600x + -17441.158</t>
-        </is>
+      <c r="W16" t="n">
+        <v>39.59990876630123</v>
       </c>
       <c r="X16" t="n">
         <v>-17441.15762665463</v>
@@ -3232,7 +3140,7 @@
         <v>399.2866874166169</v>
       </c>
       <c r="Z16" t="n">
-        <v>274.514</v>
+        <v>217826799.4182777</v>
       </c>
       <c r="AA16" t="n">
         <v>1.514899248952161e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>88.55258391024402</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 39.576x + -17243.047</t>
-        </is>
+      <c r="W17" t="n">
+        <v>39.57645013509659</v>
       </c>
       <c r="X17" t="n">
         <v>-17243.04685903747</v>
@@ -3284,7 +3190,7 @@
         <v>387.4502664951513</v>
       </c>
       <c r="Z17" t="n">
-        <v>272.915</v>
+        <v>6098.363963348514</v>
       </c>
       <c r="AA17" t="n">
         <v>1.468984113764074e-06</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>88.6153973402204</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 41.373x + -17944.371</t>
-        </is>
+      <c r="W18" t="n">
+        <v>41.37260989341588</v>
       </c>
       <c r="X18" t="n">
         <v>-17944.37131442848</v>
@@ -3336,7 +3240,7 @@
         <v>385.231271717932</v>
       </c>
       <c r="Z18" t="n">
-        <v>268.489</v>
+        <v>5723.86169981358</v>
       </c>
       <c r="AA18" t="n">
         <v>1.079634136156786e-06</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>88.64204818525057</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 42.185x + -18135.465</t>
-        </is>
+      <c r="W19" t="n">
+        <v>42.18489223197854</v>
       </c>
       <c r="X19" t="n">
         <v>-18135.46509163999</v>
@@ -3388,7 +3290,7 @@
         <v>389.4181073657846</v>
       </c>
       <c r="Z19" t="n">
-        <v>262.977</v>
+        <v>126371123.298715</v>
       </c>
       <c r="AA19" t="n">
         <v>1.500804209514123e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>88.64241017521204</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 42.196x + -17958.525</t>
-        </is>
+      <c r="W20" t="n">
+        <v>42.19614469315525</v>
       </c>
       <c r="X20" t="n">
         <v>-17958.52544821114</v>
@@ -3440,7 +3340,7 @@
         <v>386.1429010916787</v>
       </c>
       <c r="Z20" t="n">
-        <v>262.783</v>
+        <v>472492036.3502814</v>
       </c>
       <c r="AA20" t="n">
         <v>1.498408751587341e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>88.65490644638726</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 42.588x + -17946.064</t>
-        </is>
+      <c r="W21" t="n">
+        <v>42.58830400864934</v>
       </c>
       <c r="X21" t="n">
         <v>-17946.06409079452</v>
@@ -3492,7 +3390,7 @@
         <v>382.9088097882289</v>
       </c>
       <c r="Z21" t="n">
-        <v>258.266</v>
+        <v>1040154274.107222</v>
       </c>
       <c r="AA21" t="n">
         <v>1.49375746343324e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>88.65396118956778</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 42.558x + -17744.220</t>
-        </is>
+      <c r="W22" t="n">
+        <v>42.55838534295848</v>
       </c>
       <c r="X22" t="n">
         <v>-17744.21970502623</v>
@@ -3544,7 +3440,7 @@
         <v>369.4545041984531</v>
       </c>
       <c r="Z22" t="n">
-        <v>258.143</v>
+        <v>3104.873026098478</v>
       </c>
       <c r="AA22" t="n">
         <v>4.502592419324417e-06</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>85.00061494428905</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.431x + -5808.303</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.43146540766853</v>
       </c>
       <c r="X2" t="n">
         <v>-5808.302779513925</v>
@@ -3742,7 +3636,7 @@
         <v>433.3319892882081</v>
       </c>
       <c r="Z2" t="n">
-        <v>963.5230000000001</v>
+        <v>702664727.5205411</v>
       </c>
       <c r="AA2" t="n">
         <v>2.255714864846592e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.2671391483667</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.327x + -6796.954</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.32730328211609</v>
       </c>
       <c r="X3" t="n">
         <v>-6796.953724562959</v>
@@ -3794,7 +3686,7 @@
         <v>400.0097735964395</v>
       </c>
       <c r="Z3" t="n">
-        <v>726.0170000000001</v>
+        <v>219781828.8455609</v>
       </c>
       <c r="AA3" t="n">
         <v>2.01060832395525e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.95152604535487</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.777x + -8069.113</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.77716672359222</v>
       </c>
       <c r="X4" t="n">
         <v>-8069.112609432689</v>
@@ -3846,7 +3736,7 @@
         <v>391.0170644581005</v>
       </c>
       <c r="Z4" t="n">
-        <v>598.255</v>
+        <v>853377689.1218193</v>
       </c>
       <c r="AA4" t="n">
         <v>1.869888689413641e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>87.35950003177355</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 21.683x + -9173.940</t>
-        </is>
+      <c r="W5" t="n">
+        <v>21.68347343646544</v>
       </c>
       <c r="X5" t="n">
         <v>-9173.939713338897</v>
@@ -3898,7 +3786,7 @@
         <v>391.3346221138735</v>
       </c>
       <c r="Z5" t="n">
-        <v>521.946</v>
+        <v>10048.54031388172</v>
       </c>
       <c r="AA5" t="n">
         <v>3.899640745121579e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>87.58101973264372</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.672x + -9838.252</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.67184792422899</v>
       </c>
       <c r="X6" t="n">
         <v>-9838.252048670225</v>
@@ -3950,7 +3836,7 @@
         <v>381.2705759157993</v>
       </c>
       <c r="Z6" t="n">
-        <v>474.7139999999999</v>
+        <v>103637606.8395346</v>
       </c>
       <c r="AA6" t="n">
         <v>1.728071967764566e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>87.80078017159987</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 26.040x + -10743.070</t>
-        </is>
+      <c r="W7" t="n">
+        <v>26.03997926821781</v>
       </c>
       <c r="X7" t="n">
         <v>-10743.07042555574</v>
@@ -4002,7 +3886,7 @@
         <v>366.6528996274645</v>
       </c>
       <c r="Z7" t="n">
-        <v>438.241</v>
+        <v>3081.494744177717</v>
       </c>
       <c r="AA7" t="n">
         <v>3.803486606084007e-06</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>87.90012402087255</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 27.273x + -11053.071</t>
-        </is>
+      <c r="W8" t="n">
+        <v>27.27309825683981</v>
       </c>
       <c r="X8" t="n">
         <v>-11053.07098521811</v>
@@ -4054,7 +3936,7 @@
         <v>363.6376069962431</v>
       </c>
       <c r="Z8" t="n">
-        <v>413.741</v>
+        <v>3043.814780033557</v>
       </c>
       <c r="AA8" t="n">
         <v>4.373673087624089e-06</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>87.97993307133902</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 28.352x + -11312.335</t>
-        </is>
+      <c r="W9" t="n">
+        <v>28.35155427519584</v>
       </c>
       <c r="X9" t="n">
         <v>-11312.33455660986</v>
@@ -4106,7 +3986,7 @@
         <v>369.9873394758301</v>
       </c>
       <c r="Z9" t="n">
-        <v>395.441</v>
+        <v>9104.316546793854</v>
       </c>
       <c r="AA9" t="n">
         <v>2.947415348728371e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>88.09190839973874</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 30.017x + -11874.333</t>
-        </is>
+      <c r="W10" t="n">
+        <v>30.01669130786157</v>
       </c>
       <c r="X10" t="n">
         <v>-11874.33313082993</v>
@@ -4158,7 +4036,7 @@
         <v>358.0187008381943</v>
       </c>
       <c r="Z10" t="n">
-        <v>378.204</v>
+        <v>2969.661359649142</v>
       </c>
       <c r="AA10" t="n">
         <v>6.772476471591856e-06</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>88.1037037525636</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 30.204x + -11736.963</t>
-        </is>
+      <c r="W11" t="n">
+        <v>30.20353899602047</v>
       </c>
       <c r="X11" t="n">
         <v>-11736.96339846924</v>
@@ -4210,7 +4086,7 @@
         <v>360.5142991971231</v>
       </c>
       <c r="Z11" t="n">
-        <v>368.8920000000001</v>
+        <v>5922.624533486918</v>
       </c>
       <c r="AA11" t="n">
         <v>1.456784505355195e-06</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>87.40998884539238</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.107x + -11058.032</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.10675719047645</v>
       </c>
       <c r="X2" t="n">
         <v>-11058.03164845512</v>
@@ -4408,7 +4282,7 @@
         <v>428.2258639481237</v>
       </c>
       <c r="Z2" t="n">
-        <v>500.3539999999999</v>
+        <v>18372.7964795937</v>
       </c>
       <c r="AA2" t="n">
         <v>1.708124901436907e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>87.82907848491389</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 26.380x + -12887.855</t>
-        </is>
+      <c r="W3" t="n">
+        <v>26.37974608869155</v>
       </c>
       <c r="X3" t="n">
         <v>-12887.85470734534</v>
@@ -4460,7 +4332,7 @@
         <v>436.2390868813392</v>
       </c>
       <c r="Z3" t="n">
-        <v>417.432</v>
+        <v>714857312.7649179</v>
       </c>
       <c r="AA3" t="n">
         <v>1.731094755667596e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>88.03561727392091</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 29.156x + -14096.625</t>
-        </is>
+      <c r="W4" t="n">
+        <v>29.15589075786477</v>
       </c>
       <c r="X4" t="n">
         <v>-14096.6253668565</v>
@@ -4512,7 +4382,7 @@
         <v>392.2418228770213</v>
       </c>
       <c r="Z4" t="n">
-        <v>377.727</v>
+        <v>14347.69680565677</v>
       </c>
       <c r="AA4" t="n">
         <v>1.853974146356537e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>88.12590844652591</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 30.562x + -14593.081</t>
-        </is>
+      <c r="W5" t="n">
+        <v>30.56165782648232</v>
       </c>
       <c r="X5" t="n">
         <v>-14593.08078356724</v>
@@ -4564,7 +4432,7 @@
         <v>428.1113247978005</v>
       </c>
       <c r="Z5" t="n">
-        <v>356.744</v>
+        <v>36588883.84992374</v>
       </c>
       <c r="AA5" t="n">
         <v>1.659933458259396e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>88.23523104501101</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 32.456x + -15346.342</t>
-        </is>
+      <c r="W6" t="n">
+        <v>32.45618034320421</v>
       </c>
       <c r="X6" t="n">
         <v>-15346.34184152871</v>
@@ -4616,7 +4482,7 @@
         <v>423.9579095881203</v>
       </c>
       <c r="Z6" t="n">
-        <v>335.6950000000001</v>
+        <v>27559905.67447949</v>
       </c>
       <c r="AA6" t="n">
         <v>1.63809084954019e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>88.26574326382118</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 33.028x + -15431.406</t>
-        </is>
+      <c r="W7" t="n">
+        <v>33.02756706761961</v>
       </c>
       <c r="X7" t="n">
         <v>-15431.40644278099</v>
@@ -4668,7 +4532,7 @@
         <v>419.9025313780976</v>
       </c>
       <c r="Z7" t="n">
-        <v>329.619</v>
+        <v>22813193.89138057</v>
       </c>
       <c r="AA7" t="n">
         <v>1.6255153529867e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>88.34692519291823</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 34.651x + -16062.703</t>
-        </is>
+      <c r="W8" t="n">
+        <v>34.65050730635799</v>
       </c>
       <c r="X8" t="n">
         <v>-16062.70326834718</v>
@@ -4720,7 +4582,7 @@
         <v>400.5301560943147</v>
       </c>
       <c r="Z8" t="n">
-        <v>316.491</v>
+        <v>6874.129375918969</v>
       </c>
       <c r="AA8" t="n">
         <v>7.464919215754058e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>88.36326173207384</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 34.997x + -16030.590</t>
-        </is>
+      <c r="W9" t="n">
+        <v>34.99655046162921</v>
       </c>
       <c r="X9" t="n">
         <v>-16030.59039215619</v>
@@ -4772,7 +4632,7 @@
         <v>412.4537415775835</v>
       </c>
       <c r="Z9" t="n">
-        <v>309.5690000000001</v>
+        <v>901410856.1699787</v>
       </c>
       <c r="AA9" t="n">
         <v>1.605921673503404e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>88.3117973395633</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 33.929x + -15278.701</t>
-        </is>
+      <c r="W10" t="n">
+        <v>33.92910051832172</v>
       </c>
       <c r="X10" t="n">
         <v>-15278.70072850319</v>
@@ -4824,7 +4682,7 @@
         <v>390.4344537883035</v>
       </c>
       <c r="Z10" t="n">
-        <v>306.232</v>
+        <v>3351.606138140507</v>
       </c>
       <c r="AA10" t="n">
         <v>3.70935487095687e-06</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>88.40333634760319</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 35.875x + -16101.650</t>
-        </is>
+      <c r="W11" t="n">
+        <v>35.87540007591397</v>
       </c>
       <c r="X11" t="n">
         <v>-16101.64984084333</v>
@@ -4876,7 +4732,7 @@
         <v>388.2930548595324</v>
       </c>
       <c r="Z11" t="n">
-        <v>297.874</v>
+        <v>3322.798733853723</v>
       </c>
       <c r="AA11" t="n">
         <v>2.929434986793159e-06</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>88.43765963813895</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 36.664x + -16319.707</t>
-        </is>
+      <c r="W12" t="n">
+        <v>36.66395593673482</v>
       </c>
       <c r="X12" t="n">
         <v>-16319.70746934681</v>
@@ -4928,7 +4782,7 @@
         <v>402.5482859389144</v>
       </c>
       <c r="Z12" t="n">
-        <v>292.782</v>
+        <v>219749421.0854972</v>
       </c>
       <c r="AA12" t="n">
         <v>1.582254998207532e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>88.48952368140284</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 37.923x + -16775.684</t>
-        </is>
+      <c r="W13" t="n">
+        <v>37.92347138357046</v>
       </c>
       <c r="X13" t="n">
         <v>-16775.68393520089</v>
@@ -4980,7 +4832,7 @@
         <v>399.4362182370824</v>
       </c>
       <c r="Z13" t="n">
-        <v>285.513</v>
+        <v>217884101.4122648</v>
       </c>
       <c r="AA13" t="n">
         <v>1.575533681273246e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>88.43843403923236</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 36.682x + -15978.477</t>
-        </is>
+      <c r="W14" t="n">
+        <v>36.68214708828121</v>
       </c>
       <c r="X14" t="n">
         <v>-15978.47705867695</v>
@@ -5032,7 +4882,7 @@
         <v>387.243572223659</v>
       </c>
       <c r="Z14" t="n">
-        <v>284.0509999999999</v>
+        <v>6087.355515252417</v>
       </c>
       <c r="AA14" t="n">
         <v>8.750494667108169e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>88.4520607038823</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 37.005x + -15986.150</t>
-        </is>
+      <c r="W15" t="n">
+        <v>37.00522296977935</v>
       </c>
       <c r="X15" t="n">
         <v>-15986.14978403234</v>
@@ -5084,7 +4932,7 @@
         <v>385.0033597714138</v>
       </c>
       <c r="Z15" t="n">
-        <v>283.2789999999999</v>
+        <v>5817.856239181757</v>
       </c>
       <c r="AA15" t="n">
         <v>8.269584952541309e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>88.50172950716394</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 38.233x + -16410.358</t>
-        </is>
+      <c r="W16" t="n">
+        <v>38.23256173726999</v>
       </c>
       <c r="X16" t="n">
         <v>-16410.35807759123</v>
@@ -5136,7 +4982,7 @@
         <v>390.1298533925001</v>
       </c>
       <c r="Z16" t="n">
-        <v>277.4930000000001</v>
+        <v>424906154.8144028</v>
       </c>
       <c r="AA16" t="n">
         <v>1.559476524407433e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>88.53229054254551</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 39.029x + -16628.039</t>
-        </is>
+      <c r="W17" t="n">
+        <v>39.02900960042764</v>
       </c>
       <c r="X17" t="n">
         <v>-16628.03869600047</v>
@@ -5188,7 +5032,7 @@
         <v>387.0645065547251</v>
       </c>
       <c r="Z17" t="n">
-        <v>273.061</v>
+        <v>527789415.7056388</v>
       </c>
       <c r="AA17" t="n">
         <v>1.554655332137557e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>88.56643024143784</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 39.959x + -16898.867</t>
-        </is>
+      <c r="W18" t="n">
+        <v>39.95886663715626</v>
       </c>
       <c r="X18" t="n">
         <v>-16898.86726804942</v>
@@ -5240,7 +5082,7 @@
         <v>384.0055298146076</v>
       </c>
       <c r="Z18" t="n">
-        <v>269.231</v>
+        <v>209938966.7393761</v>
       </c>
       <c r="AA18" t="n">
         <v>1.549660193808371e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>88.5755622336933</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 40.215x + -16834.996</t>
-        </is>
+      <c r="W19" t="n">
+        <v>40.21514734066275</v>
       </c>
       <c r="X19" t="n">
         <v>-16834.99572961427</v>
@@ -5292,7 +5132,7 @@
         <v>369.914785747864</v>
       </c>
       <c r="Z19" t="n">
-        <v>264.191</v>
+        <v>3117.64811257039</v>
       </c>
       <c r="AA19" t="n">
         <v>4.150379421065077e-06</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>88.60138341235772</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 40.958x + -17014.745</t>
-        </is>
+      <c r="W20" t="n">
+        <v>40.95790030923192</v>
       </c>
       <c r="X20" t="n">
         <v>-17014.7453676991</v>
@@ -5344,7 +5182,7 @@
         <v>367.7615643634669</v>
       </c>
       <c r="Z20" t="n">
-        <v>261.0170000000001</v>
+        <v>3092.98069709524</v>
       </c>
       <c r="AA20" t="n">
         <v>4.719243108953146e-06</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>88.52127905446127</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 38.738x + -15826.615</t>
-        </is>
+      <c r="W21" t="n">
+        <v>38.73824733928092</v>
       </c>
       <c r="X21" t="n">
         <v>-15826.61462063316</v>
@@ -5396,7 +5232,7 @@
         <v>365.6442421361662</v>
       </c>
       <c r="Z21" t="n">
-        <v>263.503</v>
+        <v>3065.105472682255</v>
       </c>
       <c r="AA21" t="n">
         <v>4.50856728064152e-06</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>88.67967253573478</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 43.387x + -17783.630</t>
-        </is>
+      <c r="W22" t="n">
+        <v>43.387446525239</v>
       </c>
       <c r="X22" t="n">
         <v>-17783.62994468227</v>
@@ -5448,7 +5282,7 @@
         <v>363.5401248831968</v>
       </c>
       <c r="Z22" t="n">
-        <v>252.7429999999999</v>
+        <v>3041.305824953865</v>
       </c>
       <c r="AA22" t="n">
         <v>6.226150934124446e-06</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.5734836262973</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.527x + -5264.725</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.52689366006718</v>
       </c>
       <c r="X2" t="n">
         <v>-5264.72458753714</v>
@@ -5646,7 +5478,7 @@
         <v>430.7569450103838</v>
       </c>
       <c r="Z2" t="n">
-        <v>1025.074</v>
+        <v>233728674.5132036</v>
       </c>
       <c r="AA2" t="n">
         <v>2.415788474583415e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>86.0032009398027</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.312x + -6368.239</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.31215659855639</v>
       </c>
       <c r="X3" t="n">
         <v>-6368.238706289995</v>
@@ -5698,7 +5528,7 @@
         <v>403.081108882269</v>
       </c>
       <c r="Z3" t="n">
-        <v>761.4280000000001</v>
+        <v>26865526.29293975</v>
       </c>
       <c r="AA3" t="n">
         <v>2.09475894374022e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.84456018329087</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.139x + -7917.759</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.13941789571864</v>
       </c>
       <c r="X4" t="n">
         <v>-7917.759453026883</v>
@@ -5750,7 +5578,7 @@
         <v>395.4896485780671</v>
       </c>
       <c r="Z4" t="n">
-        <v>613.395</v>
+        <v>216046876.3848027</v>
       </c>
       <c r="AA4" t="n">
         <v>1.927812295393479e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>87.2567462518365</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.870x + -8929.433</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.87010420282448</v>
       </c>
       <c r="X5" t="n">
         <v>-8929.433037612014</v>
@@ -5802,7 +5628,7 @@
         <v>396.1013078597147</v>
       </c>
       <c r="Z5" t="n">
-        <v>531.818</v>
+        <v>9899.950515235945</v>
       </c>
       <c r="AA5" t="n">
         <v>2.690383414507065e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>87.55762539885507</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.445x + -9911.451</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.44483569035805</v>
       </c>
       <c r="X6" t="n">
         <v>-9911.451398944964</v>
@@ -5854,7 +5678,7 @@
         <v>386.7729435961884</v>
       </c>
       <c r="Z6" t="n">
-        <v>473.7760000000001</v>
+        <v>947233320.0759394</v>
       </c>
       <c r="AA6" t="n">
         <v>1.763108932738833e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>87.71961191690619</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 25.112x + -10457.326</t>
-        </is>
+      <c r="W7" t="n">
+        <v>25.11218304492023</v>
       </c>
       <c r="X7" t="n">
         <v>-10457.32644871787</v>
@@ -5906,7 +5728,7 @@
         <v>382.5174943840916</v>
       </c>
       <c r="Z7" t="n">
-        <v>440.054</v>
+        <v>209577946.5805859</v>
       </c>
       <c r="AA7" t="n">
         <v>1.720373641015596e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>87.89886347394258</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 27.257x + -11245.434</t>
-        </is>
+      <c r="W8" t="n">
+        <v>27.25672148466398</v>
       </c>
       <c r="X8" t="n">
         <v>-11245.43405165313</v>
@@ -5958,7 +5778,7 @@
         <v>368.5942465753271</v>
       </c>
       <c r="Z8" t="n">
-        <v>407.7500000000001</v>
+        <v>3091.854779228136</v>
       </c>
       <c r="AA8" t="n">
         <v>4.253836186046018e-06</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>87.9207469114542</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 27.544x + -11125.368</t>
-        </is>
+      <c r="W9" t="n">
+        <v>27.54384529644544</v>
       </c>
       <c r="X9" t="n">
         <v>-11125.36763713648</v>
@@ -6010,7 +5828,7 @@
         <v>365.5545231100253</v>
       </c>
       <c r="Z9" t="n">
-        <v>392.219</v>
+        <v>3055.342962976627</v>
       </c>
       <c r="AA9" t="n">
         <v>4.187563762829413e-06</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>88.06866440834293</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 29.655x + -11897.308</t>
-        </is>
+      <c r="W10" t="n">
+        <v>29.65516584665808</v>
       </c>
       <c r="X10" t="n">
         <v>-11897.30801714758</v>
@@ -6062,7 +5878,7 @@
         <v>362.7931590103153</v>
       </c>
       <c r="Z10" t="n">
-        <v>370.448</v>
+        <v>3019.408839757034</v>
       </c>
       <c r="AA10" t="n">
         <v>5.576046445387152e-06</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>88.1680233395651</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 31.265x + -12434.172</t>
-        </is>
+      <c r="W11" t="n">
+        <v>31.26472852899871</v>
       </c>
       <c r="X11" t="n">
         <v>-12434.17226967321</v>
@@ -6114,7 +5928,7 @@
         <v>360.276349917771</v>
       </c>
       <c r="Z11" t="n">
-        <v>354.895</v>
+        <v>2987.28400260335</v>
       </c>
       <c r="AA11" t="n">
         <v>6.804308553158765e-06</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>86.61199063625102</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.892x + -8686.133</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.89162513017471</v>
       </c>
       <c r="X2" t="n">
         <v>-8686.133135867789</v>
@@ -6312,7 +6124,7 @@
         <v>452.35668962881</v>
       </c>
       <c r="Z2" t="n">
-        <v>638.0010000000001</v>
+        <v>247438428.0794368</v>
       </c>
       <c r="AA2" t="n">
         <v>2.035226843614756e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>87.61820935853832</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.042x + -11896.576</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.04189980595649</v>
       </c>
       <c r="X3" t="n">
         <v>-11896.57602459269</v>
@@ -6364,7 +6174,7 @@
         <v>441.236970068914</v>
       </c>
       <c r="Z3" t="n">
-        <v>452.424</v>
+        <v>125079789.1509634</v>
       </c>
       <c r="AA3" t="n">
         <v>1.809083805034442e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.90968108703846</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.398x + -13325.243</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.39790400897862</v>
       </c>
       <c r="X4" t="n">
         <v>-13325.24316002457</v>
@@ -6416,7 +6224,7 @@
         <v>436.0491753386115</v>
       </c>
       <c r="Z4" t="n">
-        <v>392.71</v>
+        <v>387987452.8781702</v>
       </c>
       <c r="AA4" t="n">
         <v>1.738985204231838e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>88.10998604028869</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 30.304x + -14629.671</t>
-        </is>
+      <c r="W5" t="n">
+        <v>30.30400689299799</v>
       </c>
       <c r="X5" t="n">
         <v>-14629.67131829655</v>
@@ -6468,7 +6274,7 @@
         <v>431.8986589084778</v>
       </c>
       <c r="Z5" t="n">
-        <v>359.264</v>
+        <v>31910299.39771348</v>
       </c>
       <c r="AA5" t="n">
         <v>1.700756659347028e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>88.09375167779901</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 30.046x + -14209.247</t>
-        </is>
+      <c r="W6" t="n">
+        <v>30.04573790057623</v>
       </c>
       <c r="X6" t="n">
         <v>-14209.24727128199</v>
@@ -6520,7 +6324,7 @@
         <v>428.0160598089331</v>
       </c>
       <c r="Z6" t="n">
-        <v>346.229</v>
+        <v>467629884.2441313</v>
       </c>
       <c r="AA6" t="n">
         <v>1.68002551100011e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>88.06670532332714</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 29.625x + -13763.947</t>
-        </is>
+      <c r="W7" t="n">
+        <v>29.62509229111804</v>
       </c>
       <c r="X7" t="n">
         <v>-13763.94748817758</v>
@@ -6572,7 +6374,7 @@
         <v>424.1785264245281</v>
       </c>
       <c r="Z7" t="n">
-        <v>334.555</v>
+        <v>125545190.288765</v>
       </c>
       <c r="AA7" t="n">
         <v>1.66198345384196e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>88.29492502434373</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 33.593x + -15682.860</t>
-        </is>
+      <c r="W8" t="n">
+        <v>33.59316479265556</v>
       </c>
       <c r="X8" t="n">
         <v>-15682.86009572078</v>
@@ -6624,7 +6424,7 @@
         <v>413.3510388804626</v>
       </c>
       <c r="Z8" t="n">
-        <v>318.557</v>
+        <v>15685.6440730381</v>
       </c>
       <c r="AA8" t="n">
         <v>1.77094109916298e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>88.31178839547577</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 33.929x + -15651.295</t>
-        </is>
+      <c r="W9" t="n">
+        <v>33.92892065902269</v>
       </c>
       <c r="X9" t="n">
         <v>-15651.29473670315</v>
@@ -6676,7 +6474,7 @@
         <v>416.7702582982151</v>
       </c>
       <c r="Z9" t="n">
-        <v>311.059</v>
+        <v>909589822.4757632</v>
       </c>
       <c r="AA9" t="n">
         <v>1.639971929839753e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>88.33982469682809</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 34.502x + -15764.342</t>
-        </is>
+      <c r="W10" t="n">
+        <v>34.50222617392208</v>
       </c>
       <c r="X10" t="n">
         <v>-15764.34154710978</v>
@@ -6728,7 +6524,7 @@
         <v>412.4253798300946</v>
       </c>
       <c r="Z10" t="n">
-        <v>304.948</v>
+        <v>7686.457886692357</v>
       </c>
       <c r="AA10" t="n">
         <v>7.662815190856792e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>88.37191918054657</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 35.183x + -15934.396</t>
-        </is>
+      <c r="W11" t="n">
+        <v>35.18274839827001</v>
       </c>
       <c r="X11" t="n">
         <v>-15934.39619045957</v>
@@ -6780,7 +6574,7 @@
         <v>392.1903711043747</v>
       </c>
       <c r="Z11" t="n">
-        <v>299.026</v>
+        <v>3362.49531787377</v>
       </c>
       <c r="AA11" t="n">
         <v>2.561791301832183e-06</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>88.41432945599126</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 36.124x + -16252.516</t>
-        </is>
+      <c r="W12" t="n">
+        <v>36.12424477514838</v>
       </c>
       <c r="X12" t="n">
         <v>-16252.51595046164</v>
@@ -6832,7 +6624,7 @@
         <v>406.5696251295084</v>
       </c>
       <c r="Z12" t="n">
-        <v>293.3960000000001</v>
+        <v>7562.536343381692</v>
       </c>
       <c r="AA12" t="n">
         <v>1.033533860087458e-06</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>88.41061103453872</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 36.040x + -16028.722</t>
-        </is>
+      <c r="W13" t="n">
+        <v>36.03968784011037</v>
       </c>
       <c r="X13" t="n">
         <v>-16028.72150931268</v>
@@ -6884,7 +6674,7 @@
         <v>403.8964437003165</v>
       </c>
       <c r="Z13" t="n">
-        <v>288.478</v>
+        <v>220028077.1227835</v>
       </c>
       <c r="AA13" t="n">
         <v>1.609640843267215e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>88.43327254477968</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 36.561x + -16130.076</t>
-        </is>
+      <c r="W14" t="n">
+        <v>36.56123987820738</v>
       </c>
       <c r="X14" t="n">
         <v>-16130.07587172526</v>
@@ -6936,7 +6724,7 @@
         <v>391.4139537918428</v>
       </c>
       <c r="Z14" t="n">
-        <v>283.853</v>
+        <v>6274.182893957601</v>
       </c>
       <c r="AA14" t="n">
         <v>8.838704087528576e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>88.30164900253993</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 33.726x + -14594.952</t>
-        </is>
+      <c r="W15" t="n">
+        <v>33.72624261967252</v>
       </c>
       <c r="X15" t="n">
         <v>-14594.95151907926</v>
@@ -6988,7 +6774,7 @@
         <v>397.9808730092059</v>
       </c>
       <c r="Z15" t="n">
-        <v>287.0189999999999</v>
+        <v>216786082.4330912</v>
       </c>
       <c r="AA15" t="n">
         <v>1.59908970498482e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>88.51491342104781</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 38.572x + -16806.840</t>
-        </is>
+      <c r="W16" t="n">
+        <v>38.57212688822576</v>
       </c>
       <c r="X16" t="n">
         <v>-16806.83966202478</v>
@@ -7040,7 +6824,7 @@
         <v>386.1011873896881</v>
       </c>
       <c r="Z16" t="n">
-        <v>273.194</v>
+        <v>6152.843472120463</v>
       </c>
       <c r="AA16" t="n">
         <v>1.338106733968226e-06</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>88.5165870612917</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 38.616x + -16665.981</t>
-        </is>
+      <c r="W17" t="n">
+        <v>38.61566484624898</v>
       </c>
       <c r="X17" t="n">
         <v>-16665.98065748631</v>
@@ -7092,7 +6874,7 @@
         <v>392.1617665167183</v>
       </c>
       <c r="Z17" t="n">
-        <v>271.648</v>
+        <v>108141571.6773528</v>
       </c>
       <c r="AA17" t="n">
         <v>1.588498537872321e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>88.56988028413464</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 40.055x + -17201.665</t>
-        </is>
+      <c r="W18" t="n">
+        <v>40.05530421361483</v>
       </c>
       <c r="X18" t="n">
         <v>-17201.66456970658</v>
@@ -7144,7 +6924,7 @@
         <v>389.2228096335514</v>
       </c>
       <c r="Z18" t="n">
-        <v>265.635</v>
+        <v>423823252.9383525</v>
       </c>
       <c r="AA18" t="n">
         <v>1.583740140481801e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>88.54107988918297</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 39.264x + -16648.479</t>
-        </is>
+      <c r="W19" t="n">
+        <v>39.26424465960307</v>
       </c>
       <c r="X19" t="n">
         <v>-16648.47850029673</v>
@@ -7196,7 +6974,7 @@
         <v>386.3321753760547</v>
       </c>
       <c r="Z19" t="n">
-        <v>264.2040000000001</v>
+        <v>421642121.2288289</v>
       </c>
       <c r="AA19" t="n">
         <v>1.579302543440558e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>88.7222515776574</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 44.834x + -19179.413</t>
-        </is>
+      <c r="W20" t="n">
+        <v>44.83377155936709</v>
       </c>
       <c r="X20" t="n">
         <v>-19179.41293714672</v>
@@ -7248,7 +7024,7 @@
         <v>372.524350903414</v>
       </c>
       <c r="Z20" t="n">
-        <v>253.407</v>
+        <v>3137.765914510968</v>
       </c>
       <c r="AA20" t="n">
         <v>3.80558198294671e-06</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>88.46246401890861</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 37.256x + -15400.264</t>
-        </is>
+      <c r="W21" t="n">
+        <v>37.25573011912314</v>
       </c>
       <c r="X21" t="n">
         <v>-15400.26373223274</v>
@@ -7300,7 +7074,7 @@
         <v>370.3841944268697</v>
       </c>
       <c r="Z21" t="n">
-        <v>262.4709999999999</v>
+        <v>3110.482970582952</v>
       </c>
       <c r="AA21" t="n">
         <v>5.060048837761327e-06</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>88.69849085206897</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 44.015x + -18393.186</t>
-        </is>
+      <c r="W22" t="n">
+        <v>44.01499935883474</v>
       </c>
       <c r="X22" t="n">
         <v>-18393.18569421029</v>
@@ -7352,7 +7124,7 @@
         <v>368.3066786447217</v>
       </c>
       <c r="Z22" t="n">
-        <v>249.913</v>
+        <v>3088.221134289601</v>
       </c>
       <c r="AA22" t="n">
         <v>3.946012337124171e-06</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.49918395916609</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.384x + -5250.953</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.3838469103033</v>
       </c>
       <c r="X2" t="n">
         <v>-5250.953486006958</v>
@@ -7550,7 +7320,7 @@
         <v>428.2332462765251</v>
       </c>
       <c r="Z2" t="n">
-        <v>1020.75</v>
+        <v>176854762.310507</v>
       </c>
       <c r="AA2" t="n">
         <v>2.503146688684804e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>86.10331232512375</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.681x + -6428.418</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.68103658445144</v>
       </c>
       <c r="X3" t="n">
         <v>-6428.417618295207</v>
@@ -7602,7 +7370,7 @@
         <v>378.5659046197014</v>
       </c>
       <c r="Z3" t="n">
-        <v>727.758</v>
+        <v>3251.976403630118</v>
       </c>
       <c r="AA3" t="n">
         <v>2.638314156025119e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.95039915777241</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.770x + -7975.321</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.770215076152</v>
       </c>
       <c r="X4" t="n">
         <v>-7975.320502822983</v>
@@ -7654,7 +7420,7 @@
         <v>387.4135014371778</v>
       </c>
       <c r="Z4" t="n">
-        <v>574.908</v>
+        <v>5878.512002361233</v>
       </c>
       <c r="AA4" t="n">
         <v>6.027754898540164e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>87.43536910256242</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.326x + -9362.085</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.32582828733286</v>
       </c>
       <c r="X5" t="n">
         <v>-9362.084669412065</v>
@@ -7706,7 +7470,7 @@
         <v>383.8299045016033</v>
       </c>
       <c r="Z5" t="n">
-        <v>486.778</v>
+        <v>419254175.9051671</v>
       </c>
       <c r="AA5" t="n">
         <v>1.82381194019089e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.7556883062751</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 25.516x + -10601.220</t>
-        </is>
+      <c r="W6" t="n">
+        <v>25.51627431049239</v>
       </c>
       <c r="X6" t="n">
         <v>-10601.21969535638</v>
@@ -7758,7 +7520,7 @@
         <v>368.8728782930354</v>
       </c>
       <c r="Z6" t="n">
-        <v>428.646</v>
+        <v>3105.746169602751</v>
       </c>
       <c r="AA6" t="n">
         <v>3.379624438924234e-06</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.99494859295974</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 28.564x + -11797.636</t>
-        </is>
+      <c r="W7" t="n">
+        <v>28.56405010142371</v>
       </c>
       <c r="X7" t="n">
         <v>-11797.63606719903</v>
@@ -7810,7 +7570,7 @@
         <v>366.1889323686365</v>
       </c>
       <c r="Z7" t="n">
-        <v>388.851</v>
+        <v>3069.469555446921</v>
       </c>
       <c r="AA7" t="n">
         <v>4.354806899301846e-06</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>88.06013333914801</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 29.525x + -11910.999</t>
-        </is>
+      <c r="W8" t="n">
+        <v>29.52465046603283</v>
       </c>
       <c r="X8" t="n">
         <v>-11910.99916511957</v>
@@ -7862,7 +7620,7 @@
         <v>363.3927720476658</v>
       </c>
       <c r="Z8" t="n">
-        <v>363.164</v>
+        <v>3029.728417792315</v>
       </c>
       <c r="AA8" t="n">
         <v>5.595083832219959e-06</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>88.16340468963088</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 31.186x + -12423.381</t>
-        </is>
+      <c r="W9" t="n">
+        <v>31.1860506491509</v>
       </c>
       <c r="X9" t="n">
         <v>-12423.38149510681</v>
@@ -7914,7 +7670,7 @@
         <v>365.6700232995036</v>
       </c>
       <c r="Z9" t="n">
-        <v>344.14</v>
+        <v>4894.766165784499</v>
       </c>
       <c r="AA9" t="n">
         <v>1.110762989935804e-06</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>88.24712784817928</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 32.677x + -12879.701</t>
-        </is>
+      <c r="W10" t="n">
+        <v>32.67660046061189</v>
       </c>
       <c r="X10" t="n">
         <v>-12879.70078544074</v>
@@ -7966,7 +7720,7 @@
         <v>362.3122293056554</v>
       </c>
       <c r="Z10" t="n">
-        <v>329.702</v>
+        <v>393741041.4451929</v>
       </c>
       <c r="AA10" t="n">
         <v>1.648926069873349e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>88.32050250286623</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 34.105x + -13285.898</t>
-        </is>
+      <c r="W11" t="n">
+        <v>34.10506323137476</v>
       </c>
       <c r="X11" t="n">
         <v>-13285.89821834282</v>
@@ -8018,7 +7770,7 @@
         <v>358.4391175287689</v>
       </c>
       <c r="Z11" t="n">
-        <v>315.8560000000001</v>
+        <v>33422879.31864697</v>
       </c>
       <c r="AA11" t="n">
         <v>1.632150073337587e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.65441705284117</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 17.106x + -8593.638</t>
-        </is>
+      <c r="W2" t="n">
+        <v>17.10633029014837</v>
       </c>
       <c r="X2" t="n">
         <v>-8593.638004325428</v>
@@ -8216,7 +7966,7 @@
         <v>445.7947041603194</v>
       </c>
       <c r="Z2" t="n">
-        <v>608.9560000000001</v>
+        <v>244050227.6888387</v>
       </c>
       <c r="AA2" t="n">
         <v>2.071748836608976e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>87.62321067557258</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.093x + -11840.649</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.09254781736517</v>
       </c>
       <c r="X3" t="n">
         <v>-11840.64945193359</v>
@@ -8268,7 +8016,7 @@
         <v>436.9700326005391</v>
       </c>
       <c r="Z3" t="n">
-        <v>444.6999999999999</v>
+        <v>341020120.6648586</v>
       </c>
       <c r="AA3" t="n">
         <v>1.865560298812348e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.88393660932623</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.064x + -13041.572</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.06427749399874</v>
       </c>
       <c r="X4" t="n">
         <v>-13041.57198786413</v>
@@ -8320,7 +8066,7 @@
         <v>432.5868409983169</v>
       </c>
       <c r="Z4" t="n">
-        <v>383.852</v>
+        <v>27750175.75858851</v>
       </c>
       <c r="AA4" t="n">
         <v>1.787540813147449e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>88.04612989654245</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.313x + -13975.832</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.312884077808</v>
       </c>
       <c r="X5" t="n">
         <v>-13975.83191713709</v>
@@ -8372,7 +8116,7 @@
         <v>428.6187214448487</v>
       </c>
       <c r="Z5" t="n">
-        <v>351.7339999999999</v>
+        <v>234348620.6758281</v>
       </c>
       <c r="AA5" t="n">
         <v>1.752994282087224e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>88.05673054153104</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 29.473x + -13808.292</t>
-        </is>
+      <c r="W6" t="n">
+        <v>29.47291122073068</v>
       </c>
       <c r="X6" t="n">
         <v>-13808.29235260107</v>
@@ -8424,7 +8166,7 @@
         <v>424.5595634917665</v>
       </c>
       <c r="Z6" t="n">
-        <v>337.012</v>
+        <v>128756446.3089024</v>
       </c>
       <c r="AA6" t="n">
         <v>1.729583716904129e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>88.27044688663949</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 33.117x + -15532.443</t>
-        </is>
+      <c r="W7" t="n">
+        <v>33.11744231579915</v>
       </c>
       <c r="X7" t="n">
         <v>-15532.44254583502</v>
@@ -8476,7 +8216,7 @@
         <v>420.4315652067328</v>
       </c>
       <c r="Z7" t="n">
-        <v>316.075</v>
+        <v>118615617.0548192</v>
       </c>
       <c r="AA7" t="n">
         <v>1.712206307714624e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>88.24290423031162</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 32.598x + -15019.597</t>
-        </is>
+      <c r="W8" t="n">
+        <v>32.59800501140025</v>
       </c>
       <c r="X8" t="n">
         <v>-15019.59746420028</v>
@@ -8528,7 +8266,7 @@
         <v>416.3770116231983</v>
       </c>
       <c r="Z8" t="n">
-        <v>310.097</v>
+        <v>454588972.0921235</v>
       </c>
       <c r="AA8" t="n">
         <v>1.699571050475663e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>88.29186155096993</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 33.533x + -15295.800</t>
-        </is>
+      <c r="W9" t="n">
+        <v>33.53288126858914</v>
       </c>
       <c r="X9" t="n">
         <v>-15295.7998640503</v>
@@ -8580,7 +8316,7 @@
         <v>393.7922482824788</v>
       </c>
       <c r="Z9" t="n">
-        <v>301.028</v>
+        <v>3380.332953377035</v>
       </c>
       <c r="AA9" t="n">
         <v>3.299760744514844e-06</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>88.33010779802876</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 34.301x + -15496.521</t>
-        </is>
+      <c r="W10" t="n">
+        <v>34.30134918815782</v>
       </c>
       <c r="X10" t="n">
         <v>-15496.52076257386</v>
@@ -8632,7 +8366,7 @@
         <v>393.3558551742232</v>
       </c>
       <c r="Z10" t="n">
-        <v>293.661</v>
+        <v>3350.947418589739</v>
       </c>
       <c r="AA10" t="n">
         <v>2.133772204584533e-06</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>88.40474625744268</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 35.907x + -16136.333</t>
-        </is>
+      <c r="W11" t="n">
+        <v>35.90712372131114</v>
       </c>
       <c r="X11" t="n">
         <v>-16136.33295058607</v>
@@ -8684,7 +8416,7 @@
         <v>405.6987242050351</v>
       </c>
       <c r="Z11" t="n">
-        <v>285.8539999999999</v>
+        <v>223496760.40505</v>
       </c>
       <c r="AA11" t="n">
         <v>1.671143237273648e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>88.2793501247301</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 33.289x + -14647.019</t>
-        </is>
+      <c r="W12" t="n">
+        <v>33.28890730102925</v>
       </c>
       <c r="X12" t="n">
         <v>-14647.01905829087</v>
@@ -8736,7 +8466,7 @@
         <v>406.6718598625063</v>
       </c>
       <c r="Z12" t="n">
-        <v>287.692</v>
+        <v>10426.34676195086</v>
       </c>
       <c r="AA12" t="n">
         <v>2.626741760332304e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>88.40617885970838</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 35.939x + -15797.921</t>
-        </is>
+      <c r="W13" t="n">
+        <v>35.93941543066358</v>
       </c>
       <c r="X13" t="n">
         <v>-15797.92056487545</v>
@@ -8788,7 +8516,7 @@
         <v>399.4162991703378</v>
       </c>
       <c r="Z13" t="n">
-        <v>278.355</v>
+        <v>123994034.9297559</v>
       </c>
       <c r="AA13" t="n">
         <v>1.657267705748101e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>88.35504712138336</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 34.822x + -15094.628</t>
-        </is>
+      <c r="W14" t="n">
+        <v>34.8216883773384</v>
       </c>
       <c r="X14" t="n">
         <v>-15094.6284375091</v>
@@ -8840,7 +8566,7 @@
         <v>400.2324335157696</v>
       </c>
       <c r="Z14" t="n">
-        <v>278.026</v>
+        <v>10470.88867216568</v>
       </c>
       <c r="AA14" t="n">
         <v>3.269943740968406e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>88.47903605119467</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 37.662x + -16328.454</t>
-        </is>
+      <c r="W15" t="n">
+        <v>37.66185287272612</v>
       </c>
       <c r="X15" t="n">
         <v>-16328.45434062075</v>
@@ -8892,7 +8616,7 @@
         <v>393.4107771894506</v>
       </c>
       <c r="Z15" t="n">
-        <v>269.083</v>
+        <v>107723215.7499345</v>
       </c>
       <c r="AA15" t="n">
         <v>1.645584611816782e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>88.49065533624402</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 37.952x + -16298.552</t>
-        </is>
+      <c r="W16" t="n">
+        <v>37.95191827476459</v>
       </c>
       <c r="X16" t="n">
         <v>-16298.55191694088</v>
@@ -8944,7 +8666,7 @@
         <v>390.4918075518529</v>
       </c>
       <c r="Z16" t="n">
-        <v>264.576</v>
+        <v>217876328.0257168</v>
       </c>
       <c r="AA16" t="n">
         <v>1.640303864404856e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>88.44194140277973</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 36.765x + -15585.799</t>
-        </is>
+      <c r="W17" t="n">
+        <v>36.76476354958777</v>
       </c>
       <c r="X17" t="n">
         <v>-15585.79937136267</v>
@@ -8996,7 +8716,7 @@
         <v>375.5062330050512</v>
       </c>
       <c r="Z17" t="n">
-        <v>266.073</v>
+        <v>3172.946271935872</v>
       </c>
       <c r="AA17" t="n">
         <v>4.241315651755685e-06</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>88.53242985999732</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 39.033x + -16502.586</t>
-        </is>
+      <c r="W18" t="n">
+        <v>39.03271627264386</v>
       </c>
       <c r="X18" t="n">
         <v>-16502.58576815755</v>
@@ -9048,7 +8766,7 @@
         <v>373.3998191523149</v>
       </c>
       <c r="Z18" t="n">
-        <v>258.6390000000001</v>
+        <v>3149.076553888359</v>
       </c>
       <c r="AA18" t="n">
         <v>3.07087961023799e-06</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>88.55674945260151</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 39.691x + -16651.589</t>
-        </is>
+      <c r="W19" t="n">
+        <v>39.69072512253167</v>
       </c>
       <c r="X19" t="n">
         <v>-16651.58944383805</v>
@@ -9100,7 +8816,7 @@
         <v>371.3188852355273</v>
       </c>
       <c r="Z19" t="n">
-        <v>255.449</v>
+        <v>3123.663719967379</v>
       </c>
       <c r="AA19" t="n">
         <v>4.18720346893616e-06</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>88.58473711769085</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 40.476x + -16851.461</t>
-        </is>
+      <c r="W20" t="n">
+        <v>40.4759617126121</v>
       </c>
       <c r="X20" t="n">
         <v>-16851.46139508637</v>
@@ -9152,7 +8866,7 @@
         <v>369.2982471975364</v>
       </c>
       <c r="Z20" t="n">
-        <v>251.033</v>
+        <v>3099.302276693664</v>
       </c>
       <c r="AA20" t="n">
         <v>4.942202739543038e-06</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>88.60130208001813</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 40.956x + -16913.710</t>
-        </is>
+      <c r="W21" t="n">
+        <v>40.95551771787612</v>
       </c>
       <c r="X21" t="n">
         <v>-16913.70999556211</v>
@@ -9204,7 +8916,7 @@
         <v>367.1860219749532</v>
       </c>
       <c r="Z21" t="n">
-        <v>250.662</v>
+        <v>3075.127425408357</v>
       </c>
       <c r="AA21" t="n">
         <v>5.907859228920702e-06</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>88.60453112993389</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 41.050x + -16789.938</t>
-        </is>
+      <c r="W22" t="n">
+        <v>41.05032449489355</v>
       </c>
       <c r="X22" t="n">
         <v>-16789.93781409243</v>
@@ -9256,7 +8966,7 @@
         <v>365.2080411536498</v>
       </c>
       <c r="Z22" t="n">
-        <v>247.7919999999999</v>
+        <v>3048.036387501885</v>
       </c>
       <c r="AA22" t="n">
         <v>5.649870250503162e-06</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>85.07196918455699</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.598x + -5304.874</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.5978216620827</v>
       </c>
       <c r="X2" t="n">
         <v>-5304.874138784559</v>
@@ -9454,7 +9162,7 @@
         <v>401.1043403775762</v>
       </c>
       <c r="Z2" t="n">
-        <v>894.4929999999999</v>
+        <v>108907247.952289</v>
       </c>
       <c r="AA2" t="n">
         <v>2.373384584861524e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>87.01464537540696</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.175x + -8006.075</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.17491468162689</v>
       </c>
       <c r="X3" t="n">
         <v>-8006.074614647086</v>
@@ -9506,7 +9212,7 @@
         <v>381.3629202390516</v>
       </c>
       <c r="Z3" t="n">
-        <v>550.8199999999999</v>
+        <v>9439.87884057199</v>
       </c>
       <c r="AA3" t="n">
         <v>2.658933688911196e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.67743692957593</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.656x + -10066.136</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.65568924399423</v>
       </c>
       <c r="X4" t="n">
         <v>-10066.13555488129</v>
@@ -9558,7 +9262,7 @@
         <v>364.5311168886443</v>
       </c>
       <c r="Z4" t="n">
-        <v>426.4520000000001</v>
+        <v>3058.22627779957</v>
       </c>
       <c r="AA4" t="n">
         <v>3.609211404066198e-06</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>88.08235552617823</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.867x + -12164.623</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.86705027022585</v>
       </c>
       <c r="X5" t="n">
         <v>-12164.62309624022</v>
@@ -9610,7 +9312,7 @@
         <v>361.9718251685001</v>
       </c>
       <c r="Z5" t="n">
-        <v>361.5520000000001</v>
+        <v>3015.894685735782</v>
       </c>
       <c r="AA5" t="n">
         <v>5.520239378837497e-06</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>88.1532222126736</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 31.014x + -12301.637</t>
-        </is>
+      <c r="W6" t="n">
+        <v>31.01398367139811</v>
       </c>
       <c r="X6" t="n">
         <v>-12301.63704658648</v>
@@ -9662,7 +9362,7 @@
         <v>364.3538657862861</v>
       </c>
       <c r="Z6" t="n">
-        <v>333.287</v>
+        <v>105464050.9517256</v>
       </c>
       <c r="AA6" t="n">
         <v>1.705058324283315e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>88.22827363210166</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 32.329x + -12591.555</t>
-        </is>
+      <c r="W7" t="n">
+        <v>32.32864698610952</v>
       </c>
       <c r="X7" t="n">
         <v>-12591.55523584506</v>
@@ -9714,7 +9412,7 @@
         <v>359.2365938796329</v>
       </c>
       <c r="Z7" t="n">
-        <v>313.081</v>
+        <v>30867463.59770979</v>
       </c>
       <c r="AA7" t="n">
         <v>1.680696565424466e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>88.32155903305907</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 34.127x + -13108.619</t>
-        </is>
+      <c r="W8" t="n">
+        <v>34.12654368386422</v>
       </c>
       <c r="X8" t="n">
         <v>-13108.61851085418</v>
@@ -9766,7 +9462,7 @@
         <v>354.16747354124</v>
       </c>
       <c r="Z8" t="n">
-        <v>297.344</v>
+        <v>289119563.5671461</v>
       </c>
       <c r="AA8" t="n">
         <v>1.667270538946964e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>88.39740103072994</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.742x + -13545.505</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.74246454158065</v>
       </c>
       <c r="X9" t="n">
         <v>-13545.50494930807</v>
@@ -9818,7 +9512,7 @@
         <v>349.3739113736689</v>
       </c>
       <c r="Z9" t="n">
-        <v>284.604</v>
+        <v>474103179.0063043</v>
       </c>
       <c r="AA9" t="n">
         <v>1.655311809901298e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>88.4311182282699</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 36.511x + -13638.588</t>
-        </is>
+      <c r="W10" t="n">
+        <v>36.51101060817594</v>
       </c>
       <c r="X10" t="n">
         <v>-13638.58811045589</v>
@@ -9870,7 +9562,7 @@
         <v>345.0101471185797</v>
       </c>
       <c r="Z10" t="n">
-        <v>277.068</v>
+        <v>187649832.029548</v>
       </c>
       <c r="AA10" t="n">
         <v>1.646770464454235e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>88.41999804012282</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 36.254x + -13312.564</t>
-        </is>
+      <c r="W11" t="n">
+        <v>36.25391406392725</v>
       </c>
       <c r="X11" t="n">
         <v>-13312.56357781967</v>
@@ -9922,7 +9612,7 @@
         <v>333.1721359161679</v>
       </c>
       <c r="Z11" t="n">
-        <v>272.275</v>
+        <v>5602.47840505856</v>
       </c>
       <c r="AA11" t="n">
         <v>1.840085250934307e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-485.686</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-439.384</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-411.664</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-386.404</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-376.839</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-365.185</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-353.241</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-341.3070000000001</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-336.863</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-328.858</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-963.5230000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-726.0170000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-598.255</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-521.946</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-474.7139999999999</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-438.241</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-413.741</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-395.441</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-378.204</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-368.8920000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1025.074</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-761.4280000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-613.395</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-531.818</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-473.7760000000001</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-440.054</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-407.7500000000001</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-392.219</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-370.448</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-354.895</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1020.75</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-727.758</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-574.908</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-486.778</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-428.646</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-388.851</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-363.164</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-344.14</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-329.702</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-315.8560000000001</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-894.4929999999999</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-550.8199999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-426.4520000000001</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-361.5520000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-333.287</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-313.081</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-297.344</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-284.604</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-277.068</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-272.275</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-485.686</v>
+        <v>126.462</v>
       </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-439.384</v>
+        <v>120.127</v>
       </c>
       <c r="D3" t="n">
         <v>1.30011e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-411.664</v>
+        <v>113.013</v>
       </c>
       <c r="D4" t="n">
         <v>1.29335e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-386.404</v>
+        <v>111.574</v>
       </c>
       <c r="D5" t="n">
         <v>1.28864e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-376.839</v>
+        <v>104.864</v>
       </c>
       <c r="D6" t="n">
         <v>1.28581e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-365.185</v>
+        <v>100.478</v>
       </c>
       <c r="D7" t="n">
         <v>1.28356e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-353.241</v>
+        <v>99.42899999999997</v>
       </c>
       <c r="D8" t="n">
         <v>1.28196e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-341.3070000000001</v>
+        <v>97.62399999999997</v>
       </c>
       <c r="D9" t="n">
         <v>1.27971e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-336.863</v>
+        <v>90.94600000000003</v>
       </c>
       <c r="D10" t="n">
         <v>1.27854e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-328.858</v>
+        <v>89.99900000000002</v>
       </c>
       <c r="D11" t="n">
         <v>1.2773e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-381.455</v>
+        <v>115.611</v>
       </c>
       <c r="D2" t="n">
         <v>1.4007e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-329.179</v>
+        <v>97.70499999999998</v>
       </c>
       <c r="D3" t="n">
         <v>1.39345e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-304.09</v>
+        <v>97.13600000000002</v>
       </c>
       <c r="D4" t="n">
         <v>1.38986e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-294.957</v>
+        <v>90.66300000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.38786e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-281.806</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.38667e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-274.538</v>
+        <v>88.84399999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.38581e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-269.574</v>
+        <v>88.85899999999998</v>
       </c>
       <c r="D8" t="n">
         <v>1.38516e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-267.9109999999999</v>
+        <v>85.46800000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.38474e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-261.2500000000001</v>
+        <v>86.26900000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.38429e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-258.436</v>
+        <v>83.37299999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.38354e-07</v>
@@ -1685,10 +1685,10 @@
         <v>88.4780430744419</v>
       </c>
       <c r="W11" t="n">
-        <v>37.63726944066111</v>
+        <v>37.63726944066112</v>
       </c>
       <c r="X11" t="n">
-        <v>-16898.73726182366</v>
+        <v>-16898.73726182367</v>
       </c>
       <c r="Y11" t="n">
         <v>409.0010012465469</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-257.948</v>
+        <v>80.09399999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.38316e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-254.417</v>
+        <v>77.12099999999998</v>
       </c>
       <c r="D13" t="n">
         <v>1.38329e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-248.977</v>
+        <v>79.024</v>
       </c>
       <c r="D14" t="n">
         <v>1.38237e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-246.5700000000001</v>
+        <v>76.39699999999999</v>
       </c>
       <c r="D15" t="n">
         <v>1.38212e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-243.208</v>
+        <v>76.05099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.38169e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-241.561</v>
+        <v>74.41500000000002</v>
       </c>
       <c r="D17" t="n">
         <v>1.38151e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-238.047</v>
+        <v>75.26500000000004</v>
       </c>
       <c r="D18" t="n">
         <v>1.38102e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-238.684</v>
+        <v>72.649</v>
       </c>
       <c r="D19" t="n">
         <v>1.38053e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-237.926</v>
+        <v>70.15699999999998</v>
       </c>
       <c r="D20" t="n">
         <v>1.38014e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-233.692</v>
+        <v>69.86399999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.38002e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-233.659</v>
+        <v>67.46100000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.37988e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-492.792</v>
+        <v>128.455</v>
       </c>
       <c r="D2" t="n">
         <v>1.31411e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-390.406</v>
+        <v>111.482</v>
       </c>
       <c r="D3" t="n">
         <v>1.29962e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-357.253</v>
+        <v>105.075</v>
       </c>
       <c r="D4" t="n">
         <v>1.29233e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-338.177</v>
+        <v>102.436</v>
       </c>
       <c r="D5" t="n">
         <v>1.28793e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-326.828</v>
+        <v>97.84100000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.28431e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-317.366</v>
+        <v>96.60300000000001</v>
       </c>
       <c r="D7" t="n">
         <v>1.28143e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-310.542</v>
+        <v>95.69100000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.27985e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-303.485</v>
+        <v>92.08800000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.27862e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-297.688</v>
+        <v>90.72899999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.27761e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-295.909</v>
+        <v>89.14699999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.2767e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-290.691</v>
+        <v>86.73400000000004</v>
       </c>
       <c r="D12" t="n">
         <v>1.27615e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-282.789</v>
+        <v>87.87199999999996</v>
       </c>
       <c r="D13" t="n">
         <v>1.27526e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-281.032</v>
+        <v>85.00900000000001</v>
       </c>
       <c r="D14" t="n">
         <v>1.27443e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-279.723</v>
+        <v>81.565</v>
       </c>
       <c r="D15" t="n">
         <v>1.27374e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-274.514</v>
+        <v>80.928</v>
       </c>
       <c r="D16" t="n">
         <v>1.27307e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-272.915</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>1.27252e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-268.489</v>
+        <v>79.79400000000004</v>
       </c>
       <c r="D18" t="n">
         <v>1.27191e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-262.977</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>1.27144e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-262.783</v>
+        <v>76.40500000000003</v>
       </c>
       <c r="D20" t="n">
         <v>1.27113e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-258.266</v>
+        <v>74.73899999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.2708e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-258.143</v>
+        <v>72.61700000000002</v>
       </c>
       <c r="D22" t="n">
         <v>1.27013e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-963.5230000000001</v>
+        <v>130.234</v>
       </c>
       <c r="D2" t="n">
         <v>1.37996e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-726.0170000000001</v>
+        <v>85.577</v>
       </c>
       <c r="D3" t="n">
         <v>1.39236e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-598.255</v>
+        <v>76.524</v>
       </c>
       <c r="D4" t="n">
         <v>1.37508e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-521.946</v>
+        <v>73.04199999999997</v>
       </c>
       <c r="D5" t="n">
         <v>1.35982e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-474.7139999999999</v>
+        <v>67.81400000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.34835e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-438.241</v>
+        <v>68.13100000000003</v>
       </c>
       <c r="D7" t="n">
         <v>1.33972e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-413.741</v>
+        <v>63.90199999999999</v>
       </c>
       <c r="D8" t="n">
         <v>1.33379e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-395.441</v>
+        <v>60.459</v>
       </c>
       <c r="D9" t="n">
         <v>1.32873e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-378.204</v>
+        <v>61.10899999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.3251e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-368.8920000000001</v>
+        <v>56.19099999999997</v>
       </c>
       <c r="D11" t="n">
         <v>1.3222e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-500.3539999999999</v>
+        <v>113.145</v>
       </c>
       <c r="D2" t="n">
         <v>1.35036e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-417.432</v>
+        <v>104.525</v>
       </c>
       <c r="D3" t="n">
         <v>1.33679e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-377.727</v>
+        <v>101.551</v>
       </c>
       <c r="D4" t="n">
         <v>1.32952e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-356.744</v>
+        <v>98.47399999999999</v>
       </c>
       <c r="D5" t="n">
         <v>1.32425e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-335.6950000000001</v>
+        <v>96.40899999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.32104e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-329.619</v>
+        <v>93.51799999999997</v>
       </c>
       <c r="D7" t="n">
         <v>1.31841e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-316.491</v>
+        <v>92.80500000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.31663e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-309.5690000000001</v>
+        <v>90.05799999999999</v>
       </c>
       <c r="D9" t="n">
         <v>1.3149e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-306.232</v>
+        <v>83.95999999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.31353e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-297.874</v>
+        <v>85.44400000000002</v>
       </c>
       <c r="D11" t="n">
         <v>1.31225e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-292.782</v>
+        <v>83.76499999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.31102e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-285.513</v>
+        <v>84.488</v>
       </c>
       <c r="D13" t="n">
         <v>1.30994e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-284.0509999999999</v>
+        <v>79.09700000000004</v>
       </c>
       <c r="D14" t="n">
         <v>1.30901e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-283.2789999999999</v>
+        <v>77.55600000000004</v>
       </c>
       <c r="D15" t="n">
         <v>1.30828e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-277.4930000000001</v>
+        <v>77.27599999999995</v>
       </c>
       <c r="D16" t="n">
         <v>1.30739e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-273.061</v>
+        <v>76.57900000000001</v>
       </c>
       <c r="D17" t="n">
         <v>1.30682e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-269.231</v>
+        <v>76.11499999999995</v>
       </c>
       <c r="D18" t="n">
         <v>1.30609e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-264.191</v>
+        <v>74.577</v>
       </c>
       <c r="D19" t="n">
         <v>1.30585e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-261.0170000000001</v>
+        <v>73.88200000000001</v>
       </c>
       <c r="D20" t="n">
         <v>1.30541e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-263.503</v>
+        <v>68.15800000000002</v>
       </c>
       <c r="D21" t="n">
         <v>1.30485e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-252.7429999999999</v>
+        <v>73.74900000000002</v>
       </c>
       <c r="D22" t="n">
         <v>1.30452e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1025.074</v>
+        <v>124.007</v>
       </c>
       <c r="D2" t="n">
         <v>1.42364e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-761.4280000000001</v>
+        <v>83.63200000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.42039e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-613.395</v>
+        <v>79.17600000000004</v>
       </c>
       <c r="D4" t="n">
         <v>1.39813e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-531.818</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.37992e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-473.7760000000001</v>
+        <v>70.00899999999996</v>
       </c>
       <c r="D6" t="n">
         <v>1.36703e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-440.054</v>
+        <v>65.73400000000004</v>
       </c>
       <c r="D7" t="n">
         <v>1.3576e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-407.7500000000001</v>
+        <v>65.70699999999999</v>
       </c>
       <c r="D8" t="n">
         <v>1.35109e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-392.219</v>
+        <v>59.49400000000003</v>
       </c>
       <c r="D9" t="n">
         <v>1.34609e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-370.448</v>
+        <v>60.26400000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.3425e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-354.895</v>
+        <v>60.077</v>
       </c>
       <c r="D11" t="n">
         <v>1.33984e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-638.0010000000001</v>
+        <v>120.405</v>
       </c>
       <c r="D2" t="n">
         <v>1.4003e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-452.424</v>
+        <v>106.272</v>
       </c>
       <c r="D3" t="n">
         <v>1.36711e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-392.71</v>
+        <v>100.224</v>
       </c>
       <c r="D4" t="n">
         <v>1.35447e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-359.264</v>
+        <v>99.923</v>
       </c>
       <c r="D5" t="n">
         <v>1.34813e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-346.229</v>
+        <v>91.04399999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.34414e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-334.555</v>
+        <v>85.00900000000001</v>
       </c>
       <c r="D7" t="n">
         <v>1.34128e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-318.557</v>
+        <v>91.34000000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.33927e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-311.059</v>
+        <v>88.19399999999996</v>
       </c>
       <c r="D9" t="n">
         <v>1.33729e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-304.948</v>
+        <v>86.22899999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.33595e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-299.026</v>
+        <v>84.887</v>
       </c>
       <c r="D11" t="n">
         <v>1.33485e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-293.3960000000001</v>
+        <v>84.24399999999997</v>
       </c>
       <c r="D12" t="n">
         <v>1.33389e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-288.478</v>
+        <v>80.80599999999998</v>
       </c>
       <c r="D13" t="n">
         <v>1.33293e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-283.853</v>
+        <v>80.16300000000001</v>
       </c>
       <c r="D14" t="n">
         <v>1.33203e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-287.0189999999999</v>
+        <v>72.80300000000005</v>
       </c>
       <c r="D15" t="n">
         <v>1.33143e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-273.194</v>
+        <v>79.13499999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.33054e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-271.648</v>
+        <v>77.017</v>
       </c>
       <c r="D17" t="n">
         <v>1.33038e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-265.635</v>
+        <v>78.03199999999998</v>
       </c>
       <c r="D18" t="n">
         <v>1.32974e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-264.2040000000001</v>
+        <v>74.76599999999996</v>
       </c>
       <c r="D19" t="n">
         <v>1.32936e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-253.407</v>
+        <v>81.35699999999997</v>
       </c>
       <c r="D20" t="n">
         <v>1.32884e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-262.4709999999999</v>
+        <v>67.51500000000004</v>
       </c>
       <c r="D21" t="n">
         <v>1.32834e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-249.913</v>
+        <v>76.25200000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.32818e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1020.75</v>
+        <v>134.256</v>
       </c>
       <c r="D2" t="n">
         <v>1.45121e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-727.758</v>
+        <v>82.05099999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.44345e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-574.908</v>
+        <v>72.76100000000002</v>
       </c>
       <c r="D4" t="n">
         <v>1.41798e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-486.778</v>
+        <v>69.72300000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.39885e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-428.646</v>
+        <v>69.18100000000004</v>
       </c>
       <c r="D6" t="n">
         <v>1.38618e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-388.851</v>
+        <v>70.18599999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.37709e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-363.164</v>
+        <v>63.12099999999998</v>
       </c>
       <c r="D8" t="n">
         <v>1.37161e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-344.14</v>
+        <v>60.96899999999999</v>
       </c>
       <c r="D9" t="n">
         <v>1.36684e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-329.702</v>
+        <v>60.221</v>
       </c>
       <c r="D10" t="n">
         <v>1.36418e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-315.8560000000001</v>
+        <v>58.30099999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.36178e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-608.9560000000001</v>
+        <v>112.704</v>
       </c>
       <c r="D2" t="n">
         <v>1.43565e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-444.6999999999999</v>
+        <v>106.277</v>
       </c>
       <c r="D3" t="n">
         <v>1.40363e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-383.852</v>
+        <v>98.12400000000002</v>
       </c>
       <c r="D4" t="n">
         <v>1.39069e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-351.7339999999999</v>
+        <v>96.012</v>
       </c>
       <c r="D5" t="n">
         <v>1.38452e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-337.012</v>
+        <v>89.96599999999995</v>
       </c>
       <c r="D6" t="n">
         <v>1.38064e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-316.075</v>
+        <v>94.36799999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.37826e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-310.097</v>
+        <v>88.21200000000005</v>
       </c>
       <c r="D8" t="n">
         <v>1.37642e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-301.028</v>
+        <v>86.52100000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.37501e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-293.661</v>
+        <v>84.55599999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.37379e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-285.8539999999999</v>
+        <v>85.34500000000003</v>
       </c>
       <c r="D11" t="n">
         <v>1.37277e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-287.692</v>
+        <v>77.20300000000003</v>
       </c>
       <c r="D12" t="n">
         <v>1.37214e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-278.355</v>
+        <v>80.02299999999997</v>
       </c>
       <c r="D13" t="n">
         <v>1.37122e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-278.026</v>
+        <v>75.322</v>
       </c>
       <c r="D14" t="n">
         <v>1.3706e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-269.083</v>
+        <v>78.28199999999998</v>
       </c>
       <c r="D15" t="n">
         <v>1.36985e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-264.576</v>
+        <v>76.464</v>
       </c>
       <c r="D16" t="n">
         <v>1.36958e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-266.073</v>
+        <v>72.988</v>
       </c>
       <c r="D17" t="n">
         <v>1.36887e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-258.6390000000001</v>
+        <v>74.37799999999999</v>
       </c>
       <c r="D18" t="n">
         <v>1.36843e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-255.449</v>
+        <v>73.68599999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.36822e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-251.033</v>
+        <v>73.13099999999997</v>
       </c>
       <c r="D20" t="n">
         <v>1.36795e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-250.662</v>
+        <v>71.46600000000001</v>
       </c>
       <c r="D21" t="n">
         <v>1.36769e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-247.7919999999999</v>
+        <v>70.26300000000003</v>
       </c>
       <c r="D22" t="n">
         <v>1.36741e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-894.4929999999999</v>
+        <v>100.56</v>
       </c>
       <c r="D2" t="n">
         <v>1.47798e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-550.8199999999999</v>
+        <v>70.649</v>
       </c>
       <c r="D3" t="n">
         <v>1.43856e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-426.4520000000001</v>
+        <v>65.30499999999995</v>
       </c>
       <c r="D4" t="n">
         <v>1.41636e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-361.5520000000001</v>
+        <v>68.39299999999997</v>
       </c>
       <c r="D5" t="n">
         <v>1.40476e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-333.287</v>
+        <v>60.45499999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.39867e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-313.081</v>
+        <v>57.06100000000004</v>
       </c>
       <c r="D7" t="n">
         <v>1.39524e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-297.344</v>
+        <v>55.97399999999999</v>
       </c>
       <c r="D8" t="n">
         <v>1.39352e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-284.604</v>
+        <v>54.41900000000004</v>
       </c>
       <c r="D9" t="n">
         <v>1.39268e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-277.068</v>
+        <v>52.26300000000003</v>
       </c>
       <c r="D10" t="n">
         <v>1.39238e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-272.275</v>
+        <v>48.93799999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.39217e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>126.462</v>
       </c>
+      <c r="C2" t="n">
+        <v>1017.88851155658</v>
+      </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>120.127</v>
       </c>
+      <c r="C3" t="n">
+        <v>1053.888954982774</v>
+      </c>
       <c r="D3" t="n">
         <v>1.30011e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>113.013</v>
       </c>
+      <c r="C4" t="n">
+        <v>998.4176864547366</v>
+      </c>
       <c r="D4" t="n">
         <v>1.29335e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>111.574</v>
       </c>
+      <c r="C5" t="n">
+        <v>1159.72573684731</v>
+      </c>
       <c r="D5" t="n">
         <v>1.28864e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>104.864</v>
       </c>
+      <c r="C6" t="n">
+        <v>1045.020724518413</v>
+      </c>
       <c r="D6" t="n">
         <v>1.28581e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>100.478</v>
       </c>
+      <c r="C7" t="n">
+        <v>972.9363551862095</v>
+      </c>
       <c r="D7" t="n">
         <v>1.28356e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>99.42899999999997</v>
       </c>
+      <c r="C8" t="n">
+        <v>1107.770546715708</v>
+      </c>
       <c r="D8" t="n">
         <v>1.28196e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>97.62399999999997</v>
       </c>
+      <c r="C9" t="n">
+        <v>1204.438334754739</v>
+      </c>
       <c r="D9" t="n">
         <v>1.27971e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>90.94600000000003</v>
       </c>
+      <c r="C10" t="n">
+        <v>1054.261422280394</v>
+      </c>
       <c r="D10" t="n">
         <v>1.27854e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>89.99900000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1073.449074858583</v>
       </c>
       <c r="D11" t="n">
         <v>1.2773e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>115.611</v>
       </c>
+      <c r="C2" t="n">
+        <v>1278.886081384958</v>
+      </c>
       <c r="D2" t="n">
         <v>1.4007e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>97.70499999999998</v>
       </c>
+      <c r="C3" t="n">
+        <v>955.791830523703</v>
+      </c>
       <c r="D3" t="n">
         <v>1.39345e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>97.13600000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>910.4822583435306</v>
+      </c>
       <c r="D4" t="n">
         <v>1.38986e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>90.66300000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>930.8328895586332</v>
+      </c>
       <c r="D5" t="n">
         <v>1.38786e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>93.30000000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1147.42885411885</v>
+      </c>
       <c r="D6" t="n">
         <v>1.38667e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>88.84399999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>974.0600611417823</v>
+      </c>
       <c r="D7" t="n">
         <v>1.38581e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>88.85899999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>1251.218660613435</v>
+      </c>
       <c r="D8" t="n">
         <v>1.38516e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>85.46800000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1086.490157463134</v>
+      </c>
       <c r="D9" t="n">
         <v>1.38474e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>86.26900000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1286.492593500101</v>
+      </c>
       <c r="D10" t="n">
         <v>1.38429e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>83.37299999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1217.020943173798</v>
+      </c>
       <c r="D11" t="n">
         <v>1.38354e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>80.09399999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1096.031992192015</v>
+      </c>
       <c r="D12" t="n">
         <v>1.38316e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>77.12099999999998</v>
       </c>
+      <c r="C13" t="n">
+        <v>1053.382367643964</v>
+      </c>
       <c r="D13" t="n">
         <v>1.38329e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>79.024</v>
       </c>
+      <c r="C14" t="n">
+        <v>1073.381528565727</v>
+      </c>
       <c r="D14" t="n">
         <v>1.38237e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>76.39699999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1194.016196606867</v>
+      </c>
       <c r="D15" t="n">
         <v>1.38212e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>76.05099999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1277.928003933494</v>
+      </c>
       <c r="D16" t="n">
         <v>1.38169e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>74.41500000000002</v>
       </c>
+      <c r="C17" t="n">
+        <v>1194.337919193817</v>
+      </c>
       <c r="D17" t="n">
         <v>1.38151e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>75.26500000000004</v>
       </c>
+      <c r="C18" t="n">
+        <v>1677.128486219671</v>
+      </c>
       <c r="D18" t="n">
         <v>1.38102e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>72.649</v>
       </c>
+      <c r="C19" t="n">
+        <v>1295.683644519189</v>
+      </c>
       <c r="D19" t="n">
         <v>1.38053e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>70.15699999999998</v>
       </c>
+      <c r="C20" t="n">
+        <v>1227.776196302854</v>
+      </c>
       <c r="D20" t="n">
         <v>1.38014e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>69.86399999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1404.023509065789</v>
+      </c>
       <c r="D21" t="n">
         <v>1.38002e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.46100000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1204.304152207879</v>
       </c>
       <c r="D22" t="n">
         <v>1.37988e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>128.455</v>
       </c>
+      <c r="C2" t="n">
+        <v>1908.260990529206</v>
+      </c>
       <c r="D2" t="n">
         <v>1.31411e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>111.482</v>
       </c>
+      <c r="C3" t="n">
+        <v>1141.811360119688</v>
+      </c>
       <c r="D3" t="n">
         <v>1.29962e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>105.075</v>
       </c>
+      <c r="C4" t="n">
+        <v>1032.021289282736</v>
+      </c>
       <c r="D4" t="n">
         <v>1.29233e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>102.436</v>
       </c>
+      <c r="C5" t="n">
+        <v>1074.053095067493</v>
+      </c>
       <c r="D5" t="n">
         <v>1.28793e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>97.84100000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1012.492127963182</v>
+      </c>
       <c r="D6" t="n">
         <v>1.28431e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>96.60300000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>1008.735500400367</v>
+      </c>
       <c r="D7" t="n">
         <v>1.28143e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>95.69100000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>1195.40325980122</v>
+      </c>
       <c r="D8" t="n">
         <v>1.27985e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>92.08800000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1160.865717802625</v>
+      </c>
       <c r="D9" t="n">
         <v>1.27862e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>90.72899999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>1227.721660610156</v>
+      </c>
       <c r="D10" t="n">
         <v>1.27761e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>89.14699999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1156.201695695959</v>
+      </c>
       <c r="D11" t="n">
         <v>1.2767e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>86.73400000000004</v>
       </c>
+      <c r="C12" t="n">
+        <v>1232.905274456279</v>
+      </c>
       <c r="D12" t="n">
         <v>1.27615e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>87.87199999999996</v>
       </c>
+      <c r="C13" t="n">
+        <v>1460.598831866239</v>
+      </c>
       <c r="D13" t="n">
         <v>1.27526e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>85.00900000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>1356.21092116884</v>
+      </c>
       <c r="D14" t="n">
         <v>1.27443e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>81.565</v>
       </c>
+      <c r="C15" t="n">
+        <v>1182.097038330038</v>
+      </c>
       <c r="D15" t="n">
         <v>1.27374e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>80.928</v>
       </c>
+      <c r="C16" t="n">
+        <v>1249.14829636005</v>
+      </c>
       <c r="D16" t="n">
         <v>1.27307e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>78.68000000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>1292.995816153867</v>
+      </c>
       <c r="D17" t="n">
         <v>1.27252e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>79.79400000000004</v>
       </c>
+      <c r="C18" t="n">
+        <v>1306.758203646116</v>
+      </c>
       <c r="D18" t="n">
         <v>1.27191e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>78.06999999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>1587.364579979923</v>
+      </c>
       <c r="D19" t="n">
         <v>1.27144e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>76.40500000000003</v>
       </c>
+      <c r="C20" t="n">
+        <v>1615.065107499896</v>
+      </c>
       <c r="D20" t="n">
         <v>1.27113e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>74.73899999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1472.759252385429</v>
+      </c>
       <c r="D21" t="n">
         <v>1.2708e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>72.61700000000002</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1552.585842567669</v>
       </c>
       <c r="D22" t="n">
         <v>1.27013e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>130.234</v>
       </c>
+      <c r="C2" t="n">
+        <v>2030.380010873487</v>
+      </c>
       <c r="D2" t="n">
         <v>1.37996e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>85.577</v>
       </c>
+      <c r="C3" t="n">
+        <v>3445.383928418348</v>
+      </c>
       <c r="D3" t="n">
         <v>1.39236e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>76.524</v>
       </c>
+      <c r="C4" t="n">
+        <v>2050.609081365511</v>
+      </c>
       <c r="D4" t="n">
         <v>1.37508e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>73.04199999999997</v>
       </c>
+      <c r="C5" t="n">
+        <v>2785.41534179792</v>
+      </c>
       <c r="D5" t="n">
         <v>1.35982e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>67.81400000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1735.471983707592</v>
+      </c>
       <c r="D6" t="n">
         <v>1.34835e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>68.13100000000003</v>
       </c>
+      <c r="C7" t="n">
+        <v>6488.034504567761</v>
+      </c>
       <c r="D7" t="n">
         <v>1.33972e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>63.90199999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>3124.800378239937</v>
+      </c>
       <c r="D8" t="n">
         <v>1.33379e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>60.459</v>
       </c>
+      <c r="C9" t="n">
+        <v>2165.777267477766</v>
+      </c>
       <c r="D9" t="n">
         <v>1.32873e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>61.10899999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>8789.157046651355</v>
+      </c>
       <c r="D10" t="n">
         <v>1.3251e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>56.19099999999997</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2077.900725664247</v>
       </c>
       <c r="D11" t="n">
         <v>1.3222e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>113.145</v>
       </c>
+      <c r="C2" t="n">
+        <v>1219.300204779536</v>
+      </c>
       <c r="D2" t="n">
         <v>1.35036e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>104.525</v>
       </c>
+      <c r="C3" t="n">
+        <v>1064.446076648025</v>
+      </c>
       <c r="D3" t="n">
         <v>1.33679e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>101.551</v>
       </c>
+      <c r="C4" t="n">
+        <v>1110.308718057529</v>
+      </c>
       <c r="D4" t="n">
         <v>1.32952e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>98.47399999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>1070.902101066394</v>
+      </c>
       <c r="D5" t="n">
         <v>1.32425e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>96.40899999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>991.9698681954582</v>
+      </c>
       <c r="D6" t="n">
         <v>1.32104e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>93.51799999999997</v>
       </c>
+      <c r="C7" t="n">
+        <v>1185.173663089795</v>
+      </c>
       <c r="D7" t="n">
         <v>1.31841e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>92.80500000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1216.51410693814</v>
+      </c>
       <c r="D8" t="n">
         <v>1.31663e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>90.05799999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1198.402847344292</v>
+      </c>
       <c r="D9" t="n">
         <v>1.3149e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>83.95999999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>1047.033273564958</v>
+      </c>
       <c r="D10" t="n">
         <v>1.31353e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>85.44400000000002</v>
       </c>
+      <c r="C11" t="n">
+        <v>1140.823173333995</v>
+      </c>
       <c r="D11" t="n">
         <v>1.31225e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>83.76499999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1079.32323783227</v>
+      </c>
       <c r="D12" t="n">
         <v>1.31102e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>84.488</v>
       </c>
+      <c r="C13" t="n">
+        <v>1145.375326485122</v>
+      </c>
       <c r="D13" t="n">
         <v>1.30994e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>79.09700000000004</v>
       </c>
+      <c r="C14" t="n">
+        <v>1139.184100029985</v>
+      </c>
       <c r="D14" t="n">
         <v>1.30901e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>77.55600000000004</v>
       </c>
+      <c r="C15" t="n">
+        <v>1114.08622816765</v>
+      </c>
       <c r="D15" t="n">
         <v>1.30828e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>77.27599999999995</v>
       </c>
+      <c r="C16" t="n">
+        <v>1155.619075740245</v>
+      </c>
       <c r="D16" t="n">
         <v>1.30739e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>76.57900000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>1155.005186868228</v>
+      </c>
       <c r="D17" t="n">
         <v>1.30682e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>76.11499999999995</v>
       </c>
+      <c r="C18" t="n">
+        <v>1348.199724793148</v>
+      </c>
       <c r="D18" t="n">
         <v>1.30609e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>74.577</v>
       </c>
+      <c r="C19" t="n">
+        <v>1253.286013960683</v>
+      </c>
       <c r="D19" t="n">
         <v>1.30585e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>73.88200000000001</v>
       </c>
+      <c r="C20" t="n">
+        <v>1351.5918730016</v>
+      </c>
       <c r="D20" t="n">
         <v>1.30541e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>68.15800000000002</v>
       </c>
+      <c r="C21" t="n">
+        <v>1350.186345133656</v>
+      </c>
       <c r="D21" t="n">
         <v>1.30485e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>73.74900000000002</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1454.142843256388</v>
       </c>
       <c r="D22" t="n">
         <v>1.30452e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>124.007</v>
       </c>
+      <c r="C2" t="n">
+        <v>2011.612443724747</v>
+      </c>
       <c r="D2" t="n">
         <v>1.42364e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>83.63200000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>3495.85189406501</v>
+      </c>
       <c r="D3" t="n">
         <v>1.42039e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>79.17600000000004</v>
       </c>
+      <c r="C4" t="n">
+        <v>2033.903716206219</v>
+      </c>
       <c r="D4" t="n">
         <v>1.39813e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>72.18000000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>2168.67188992175</v>
+      </c>
       <c r="D5" t="n">
         <v>1.37992e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>70.00899999999996</v>
       </c>
+      <c r="C6" t="n">
+        <v>2084.806536333833</v>
+      </c>
       <c r="D6" t="n">
         <v>1.36703e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>65.73400000000004</v>
       </c>
+      <c r="C7" t="n">
+        <v>1796.265174325102</v>
+      </c>
       <c r="D7" t="n">
         <v>1.3576e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>65.70699999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>3086.262510982587</v>
+      </c>
       <c r="D8" t="n">
         <v>1.35109e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>59.49400000000003</v>
       </c>
+      <c r="C9" t="n">
+        <v>3897.388047761029</v>
+      </c>
       <c r="D9" t="n">
         <v>1.34609e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>60.26400000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>3487.529652362728</v>
+      </c>
       <c r="D10" t="n">
         <v>1.3425e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>60.077</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5828.930850222042</v>
       </c>
       <c r="D11" t="n">
         <v>1.33984e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>120.405</v>
       </c>
+      <c r="C2" t="n">
+        <v>1511.883306060246</v>
+      </c>
       <c r="D2" t="n">
         <v>1.4003e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>106.272</v>
       </c>
+      <c r="C3" t="n">
+        <v>1111.215722597798</v>
+      </c>
       <c r="D3" t="n">
         <v>1.36711e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>100.224</v>
       </c>
+      <c r="C4" t="n">
+        <v>1044.551409053521</v>
+      </c>
       <c r="D4" t="n">
         <v>1.35447e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>99.923</v>
       </c>
+      <c r="C5" t="n">
+        <v>964.896273246979</v>
+      </c>
       <c r="D5" t="n">
         <v>1.34813e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>91.04399999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>942.9364327278213</v>
+      </c>
       <c r="D6" t="n">
         <v>1.34414e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>85.00900000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>956.5271380866474</v>
+      </c>
       <c r="D7" t="n">
         <v>1.34128e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>91.34000000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>1196.886266794471</v>
+      </c>
       <c r="D8" t="n">
         <v>1.33927e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>88.19399999999996</v>
       </c>
+      <c r="C9" t="n">
+        <v>1190.220921449024</v>
+      </c>
       <c r="D9" t="n">
         <v>1.33729e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>86.22899999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>1128.509710844802</v>
+      </c>
       <c r="D10" t="n">
         <v>1.33595e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>84.887</v>
       </c>
+      <c r="C11" t="n">
+        <v>1142.898646326923</v>
+      </c>
       <c r="D11" t="n">
         <v>1.33485e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>84.24399999999997</v>
       </c>
+      <c r="C12" t="n">
+        <v>1247.375020500277</v>
+      </c>
       <c r="D12" t="n">
         <v>1.33389e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>80.80599999999998</v>
       </c>
+      <c r="C13" t="n">
+        <v>1075.41726769733</v>
+      </c>
       <c r="D13" t="n">
         <v>1.33293e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>80.16300000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>1057.674916194222</v>
+      </c>
       <c r="D14" t="n">
         <v>1.33203e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>72.80300000000005</v>
       </c>
+      <c r="C15" t="n">
+        <v>1073.914181366701</v>
+      </c>
       <c r="D15" t="n">
         <v>1.33143e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>79.13499999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1344.542937852518</v>
+      </c>
       <c r="D16" t="n">
         <v>1.33054e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>77.017</v>
       </c>
+      <c r="C17" t="n">
+        <v>1243.196112514063</v>
+      </c>
       <c r="D17" t="n">
         <v>1.33038e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>78.03199999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>1180.872582257425</v>
+      </c>
       <c r="D18" t="n">
         <v>1.32974e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>74.76599999999996</v>
       </c>
+      <c r="C19" t="n">
+        <v>1321.017014404334</v>
+      </c>
       <c r="D19" t="n">
         <v>1.32936e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>81.35699999999997</v>
       </c>
+      <c r="C20" t="n">
+        <v>1380.415501785433</v>
+      </c>
       <c r="D20" t="n">
         <v>1.32884e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>67.51500000000004</v>
       </c>
+      <c r="C21" t="n">
+        <v>1234.261565383726</v>
+      </c>
       <c r="D21" t="n">
         <v>1.32834e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>76.25200000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1447.475565144302</v>
       </c>
       <c r="D22" t="n">
         <v>1.32818e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>134.256</v>
       </c>
+      <c r="C2" t="n">
+        <v>1357.332671937825</v>
+      </c>
       <c r="D2" t="n">
         <v>1.45121e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>82.05099999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>2576.242322725203</v>
+      </c>
       <c r="D3" t="n">
         <v>1.44345e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>72.76100000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>1729.448086621572</v>
+      </c>
       <c r="D4" t="n">
         <v>1.41798e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>69.72300000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1557.670874235105</v>
+      </c>
       <c r="D5" t="n">
         <v>1.39885e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>69.18100000000004</v>
       </c>
+      <c r="C6" t="n">
+        <v>2728.311317800298</v>
+      </c>
       <c r="D6" t="n">
         <v>1.38618e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>70.18599999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>2699.881846719973</v>
+      </c>
       <c r="D7" t="n">
         <v>1.37709e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>63.12099999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>2191.806692688222</v>
+      </c>
       <c r="D8" t="n">
         <v>1.37161e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>60.96899999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>2997.566226451623</v>
+      </c>
       <c r="D9" t="n">
         <v>1.36684e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>60.221</v>
       </c>
+      <c r="C10" t="n">
+        <v>5984.979771433238</v>
+      </c>
       <c r="D10" t="n">
         <v>1.36418e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>58.30099999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7700.796048501948</v>
       </c>
       <c r="D11" t="n">
         <v>1.36178e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>112.704</v>
       </c>
+      <c r="C2" t="n">
+        <v>1193.055211275207</v>
+      </c>
       <c r="D2" t="n">
         <v>1.43565e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>106.277</v>
       </c>
+      <c r="C3" t="n">
+        <v>961.4522379248406</v>
+      </c>
       <c r="D3" t="n">
         <v>1.40363e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>98.12400000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>985.494511659311</v>
+      </c>
       <c r="D4" t="n">
         <v>1.39069e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>96.012</v>
       </c>
+      <c r="C5" t="n">
+        <v>1002.10624829965</v>
+      </c>
       <c r="D5" t="n">
         <v>1.38452e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>89.96599999999995</v>
       </c>
+      <c r="C6" t="n">
+        <v>943.4716840086022</v>
+      </c>
       <c r="D6" t="n">
         <v>1.38064e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>94.36799999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>957.796178747469</v>
+      </c>
       <c r="D7" t="n">
         <v>1.37826e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>88.21200000000005</v>
       </c>
+      <c r="C8" t="n">
+        <v>961.9155868322862</v>
+      </c>
       <c r="D8" t="n">
         <v>1.37642e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>86.52100000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1001.090225451148</v>
+      </c>
       <c r="D9" t="n">
         <v>1.37501e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>84.55599999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>993.1428419713969</v>
+      </c>
       <c r="D10" t="n">
         <v>1.37379e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>85.34500000000003</v>
       </c>
+      <c r="C11" t="n">
+        <v>1014.198733875123</v>
+      </c>
       <c r="D11" t="n">
         <v>1.37277e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>77.20300000000003</v>
       </c>
+      <c r="C12" t="n">
+        <v>1010.515173696825</v>
+      </c>
       <c r="D12" t="n">
         <v>1.37214e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>80.02299999999997</v>
       </c>
+      <c r="C13" t="n">
+        <v>1043.592620797343</v>
+      </c>
       <c r="D13" t="n">
         <v>1.37122e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>75.322</v>
       </c>
+      <c r="C14" t="n">
+        <v>1035.771274177843</v>
+      </c>
       <c r="D14" t="n">
         <v>1.3706e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>78.28199999999998</v>
       </c>
+      <c r="C15" t="n">
+        <v>1147.580437365002</v>
+      </c>
       <c r="D15" t="n">
         <v>1.36985e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>76.464</v>
       </c>
+      <c r="C16" t="n">
+        <v>1175.301653432448</v>
+      </c>
       <c r="D16" t="n">
         <v>1.36958e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>72.988</v>
       </c>
+      <c r="C17" t="n">
+        <v>1089.703197627686</v>
+      </c>
       <c r="D17" t="n">
         <v>1.36887e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>74.37799999999999</v>
       </c>
+      <c r="C18" t="n">
+        <v>1237.866964721545</v>
+      </c>
       <c r="D18" t="n">
         <v>1.36843e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>73.68599999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>1374.122971297147</v>
+      </c>
       <c r="D19" t="n">
         <v>1.36822e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>73.13099999999997</v>
       </c>
+      <c r="C20" t="n">
+        <v>1219.265013511809</v>
+      </c>
       <c r="D20" t="n">
         <v>1.36795e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>71.46600000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>1425.72425234788</v>
+      </c>
       <c r="D21" t="n">
         <v>1.36769e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>70.26300000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1582.263100357433</v>
       </c>
       <c r="D22" t="n">
         <v>1.36741e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>100.56</v>
       </c>
+      <c r="C2" t="n">
+        <v>1212.64855539107</v>
+      </c>
       <c r="D2" t="n">
         <v>1.47798e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>70.649</v>
       </c>
+      <c r="C3" t="n">
+        <v>2680.169616607989</v>
+      </c>
       <c r="D3" t="n">
         <v>1.43856e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>65.30499999999995</v>
       </c>
+      <c r="C4" t="n">
+        <v>2772.353020694173</v>
+      </c>
       <c r="D4" t="n">
         <v>1.41636e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>68.39299999999997</v>
       </c>
+      <c r="C5" t="n">
+        <v>3936.753456025812</v>
+      </c>
       <c r="D5" t="n">
         <v>1.40476e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>60.45499999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>3800.93210713362</v>
+      </c>
       <c r="D6" t="n">
         <v>1.39867e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>57.06100000000004</v>
       </c>
+      <c r="C7" t="n">
+        <v>10932.94245709177</v>
+      </c>
       <c r="D7" t="n">
         <v>1.39524e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>55.97399999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>5691.992514653214</v>
+      </c>
       <c r="D8" t="n">
         <v>1.39352e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>54.41900000000004</v>
       </c>
+      <c r="C9" t="n">
+        <v>80690.26115623501</v>
+      </c>
       <c r="D9" t="n">
         <v>1.39268e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>52.26300000000003</v>
       </c>
+      <c r="C10" t="n">
+        <v>137086.1988007794</v>
+      </c>
       <c r="D10" t="n">
         <v>1.39238e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>48.93799999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5218.273174827402</v>
       </c>
       <c r="D11" t="n">
         <v>1.39217e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -565,7 +565,7 @@
         <v>126.462</v>
       </c>
       <c r="C2" t="n">
-        <v>1017.88851155658</v>
+        <v>126.462</v>
       </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-12344.37768874648</v>
       </c>
-      <c r="Y2" t="n">
-        <v>467.6570940016832</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>256485948.4332564</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>1.765856924959165e-07</v>
@@ -618,7 +617,7 @@
         <v>120.127</v>
       </c>
       <c r="C3" t="n">
-        <v>1053.888954982774</v>
+        <v>350.709514039002</v>
       </c>
       <c r="D3" t="n">
         <v>1.30011e-07</v>
@@ -651,16 +650,13 @@
         <v>-13489.03786423497</v>
       </c>
       <c r="Y3" t="n">
-        <v>460.842479074512</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>630266120.0473253</v>
+        <v>167.4605554971177</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.708017582691505e-07</v>
+        <v>1.722063759940185e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9578916680277162</v>
+        <v>0.9986138260103288</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>113.013</v>
       </c>
       <c r="C4" t="n">
-        <v>998.4176864547366</v>
+        <v>113.013</v>
       </c>
       <c r="D4" t="n">
         <v>1.29335e-07</v>
@@ -703,11 +699,10 @@
       <c r="X4" t="n">
         <v>-13863.96538051371</v>
       </c>
-      <c r="Y4" t="n">
-        <v>436.8494436332582</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>18892.58923630365</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.661877335263083e-07</v>
@@ -724,7 +719,7 @@
         <v>111.574</v>
       </c>
       <c r="C5" t="n">
-        <v>1159.72573684731</v>
+        <v>324.494113168882</v>
       </c>
       <c r="D5" t="n">
         <v>1.28864e-07</v>
@@ -757,16 +752,13 @@
         <v>-14903.05133271452</v>
       </c>
       <c r="Y5" t="n">
-        <v>448.7462546299487</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>491689290.2403167</v>
+        <v>179.9931945001656</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.642305570667434e-07</v>
+        <v>1.863579473728639e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9625287614976732</v>
+        <v>0.9997911715928505</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +769,7 @@
         <v>104.864</v>
       </c>
       <c r="C6" t="n">
-        <v>1045.020724518413</v>
+        <v>104.864</v>
       </c>
       <c r="D6" t="n">
         <v>1.28581e-07</v>
@@ -809,11 +801,10 @@
       <c r="X6" t="n">
         <v>-14783.95811005138</v>
       </c>
-      <c r="Y6" t="n">
-        <v>443.3097998353818</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>485544532.7090031</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.624525978720059e-07</v>
@@ -830,7 +821,7 @@
         <v>100.478</v>
       </c>
       <c r="C7" t="n">
-        <v>972.9363551862095</v>
+        <v>279.6211029875773</v>
       </c>
       <c r="D7" t="n">
         <v>1.28356e-07</v>
@@ -863,16 +854,13 @@
         <v>-14768.77376278749</v>
       </c>
       <c r="Y7" t="n">
-        <v>438.1425064061951</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>120043184.2007365</v>
+        <v>224.5901466005297</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.608399886353592e-07</v>
+        <v>2.803919173082032e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9651172059383819</v>
+        <v>0.9943017056898975</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +871,7 @@
         <v>99.42899999999997</v>
       </c>
       <c r="C8" t="n">
-        <v>1107.770546715708</v>
+        <v>258.2593503850659</v>
       </c>
       <c r="D8" t="n">
         <v>1.28196e-07</v>
@@ -916,16 +904,13 @@
         <v>-15407.87487417757</v>
       </c>
       <c r="Y8" t="n">
-        <v>379.6747431750197</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14352.53679729584</v>
+        <v>242.4975014458217</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88059960962276e-07</v>
+        <v>3.995261903214791e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9995785702830648</v>
+        <v>0.9802154211008546</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +921,7 @@
         <v>97.62399999999997</v>
       </c>
       <c r="C9" t="n">
-        <v>1204.438334754739</v>
+        <v>272.4940011150844</v>
       </c>
       <c r="D9" t="n">
         <v>1.27971e-07</v>
@@ -969,16 +954,13 @@
         <v>-15823.33750516756</v>
       </c>
       <c r="Y9" t="n">
-        <v>428.0859084856359</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>934326069.9412551</v>
+        <v>217.7810283576211</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.582859134618542e-07</v>
+        <v>2.817194370839032e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.967108551661319</v>
+        <v>0.9901845443776265</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +971,7 @@
         <v>90.94600000000003</v>
       </c>
       <c r="C10" t="n">
-        <v>1054.261422280394</v>
+        <v>270.464489143676</v>
       </c>
       <c r="D10" t="n">
         <v>1.27854e-07</v>
@@ -1022,16 +1004,13 @@
         <v>-15136.25084606659</v>
       </c>
       <c r="Y10" t="n">
-        <v>423.2099813772927</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>236038914.182063</v>
+        <v>216.4949910995768</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57251038502611e-07</v>
+        <v>2.596509624283394e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9679733493192154</v>
+        <v>0.9992307438145945</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1021,7 @@
         <v>89.99900000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1073.449074858583</v>
+        <v>271.653225451993</v>
       </c>
       <c r="D11" t="n">
         <v>1.2773e-07</v>
@@ -1075,16 +1054,13 @@
         <v>-15531.25305697876</v>
       </c>
       <c r="Y11" t="n">
-        <v>418.6770996582599</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>344760190.966718</v>
+        <v>215.1335023312679</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.563857707125518e-07</v>
+        <v>2.782526557021624e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9686732710935785</v>
+        <v>0.9993444902882843</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1217,7 @@
         <v>115.611</v>
       </c>
       <c r="C2" t="n">
-        <v>1278.886081384958</v>
+        <v>432.9188242283471</v>
       </c>
       <c r="D2" t="n">
         <v>1.4007e-07</v>
@@ -1274,16 +1250,13 @@
         <v>-12822.02778880958</v>
       </c>
       <c r="Y2" t="n">
-        <v>449.6745171879671</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>42554130.69681846</v>
+        <v>60.87000534837613</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.835511574532325e-07</v>
+        <v>1.064323391996013e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9582779782550677</v>
+        <v>0.9999668573480585</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1267,7 @@
         <v>97.70499999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>955.791830523703</v>
+        <v>319.0570815725959</v>
       </c>
       <c r="D3" t="n">
         <v>1.39345e-07</v>
@@ -1327,16 +1300,13 @@
         <v>-13557.94999070565</v>
       </c>
       <c r="Y3" t="n">
-        <v>438.4540737227541</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>246431000.570932</v>
+        <v>170.5074650354634</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.763430389738114e-07</v>
+        <v>1.861639195196563e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9635870822507515</v>
+        <v>0.9994498645718658</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1317,7 @@
         <v>97.13600000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>910.4822583435306</v>
+        <v>315.7422532920529</v>
       </c>
       <c r="D4" t="n">
         <v>1.38986e-07</v>
@@ -1380,16 +1350,13 @@
         <v>-15147.33515707951</v>
       </c>
       <c r="Y4" t="n">
-        <v>433.2248310180203</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>25393117.07049244</v>
+        <v>171.8033923509021</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.732865694075292e-07</v>
+        <v>1.9756810319459e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9658671588310183</v>
+        <v>0.9980537300563038</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1367,7 @@
         <v>90.66300000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>930.8328895586332</v>
+        <v>311.8263089877233</v>
       </c>
       <c r="D5" t="n">
         <v>1.38786e-07</v>
@@ -1433,16 +1400,13 @@
         <v>-14808.5196472664</v>
       </c>
       <c r="Y5" t="n">
-        <v>428.8137887709896</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>467768447.6888936</v>
+        <v>170.423984622585</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.718479741523072e-07</v>
+        <v>1.976426949693028e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9669316818352978</v>
+        <v>0.9985737716960523</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1417,7 @@
         <v>93.30000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1147.42885411885</v>
+        <v>307.1084015695213</v>
       </c>
       <c r="D6" t="n">
         <v>1.38667e-07</v>
@@ -1486,16 +1450,13 @@
         <v>-16171.68798660787</v>
       </c>
       <c r="Y6" t="n">
-        <v>408.1742188563638</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7009.65058287773</v>
+        <v>167.6719778983982</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.919311721271531e-07</v>
+        <v>1.936006934540406e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8718001307299609</v>
+        <v>0.9997065339387018</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1467,7 @@
         <v>88.84399999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>974.0600611417823</v>
+        <v>88.84399999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.38581e-07</v>
@@ -1538,11 +1499,10 @@
       <c r="X7" t="n">
         <v>-16045.38937363871</v>
       </c>
-      <c r="Y7" t="n">
-        <v>420.4195331226477</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>25072149.92516794</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.692610012807808e-07</v>
@@ -1559,7 +1519,7 @@
         <v>88.85899999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1251.218660613435</v>
+        <v>299.0334211437487</v>
       </c>
       <c r="D8" t="n">
         <v>1.38516e-07</v>
@@ -1592,16 +1552,13 @@
         <v>-16726.77627878552</v>
       </c>
       <c r="Y8" t="n">
-        <v>397.3689196272579</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3410.637819077788</v>
+        <v>168.7170967600322</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.318479908176496e-06</v>
+        <v>2.02564472857097e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7233618543659136</v>
+        <v>0.9996885055529533</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1569,7 @@
         <v>85.46800000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1086.490157463134</v>
+        <v>293.6406992571287</v>
       </c>
       <c r="D9" t="n">
         <v>1.38474e-07</v>
@@ -1645,16 +1602,13 @@
         <v>-16205.02873704155</v>
       </c>
       <c r="Y9" t="n">
-        <v>395.4983703746601</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3382.47338464426</v>
+        <v>170.0229316831216</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.679114916044387e-06</v>
+        <v>2.063527238391141e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7403640421130188</v>
+        <v>0.9997767645629628</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1619,7 @@
         <v>86.26900000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1286.492593500101</v>
+        <v>86.26900000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.38429e-07</v>
@@ -1697,11 +1651,10 @@
       <c r="X10" t="n">
         <v>-17172.75378590349</v>
       </c>
-      <c r="Y10" t="n">
-        <v>409.177831085275</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>446354202.0403723</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.676641170578329e-07</v>
@@ -1718,7 +1671,7 @@
         <v>83.37299999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1217.020943173798</v>
+        <v>83.37299999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.38354e-07</v>
@@ -1750,11 +1703,10 @@
       <c r="X11" t="n">
         <v>-16898.73726182367</v>
       </c>
-      <c r="Y11" t="n">
-        <v>409.0010012465469</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10607.0661543138</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>2.560644274500548e-07</v>
@@ -1771,7 +1723,7 @@
         <v>80.09399999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1096.031992192015</v>
+        <v>272.9577811281451</v>
       </c>
       <c r="D12" t="n">
         <v>1.38316e-07</v>
@@ -1804,16 +1756,13 @@
         <v>-16228.82403837326</v>
       </c>
       <c r="Y12" t="n">
-        <v>400.011940678606</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6002.323577819623</v>
+        <v>183.2363048643726</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.522591193554731e-07</v>
+        <v>2.418732902253571e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9116645710089836</v>
+        <v>0.9991202805606091</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1773,7 @@
         <v>77.12099999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>1053.382367643964</v>
+        <v>271.3942577503896</v>
       </c>
       <c r="D13" t="n">
         <v>1.38329e-07</v>
@@ -1857,16 +1806,13 @@
         <v>-15942.18692873509</v>
       </c>
       <c r="Y13" t="n">
-        <v>389.3982734493844</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6314.678051446853</v>
+        <v>180.8074417378887</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.299234505709092e-06</v>
+        <v>2.409270555259314e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.7948567441408684</v>
+        <v>0.9993451830201321</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1823,7 @@
         <v>79.024</v>
       </c>
       <c r="C14" t="n">
-        <v>1073.381528565727</v>
+        <v>231.171530875439</v>
       </c>
       <c r="D14" t="n">
         <v>1.38237e-07</v>
@@ -1910,16 +1856,13 @@
         <v>-16936.36643620468</v>
       </c>
       <c r="Y14" t="n">
-        <v>396.5011400072781</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>435210888.7657615</v>
+        <v>211.6828465587813</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.655031488858451e-07</v>
+        <v>2.751417442834842e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9721055695092801</v>
+        <v>0.9996087324300101</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1873,7 @@
         <v>76.39699999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1194.016196606867</v>
+        <v>229.2730070242341</v>
       </c>
       <c r="D15" t="n">
         <v>1.38212e-07</v>
@@ -1963,16 +1906,13 @@
         <v>-16643.30296134172</v>
       </c>
       <c r="Y15" t="n">
-        <v>393.5601479490324</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>214651657.0973744</v>
+        <v>218.0679127214798</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.650238820506533e-07</v>
+        <v>3.029233658340091e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9725220223827753</v>
+        <v>0.9994263817253142</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1923,7 @@
         <v>76.05099999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1277.928003933494</v>
+        <v>76.05099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.38169e-07</v>
@@ -2015,11 +1955,10 @@
       <c r="X16" t="n">
         <v>-16846.48349964605</v>
       </c>
-      <c r="Y16" t="n">
-        <v>378.0915880934682</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3200.021776007199</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.959794187255251e-06</v>
@@ -2036,7 +1975,7 @@
         <v>74.41500000000002</v>
       </c>
       <c r="C17" t="n">
-        <v>1194.337919193817</v>
+        <v>224.8053977943077</v>
       </c>
       <c r="D17" t="n">
         <v>1.38151e-07</v>
@@ -2069,16 +2008,13 @@
         <v>-16857.01893624054</v>
       </c>
       <c r="Y17" t="n">
-        <v>376.0505910099079</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3175.754908420079</v>
+        <v>215.365619841092</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.546383489236969e-06</v>
+        <v>3.026180329335461e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.6872385930589926</v>
+        <v>0.9995291605925954</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2025,7 @@
         <v>75.26500000000004</v>
       </c>
       <c r="C18" t="n">
-        <v>1677.128486219671</v>
+        <v>223.7890633677353</v>
       </c>
       <c r="D18" t="n">
         <v>1.38102e-07</v>
@@ -2122,16 +2058,13 @@
         <v>-17362.76992330362</v>
       </c>
       <c r="Y18" t="n">
-        <v>374.0487902565378</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3150.450023124124</v>
+        <v>216.2720785789252</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.344126717681031e-06</v>
+        <v>3.339379047266922e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.6676270672898907</v>
+        <v>0.9984957090615103</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2075,7 @@
         <v>72.649</v>
       </c>
       <c r="C19" t="n">
-        <v>1295.683644519189</v>
+        <v>72.649</v>
       </c>
       <c r="D19" t="n">
         <v>1.38053e-07</v>
@@ -2174,11 +2107,10 @@
       <c r="X19" t="n">
         <v>-16876.74777693363</v>
       </c>
-      <c r="Y19" t="n">
-        <v>372.049145487165</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3127.323934210941</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.972757512800434e-06</v>
@@ -2195,7 +2127,7 @@
         <v>70.15699999999998</v>
       </c>
       <c r="C20" t="n">
-        <v>1227.776196302854</v>
+        <v>177.4273552731111</v>
       </c>
       <c r="D20" t="n">
         <v>1.38014e-07</v>
@@ -2228,10 +2160,7 @@
         <v>-16516.71193339312</v>
       </c>
       <c r="Y20" t="n">
-        <v>370.0793780290469</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3102.817741932373</v>
+        <v>463.6581291628252</v>
       </c>
       <c r="AA20" t="n">
         <v>4.487402432016493e-06</v>
@@ -2248,7 +2177,7 @@
         <v>69.86399999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1404.023509065789</v>
+        <v>175.183752488253</v>
       </c>
       <c r="D21" t="n">
         <v>1.38002e-07</v>
@@ -2281,10 +2210,7 @@
         <v>-16857.07896105192</v>
       </c>
       <c r="Y21" t="n">
-        <v>368.1090043012</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3080.740831432381</v>
+        <v>459.3149737816511</v>
       </c>
       <c r="AA21" t="n">
         <v>5.742969046266379e-06</v>
@@ -2301,7 +2227,7 @@
         <v>67.46100000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1204.304152207879</v>
+        <v>67.46100000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.37988e-07</v>
@@ -2333,11 +2259,10 @@
       <c r="X22" t="n">
         <v>-16423.9140367922</v>
       </c>
-      <c r="Y22" t="n">
-        <v>366.0718103345478</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3057.675703850157</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>5.641388053161204e-06</v>
@@ -2500,7 +2425,7 @@
         <v>128.455</v>
       </c>
       <c r="C2" t="n">
-        <v>1908.260990529206</v>
+        <v>309.090945875449</v>
       </c>
       <c r="D2" t="n">
         <v>1.31411e-07</v>
@@ -2533,16 +2458,13 @@
         <v>-12123.84202056224</v>
       </c>
       <c r="Y2" t="n">
-        <v>460.6238995794369</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1006766927.235635</v>
+        <v>218.5960779723586</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.774403400401903e-07</v>
+        <v>2.506183856205819e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9537545230038583</v>
+        <v>0.9904481954231168</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2475,7 @@
         <v>111.482</v>
       </c>
       <c r="C3" t="n">
-        <v>1141.811360119688</v>
+        <v>111.482</v>
       </c>
       <c r="D3" t="n">
         <v>1.29962e-07</v>
@@ -2585,11 +2507,10 @@
       <c r="X3" t="n">
         <v>-14481.42614730383</v>
       </c>
-      <c r="Y3" t="n">
-        <v>450.2200509822064</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>184198450.6248948</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.664567588103265e-07</v>
@@ -2606,7 +2527,7 @@
         <v>105.075</v>
       </c>
       <c r="C4" t="n">
-        <v>1032.021289282736</v>
+        <v>105.075</v>
       </c>
       <c r="D4" t="n">
         <v>1.29233e-07</v>
@@ -2638,11 +2559,10 @@
       <c r="X4" t="n">
         <v>-15304.82075703165</v>
       </c>
-      <c r="Y4" t="n">
-        <v>445.3684382892027</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>850327921.6281017</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.625654406343331e-07</v>
@@ -2659,7 +2579,7 @@
         <v>102.436</v>
       </c>
       <c r="C5" t="n">
-        <v>1074.053095067493</v>
+        <v>102.436</v>
       </c>
       <c r="D5" t="n">
         <v>1.28793e-07</v>
@@ -2691,11 +2611,10 @@
       <c r="X5" t="n">
         <v>-16064.31660664211</v>
       </c>
-      <c r="Y5" t="n">
-        <v>441.057126885874</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>721825974.9817973</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.603182105650482e-07</v>
@@ -2712,7 +2631,7 @@
         <v>97.84100000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1012.492127963182</v>
+        <v>267.5499114864695</v>
       </c>
       <c r="D6" t="n">
         <v>1.28431e-07</v>
@@ -2745,16 +2664,13 @@
         <v>-16013.82608106867</v>
       </c>
       <c r="Y6" t="n">
-        <v>381.922818856085</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14479.40661746183</v>
+        <v>247.2320461830803</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.834295378082544e-07</v>
+        <v>4.851636355764561e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9992569699770993</v>
+        <v>0.9649610830119966</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2681,7 @@
         <v>96.60300000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1008.735500400367</v>
+        <v>276.4563527064457</v>
       </c>
       <c r="D7" t="n">
         <v>1.28143e-07</v>
@@ -2798,16 +2714,13 @@
         <v>-16357.28705731489</v>
       </c>
       <c r="Y7" t="n">
-        <v>385.6662286725656</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14336.89875579788</v>
+        <v>213.5683248966414</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.052840766674812e-07</v>
+        <v>2.470797542756943e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9984004369077244</v>
+        <v>0.9992737909397531</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2731,7 @@
         <v>95.69100000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>1195.40325980122</v>
+        <v>95.69100000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.27985e-07</v>
@@ -2850,11 +2763,10 @@
       <c r="X8" t="n">
         <v>-16865.19531556046</v>
       </c>
-      <c r="Y8" t="n">
-        <v>428.163097075322</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>23741318.15268247</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.561360683189014e-07</v>
@@ -2871,7 +2783,7 @@
         <v>92.08800000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1160.865717802625</v>
+        <v>92.08800000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.27862e-07</v>
@@ -2903,11 +2815,10 @@
       <c r="X9" t="n">
         <v>-16874.71697691734</v>
       </c>
-      <c r="Y9" t="n">
-        <v>424.128099526301</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29019382.78923294</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.55284447976298e-07</v>
@@ -2924,7 +2835,7 @@
         <v>90.72899999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>1227.721660610156</v>
+        <v>227.7078918635201</v>
       </c>
       <c r="D10" t="n">
         <v>1.27761e-07</v>
@@ -2957,10 +2868,7 @@
         <v>-17247.43865135637</v>
       </c>
       <c r="Y10" t="n">
-        <v>420.2519489761569</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>459212508.7763305</v>
+        <v>523.0434587157682</v>
       </c>
       <c r="AA10" t="n">
         <v>1.548064645108504e-07</v>
@@ -2977,7 +2885,7 @@
         <v>89.14699999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1156.201695695959</v>
+        <v>251.5490738405515</v>
       </c>
       <c r="D11" t="n">
         <v>1.2767e-07</v>
@@ -3010,16 +2918,13 @@
         <v>-17040.17357784339</v>
       </c>
       <c r="Y11" t="n">
-        <v>398.7846648972076</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6877.533398922906</v>
+        <v>213.4479109632603</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.954473502611596e-07</v>
+        <v>2.494282660667083e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9090186399210735</v>
+        <v>0.9995595965316134</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2935,7 @@
         <v>86.73400000000004</v>
       </c>
       <c r="C12" t="n">
-        <v>1232.905274456279</v>
+        <v>86.73400000000004</v>
       </c>
       <c r="D12" t="n">
         <v>1.27615e-07</v>
@@ -3062,11 +2967,10 @@
       <c r="X12" t="n">
         <v>-17120.1256064699</v>
       </c>
-      <c r="Y12" t="n">
-        <v>412.9498010680853</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>281094450.2318594</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>1.536621899455083e-07</v>
@@ -3083,7 +2987,7 @@
         <v>87.87199999999996</v>
       </c>
       <c r="C13" t="n">
-        <v>1460.598831866239</v>
+        <v>87.87199999999996</v>
       </c>
       <c r="D13" t="n">
         <v>1.27526e-07</v>
@@ -3115,11 +3019,10 @@
       <c r="X13" t="n">
         <v>-18003.73978618631</v>
       </c>
-      <c r="Y13" t="n">
-        <v>409.9714713688827</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7604.693690718798</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>7.586148895956666e-07</v>
@@ -3136,7 +3039,7 @@
         <v>85.00900000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>1356.21092116884</v>
+        <v>239.1248549653668</v>
       </c>
       <c r="D14" t="n">
         <v>1.27443e-07</v>
@@ -3169,16 +3072,13 @@
         <v>-17610.9871134212</v>
       </c>
       <c r="Y14" t="n">
-        <v>388.8352672729376</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3324.365182566327</v>
+        <v>227.3938993653259</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.882408580975925e-06</v>
+        <v>2.975471881381715e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7002968364637472</v>
+        <v>0.9999866947802626</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3089,7 @@
         <v>81.565</v>
       </c>
       <c r="C15" t="n">
-        <v>1182.097038330038</v>
+        <v>81.565</v>
       </c>
       <c r="D15" t="n">
         <v>1.27374e-07</v>
@@ -3221,11 +3121,10 @@
       <c r="X15" t="n">
         <v>-17208.48884818449</v>
       </c>
-      <c r="Y15" t="n">
-        <v>402.6533208395448</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>438452594.0219834</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>1.520169188990871e-07</v>
@@ -3242,7 +3141,7 @@
         <v>80.928</v>
       </c>
       <c r="C16" t="n">
-        <v>1249.14829636005</v>
+        <v>232.7146077793028</v>
       </c>
       <c r="D16" t="n">
         <v>1.27307e-07</v>
@@ -3275,16 +3174,13 @@
         <v>-17441.15762665463</v>
       </c>
       <c r="Y16" t="n">
-        <v>399.2866874166169</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>217826799.4182777</v>
+        <v>232.0383683266263</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.514899248952161e-07</v>
+        <v>3.496266441345273e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9730381413063854</v>
+        <v>0.9992220583353456</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3191,7 @@
         <v>78.68000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>1292.995816153867</v>
+        <v>230.0824630859932</v>
       </c>
       <c r="D17" t="n">
         <v>1.27252e-07</v>
@@ -3328,16 +3224,13 @@
         <v>-17243.04685903747</v>
       </c>
       <c r="Y17" t="n">
-        <v>387.4502664951513</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6098.363963348514</v>
+        <v>213.8263170288621</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.468984113764074e-06</v>
+        <v>2.868538484210145e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.775440283898572</v>
+        <v>0.9992800698387687</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3241,7 @@
         <v>79.79400000000004</v>
       </c>
       <c r="C18" t="n">
-        <v>1306.758203646116</v>
+        <v>79.79400000000004</v>
       </c>
       <c r="D18" t="n">
         <v>1.27191e-07</v>
@@ -3380,11 +3273,10 @@
       <c r="X18" t="n">
         <v>-17944.37131442848</v>
       </c>
-      <c r="Y18" t="n">
-        <v>385.231271717932</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5723.86169981358</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.079634136156786e-06</v>
@@ -3401,7 +3293,7 @@
         <v>78.06999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>1587.364579979923</v>
+        <v>225.2728379747509</v>
       </c>
       <c r="D19" t="n">
         <v>1.27144e-07</v>
@@ -3434,16 +3326,13 @@
         <v>-18135.46509163999</v>
       </c>
       <c r="Y19" t="n">
-        <v>389.4181073657846</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>126371123.298715</v>
+        <v>217.8833178602723</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.500804209514123e-07</v>
+        <v>3.014317417191389e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9742734114328043</v>
+        <v>0.9979532296584781</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3343,7 @@
         <v>76.40500000000003</v>
       </c>
       <c r="C20" t="n">
-        <v>1615.065107499896</v>
+        <v>226.6062768689688</v>
       </c>
       <c r="D20" t="n">
         <v>1.27113e-07</v>
@@ -3487,16 +3376,13 @@
         <v>-17958.52544821114</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.1429010916787</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>472492036.3502814</v>
+        <v>211.296924098891</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.498408751587341e-07</v>
+        <v>2.857972871790189e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9744883841235749</v>
+        <v>0.999552870680942</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3393,7 @@
         <v>74.73899999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1472.759252385429</v>
+        <v>74.73899999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.2708e-07</v>
@@ -3539,11 +3425,10 @@
       <c r="X21" t="n">
         <v>-17946.06409079452</v>
       </c>
-      <c r="Y21" t="n">
-        <v>382.9088097882289</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1040154274.107222</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.49375746343324e-07</v>
@@ -3560,7 +3445,7 @@
         <v>72.61700000000002</v>
       </c>
       <c r="C22" t="n">
-        <v>1552.585842567669</v>
+        <v>72.61700000000002</v>
       </c>
       <c r="D22" t="n">
         <v>1.27013e-07</v>
@@ -3592,11 +3477,10 @@
       <c r="X22" t="n">
         <v>-17744.21970502623</v>
       </c>
-      <c r="Y22" t="n">
-        <v>369.4545041984531</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3104.873026098478</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>4.502592419324417e-06</v>
@@ -3759,7 +3643,7 @@
         <v>130.234</v>
       </c>
       <c r="C2" t="n">
-        <v>2030.380010873487</v>
+        <v>492.2811540955083</v>
       </c>
       <c r="D2" t="n">
         <v>1.37996e-07</v>
@@ -3792,16 +3676,13 @@
         <v>-5808.302779513925</v>
       </c>
       <c r="Y2" t="n">
-        <v>433.3319892882081</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>702664727.5205411</v>
+        <v>0.195972326343027</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.255714864846592e-07</v>
+        <v>1.09149498252307e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9252792117604457</v>
+        <v>0.9875348917133651</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3693,7 @@
         <v>85.577</v>
       </c>
       <c r="C3" t="n">
-        <v>3445.383928418348</v>
+        <v>234.8483986639029</v>
       </c>
       <c r="D3" t="n">
         <v>1.39236e-07</v>
@@ -3845,16 +3726,13 @@
         <v>-6796.953724562959</v>
       </c>
       <c r="Y3" t="n">
-        <v>400.0097735964395</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>219781828.8455609</v>
+        <v>238.7307453422851</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01060832395525e-07</v>
+        <v>4.560917345551804e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9438294914318545</v>
+        <v>0.9809900783642836</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3743,7 @@
         <v>76.524</v>
       </c>
       <c r="C4" t="n">
-        <v>2050.609081365511</v>
+        <v>232.8792445915996</v>
       </c>
       <c r="D4" t="n">
         <v>1.37508e-07</v>
@@ -3898,16 +3776,13 @@
         <v>-8069.112609432689</v>
       </c>
       <c r="Y4" t="n">
-        <v>391.0170644581005</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>853377689.1218193</v>
+        <v>208.0564861196497</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.869888689413641e-07</v>
+        <v>2.684395215091432e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9528630097236869</v>
+        <v>0.9994109649278061</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3793,7 @@
         <v>73.04199999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>2785.41534179792</v>
+        <v>73.04199999999997</v>
       </c>
       <c r="D5" t="n">
         <v>1.35982e-07</v>
@@ -3950,11 +3825,10 @@
       <c r="X5" t="n">
         <v>-9173.939713338897</v>
       </c>
-      <c r="Y5" t="n">
-        <v>391.3346221138735</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10048.54031388172</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>3.899640745121579e-07</v>
@@ -3971,7 +3845,7 @@
         <v>67.81400000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1735.471983707592</v>
+        <v>67.81400000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.34835e-07</v>
@@ -4003,11 +3877,10 @@
       <c r="X6" t="n">
         <v>-9838.252048670225</v>
       </c>
-      <c r="Y6" t="n">
-        <v>381.2705759157993</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>103637606.8395346</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.728071967764566e-07</v>
@@ -4024,7 +3897,7 @@
         <v>68.13100000000003</v>
       </c>
       <c r="C7" t="n">
-        <v>6488.034504567761</v>
+        <v>68.13100000000003</v>
       </c>
       <c r="D7" t="n">
         <v>1.33972e-07</v>
@@ -4056,11 +3929,10 @@
       <c r="X7" t="n">
         <v>-10743.07042555574</v>
       </c>
-      <c r="Y7" t="n">
-        <v>366.6528996274645</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3081.494744177717</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.803486606084007e-06</v>
@@ -4077,7 +3949,7 @@
         <v>63.90199999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>3124.800378239937</v>
+        <v>63.90199999999999</v>
       </c>
       <c r="D8" t="n">
         <v>1.33379e-07</v>
@@ -4109,11 +3981,10 @@
       <c r="X8" t="n">
         <v>-11053.07098521811</v>
       </c>
-      <c r="Y8" t="n">
-        <v>363.6376069962431</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3043.814780033557</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.373673087624089e-06</v>
@@ -4130,7 +4001,7 @@
         <v>60.459</v>
       </c>
       <c r="C9" t="n">
-        <v>2165.777267477766</v>
+        <v>388.7748303033882</v>
       </c>
       <c r="D9" t="n">
         <v>1.32873e-07</v>
@@ -4163,16 +4034,13 @@
         <v>-11312.33455660986</v>
       </c>
       <c r="Y9" t="n">
-        <v>369.9873394758301</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9104.316546793854</v>
+        <v>27.72185781669272</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.947415348728371e-07</v>
+        <v>1.257772642469243e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9492814755227535</v>
+        <v>0.9999955845973827</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4051,7 @@
         <v>61.10899999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>8789.157046651355</v>
+        <v>61.10899999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.3251e-07</v>
@@ -4215,11 +4083,10 @@
       <c r="X10" t="n">
         <v>-11874.33313082993</v>
       </c>
-      <c r="Y10" t="n">
-        <v>358.0187008381943</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2969.661359649142</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>6.772476471591856e-06</v>
@@ -4236,7 +4103,7 @@
         <v>56.19099999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>2077.900725664247</v>
+        <v>388.7978229911109</v>
       </c>
       <c r="D11" t="n">
         <v>1.3222e-07</v>
@@ -4269,16 +4136,13 @@
         <v>-11736.96339846924</v>
       </c>
       <c r="Y11" t="n">
-        <v>360.5142991971231</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5922.624533486918</v>
+        <v>20.79965479585404</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.456784505355195e-06</v>
+        <v>1.307388778844133e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7586072186923243</v>
+        <v>0.9999546695617846</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4299,7 @@
         <v>113.145</v>
       </c>
       <c r="C2" t="n">
-        <v>1219.300204779536</v>
+        <v>357.0406866607453</v>
       </c>
       <c r="D2" t="n">
         <v>1.35036e-07</v>
@@ -4468,16 +4332,13 @@
         <v>-11058.03164845512</v>
       </c>
       <c r="Y2" t="n">
-        <v>428.2258639481237</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>18372.7964795937</v>
+        <v>138.7483403789973</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.708124901436907e-07</v>
+        <v>1.574338419642469e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9997735852864446</v>
+        <v>0.9992769428408949</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4349,7 @@
         <v>104.525</v>
       </c>
       <c r="C3" t="n">
-        <v>1064.446076648025</v>
+        <v>104.525</v>
       </c>
       <c r="D3" t="n">
         <v>1.33679e-07</v>
@@ -4520,11 +4381,10 @@
       <c r="X3" t="n">
         <v>-12887.85470734534</v>
       </c>
-      <c r="Y3" t="n">
-        <v>436.2390868813392</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>714857312.7649179</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.731094755667596e-07</v>
@@ -4541,7 +4401,7 @@
         <v>101.551</v>
       </c>
       <c r="C4" t="n">
-        <v>1110.308718057529</v>
+        <v>318.3698906999048</v>
       </c>
       <c r="D4" t="n">
         <v>1.32952e-07</v>
@@ -4574,16 +4434,13 @@
         <v>-14096.6253668565</v>
       </c>
       <c r="Y4" t="n">
-        <v>392.2418228770213</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14347.69680565677</v>
+        <v>169.3647104570704</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.853974146356537e-07</v>
+        <v>1.904823113376739e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9999894978399823</v>
+        <v>0.9997179709786372</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4451,7 @@
         <v>98.47399999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1070.902101066394</v>
+        <v>298.5523260551529</v>
       </c>
       <c r="D5" t="n">
         <v>1.32425e-07</v>
@@ -4627,16 +4484,13 @@
         <v>-14593.08078356724</v>
       </c>
       <c r="Y5" t="n">
-        <v>428.1113247978005</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>36588883.84992374</v>
+        <v>189.6561200663218</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.659933458259396e-07</v>
+        <v>2.267063419918336e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9650895641874155</v>
+        <v>0.9969319898238623</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4501,7 @@
         <v>96.40899999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>991.9698681954582</v>
+        <v>96.40899999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.32104e-07</v>
@@ -4679,11 +4533,10 @@
       <c r="X6" t="n">
         <v>-15346.34184152871</v>
       </c>
-      <c r="Y6" t="n">
-        <v>423.9579095881203</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>27559905.67447949</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.63809084954019e-07</v>
@@ -4700,7 +4553,7 @@
         <v>93.51799999999997</v>
       </c>
       <c r="C7" t="n">
-        <v>1185.173663089795</v>
+        <v>93.51799999999997</v>
       </c>
       <c r="D7" t="n">
         <v>1.31841e-07</v>
@@ -4732,11 +4585,10 @@
       <c r="X7" t="n">
         <v>-15431.40644278099</v>
       </c>
-      <c r="Y7" t="n">
-        <v>419.9025313780976</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>22813193.89138057</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.6255153529867e-07</v>
@@ -4753,7 +4605,7 @@
         <v>92.80500000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1216.51410693814</v>
+        <v>264.207426986884</v>
       </c>
       <c r="D8" t="n">
         <v>1.31663e-07</v>
@@ -4786,16 +4638,13 @@
         <v>-16062.70326834718</v>
       </c>
       <c r="Y8" t="n">
-        <v>400.5301560943147</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6874.129375918969</v>
+        <v>219.5398450126584</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.464919215754058e-07</v>
+        <v>3.775301442959909e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8680630262029891</v>
+        <v>0.9795553396058071</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4655,7 @@
         <v>90.05799999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1198.402847344292</v>
+        <v>262.6383216864274</v>
       </c>
       <c r="D9" t="n">
         <v>1.3149e-07</v>
@@ -4839,16 +4688,13 @@
         <v>-16030.59039215619</v>
       </c>
       <c r="Y9" t="n">
-        <v>412.4537415775835</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>901410856.1699787</v>
+        <v>206.9145829262023</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.605921673503404e-07</v>
+        <v>2.623853272567415e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9690636093497924</v>
+        <v>0.9992988041667972</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4705,7 @@
         <v>83.95999999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>1047.033273564958</v>
+        <v>261.9993710065137</v>
       </c>
       <c r="D10" t="n">
         <v>1.31353e-07</v>
@@ -4892,16 +4738,13 @@
         <v>-15278.70072850319</v>
       </c>
       <c r="Y10" t="n">
-        <v>390.4344537883035</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3351.606138140507</v>
+        <v>201.7827677252746</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.70935487095687e-06</v>
+        <v>2.61683885930695e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6719996310187298</v>
+        <v>0.9958587714030758</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4755,7 @@
         <v>85.44400000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1140.823173333995</v>
+        <v>264.4213758382353</v>
       </c>
       <c r="D11" t="n">
         <v>1.31225e-07</v>
@@ -4945,16 +4788,13 @@
         <v>-16101.64984084333</v>
       </c>
       <c r="Y11" t="n">
-        <v>388.2930548595324</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3322.798733853723</v>
+        <v>200.8568937967151</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.929434986793159e-06</v>
+        <v>2.632875497945146e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6988673094316408</v>
+        <v>0.9976457976696619</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4805,7 @@
         <v>83.76499999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1079.32323783227</v>
+        <v>241.7371284043806</v>
       </c>
       <c r="D12" t="n">
         <v>1.31102e-07</v>
@@ -4998,16 +4838,13 @@
         <v>-16319.70746934681</v>
       </c>
       <c r="Y12" t="n">
-        <v>402.5482859389144</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>219749421.0854972</v>
+        <v>214.7450050896306</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.582254998207532e-07</v>
+        <v>2.794818689721383e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.970889300678743</v>
+        <v>0.9980643042087907</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4855,7 @@
         <v>84.488</v>
       </c>
       <c r="C13" t="n">
-        <v>1145.375326485122</v>
+        <v>223.2465500139266</v>
       </c>
       <c r="D13" t="n">
         <v>1.30994e-07</v>
@@ -5051,10 +4888,7 @@
         <v>-16775.68393520089</v>
       </c>
       <c r="Y13" t="n">
-        <v>399.4362182370824</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>217884101.4122648</v>
+        <v>492.7288020040396</v>
       </c>
       <c r="AA13" t="n">
         <v>1.575533681273246e-07</v>
@@ -5071,7 +4905,7 @@
         <v>79.09700000000004</v>
       </c>
       <c r="C14" t="n">
-        <v>1139.184100029985</v>
+        <v>79.09700000000004</v>
       </c>
       <c r="D14" t="n">
         <v>1.30901e-07</v>
@@ -5103,11 +4937,10 @@
       <c r="X14" t="n">
         <v>-15978.47705867695</v>
       </c>
-      <c r="Y14" t="n">
-        <v>387.243572223659</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6087.355515252417</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>8.750494667108169e-07</v>
@@ -5124,7 +4957,7 @@
         <v>77.55600000000004</v>
       </c>
       <c r="C15" t="n">
-        <v>1114.08622816765</v>
+        <v>228.7526972579346</v>
       </c>
       <c r="D15" t="n">
         <v>1.30828e-07</v>
@@ -5157,16 +4990,13 @@
         <v>-15986.14978403234</v>
       </c>
       <c r="Y15" t="n">
-        <v>385.0033597714138</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5817.856239181757</v>
+        <v>212.8787575204846</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.269584952541309e-07</v>
+        <v>2.918715015026392e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8579401766700118</v>
+        <v>0.9989942531731318</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +5007,7 @@
         <v>77.27599999999995</v>
       </c>
       <c r="C16" t="n">
-        <v>1155.619075740245</v>
+        <v>226.7130750809242</v>
       </c>
       <c r="D16" t="n">
         <v>1.30739e-07</v>
@@ -5210,16 +5040,13 @@
         <v>-16410.35807759123</v>
       </c>
       <c r="Y16" t="n">
-        <v>390.1298533925001</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>424906154.8144028</v>
+        <v>227.6405702061418</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.559476524407433e-07</v>
+        <v>3.597525324439303e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9726902902154484</v>
+        <v>0.9991496440311213</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5057,7 @@
         <v>76.57900000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>1155.005186868228</v>
+        <v>224.3014833739286</v>
       </c>
       <c r="D17" t="n">
         <v>1.30682e-07</v>
@@ -5263,16 +5090,13 @@
         <v>-16628.03869600047</v>
       </c>
       <c r="Y17" t="n">
-        <v>387.0645065547251</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>527789415.7056388</v>
+        <v>209.8739459890468</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.554655332137557e-07</v>
+        <v>2.958447196195316e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9730985830748725</v>
+        <v>0.9992431696190411</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5107,7 @@
         <v>76.11499999999995</v>
       </c>
       <c r="C18" t="n">
-        <v>1348.199724793148</v>
+        <v>76.11499999999995</v>
       </c>
       <c r="D18" t="n">
         <v>1.30609e-07</v>
@@ -5315,11 +5139,10 @@
       <c r="X18" t="n">
         <v>-16898.86726804942</v>
       </c>
-      <c r="Y18" t="n">
-        <v>384.0055298146076</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>209938966.7393761</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.549660193808371e-07</v>
@@ -5336,7 +5159,7 @@
         <v>74.577</v>
       </c>
       <c r="C19" t="n">
-        <v>1253.286013960683</v>
+        <v>74.577</v>
       </c>
       <c r="D19" t="n">
         <v>1.30585e-07</v>
@@ -5368,11 +5191,10 @@
       <c r="X19" t="n">
         <v>-16834.99572961427</v>
       </c>
-      <c r="Y19" t="n">
-        <v>369.914785747864</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3117.64811257039</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>4.150379421065077e-06</v>
@@ -5389,7 +5211,7 @@
         <v>73.88200000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>1351.5918730016</v>
+        <v>73.88200000000001</v>
       </c>
       <c r="D20" t="n">
         <v>1.30541e-07</v>
@@ -5421,11 +5243,10 @@
       <c r="X20" t="n">
         <v>-17014.7453676991</v>
       </c>
-      <c r="Y20" t="n">
-        <v>367.7615643634669</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3092.98069709524</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>4.719243108953146e-06</v>
@@ -5442,7 +5263,7 @@
         <v>68.15800000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>1350.186345133656</v>
+        <v>219.1383865423527</v>
       </c>
       <c r="D21" t="n">
         <v>1.30485e-07</v>
@@ -5475,16 +5296,13 @@
         <v>-15826.61462063316</v>
       </c>
       <c r="Y21" t="n">
-        <v>365.6442421361662</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3065.105472682255</v>
+        <v>211.0848938209815</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.50856728064152e-06</v>
+        <v>3.138904427055603e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.6589229649273686</v>
+        <v>0.9999888794924949</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5313,7 @@
         <v>73.74900000000002</v>
       </c>
       <c r="C22" t="n">
-        <v>1454.142843256388</v>
+        <v>216.6645480753944</v>
       </c>
       <c r="D22" t="n">
         <v>1.30452e-07</v>
@@ -5528,16 +5346,13 @@
         <v>-17783.62994468227</v>
       </c>
       <c r="Y22" t="n">
-        <v>363.5401248831968</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3041.305824953865</v>
+        <v>210.9395793547784</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.226150934124446e-06</v>
+        <v>3.327877936435559e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.6244279840078788</v>
+        <v>0.9997574737254421</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5509,7 @@
         <v>124.007</v>
       </c>
       <c r="C2" t="n">
-        <v>2011.612443724747</v>
+        <v>377.1986485961716</v>
       </c>
       <c r="D2" t="n">
         <v>1.42364e-07</v>
@@ -5727,16 +5542,13 @@
         <v>-5264.72458753714</v>
       </c>
       <c r="Y2" t="n">
-        <v>430.7569450103838</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>233728674.5132036</v>
+        <v>106.1328657442626</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.415788474583415e-07</v>
+        <v>1.288734449132212e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9197166466712509</v>
+        <v>0.9989342332759684</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5559,7 @@
         <v>83.63200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>3495.85189406501</v>
+        <v>234.7414298331167</v>
       </c>
       <c r="D3" t="n">
         <v>1.42039e-07</v>
@@ -5780,16 +5592,13 @@
         <v>-6368.238706289995</v>
       </c>
       <c r="Y3" t="n">
-        <v>403.081108882269</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>26865526.29293975</v>
+        <v>227.0477299226874</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.09475894374022e-07</v>
+        <v>3.089800078248353e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9406702993587325</v>
+        <v>0.9978623643395942</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5609,7 @@
         <v>79.17600000000004</v>
       </c>
       <c r="C4" t="n">
-        <v>2033.903716206219</v>
+        <v>238.7608751817361</v>
       </c>
       <c r="D4" t="n">
         <v>1.39813e-07</v>
@@ -5833,16 +5642,13 @@
         <v>-7917.759453026883</v>
       </c>
       <c r="Y4" t="n">
-        <v>395.4896485780671</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>216046876.3848027</v>
+        <v>206.9449467062814</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.927812295393479e-07</v>
+        <v>2.6287256339928e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9507651565317236</v>
+        <v>0.9994832596885793</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5659,7 @@
         <v>72.18000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>2168.67188992175</v>
+        <v>233.5702075834454</v>
       </c>
       <c r="D5" t="n">
         <v>1.37992e-07</v>
@@ -5886,16 +5692,13 @@
         <v>-8929.433037612014</v>
       </c>
       <c r="Y5" t="n">
-        <v>396.1013078597147</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9899.950515235945</v>
+        <v>212.6941255730871</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.690383414507065e-07</v>
+        <v>2.929332133305095e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9979303241153106</v>
+        <v>0.9986058894156015</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5709,7 @@
         <v>70.00899999999996</v>
       </c>
       <c r="C6" t="n">
-        <v>2084.806536333833</v>
+        <v>328.8894945728115</v>
       </c>
       <c r="D6" t="n">
         <v>1.36703e-07</v>
@@ -5939,16 +5742,13 @@
         <v>-9911.451398944964</v>
       </c>
       <c r="Y6" t="n">
-        <v>386.7729435961884</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>947233320.0759394</v>
+        <v>111.9193884551673</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.763108932738833e-07</v>
+        <v>1.912842229381056e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9608585626297973</v>
+        <v>0.992063009943382</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5759,7 @@
         <v>65.73400000000004</v>
       </c>
       <c r="C7" t="n">
-        <v>1796.265174325102</v>
+        <v>327.1044915943984</v>
       </c>
       <c r="D7" t="n">
         <v>1.3576e-07</v>
@@ -5992,16 +5792,13 @@
         <v>-10457.32644871787</v>
       </c>
       <c r="Y7" t="n">
-        <v>382.5174943840916</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>209577946.5805859</v>
+        <v>107.6448616650236</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.720373641015596e-07</v>
+        <v>1.752909804369162e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9635320430160704</v>
+        <v>0.9964524197215489</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5809,7 @@
         <v>65.70699999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>3086.262510982587</v>
+        <v>315.0342460614964</v>
       </c>
       <c r="D8" t="n">
         <v>1.35109e-07</v>
@@ -6045,16 +5842,13 @@
         <v>-11245.43405165313</v>
       </c>
       <c r="Y8" t="n">
-        <v>368.5942465753271</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3091.854779228136</v>
+        <v>114.5326330015931</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.253836186046018e-06</v>
+        <v>1.798702133260367e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6884210375358281</v>
+        <v>0.9983456045523751</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5859,7 @@
         <v>59.49400000000003</v>
       </c>
       <c r="C9" t="n">
-        <v>3897.388047761029</v>
+        <v>388.3644729518133</v>
       </c>
       <c r="D9" t="n">
         <v>1.34609e-07</v>
@@ -6098,16 +5892,13 @@
         <v>-11125.36763713648</v>
       </c>
       <c r="Y9" t="n">
-        <v>365.5545231100253</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3055.342962976627</v>
+        <v>33.81805713029578</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.187563762829413e-06</v>
+        <v>1.26060767062711e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6659380877268782</v>
+        <v>0.9999898475104083</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5909,7 @@
         <v>60.26400000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>3487.529652362728</v>
+        <v>285.7224593983365</v>
       </c>
       <c r="D10" t="n">
         <v>1.3425e-07</v>
@@ -6151,16 +5942,13 @@
         <v>-11897.30801714758</v>
       </c>
       <c r="Y10" t="n">
-        <v>362.7931590103153</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3019.408839757034</v>
+        <v>134.0890254746868</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.576046445387152e-06</v>
+        <v>2.004135561621898e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6345541794673513</v>
+        <v>0.9998882337304682</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5959,7 @@
         <v>60.077</v>
       </c>
       <c r="C11" t="n">
-        <v>5828.930850222042</v>
+        <v>60.077</v>
       </c>
       <c r="D11" t="n">
         <v>1.33984e-07</v>
@@ -6203,11 +5991,10 @@
       <c r="X11" t="n">
         <v>-12434.17226967321</v>
       </c>
-      <c r="Y11" t="n">
-        <v>360.276349917771</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2987.28400260335</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>6.804308553158765e-06</v>
@@ -6370,7 +6157,7 @@
         <v>120.405</v>
       </c>
       <c r="C2" t="n">
-        <v>1511.883306060246</v>
+        <v>297.8238852640771</v>
       </c>
       <c r="D2" t="n">
         <v>1.4003e-07</v>
@@ -6403,16 +6190,13 @@
         <v>-8686.133135867789</v>
       </c>
       <c r="Y2" t="n">
-        <v>452.35668962881</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>247438428.0794368</v>
+        <v>210.9188048562233</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.035226843614756e-07</v>
+        <v>2.137940533595913e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9426902992629592</v>
+        <v>0.9989564695668066</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6207,7 @@
         <v>106.272</v>
       </c>
       <c r="C3" t="n">
-        <v>1111.215722597798</v>
+        <v>106.272</v>
       </c>
       <c r="D3" t="n">
         <v>1.36711e-07</v>
@@ -6455,11 +6239,10 @@
       <c r="X3" t="n">
         <v>-11896.57602459269</v>
       </c>
-      <c r="Y3" t="n">
-        <v>441.236970068914</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>125079789.1509634</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.809083805034442e-07</v>
@@ -6476,7 +6259,7 @@
         <v>100.224</v>
       </c>
       <c r="C4" t="n">
-        <v>1044.551409053521</v>
+        <v>328.9782540854742</v>
       </c>
       <c r="D4" t="n">
         <v>1.35447e-07</v>
@@ -6509,16 +6292,13 @@
         <v>-13325.24316002457</v>
       </c>
       <c r="Y4" t="n">
-        <v>436.0491753386115</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>387987452.8781702</v>
+        <v>159.2647027131401</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.738985204231838e-07</v>
+        <v>1.788007909662091e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9614436847749341</v>
+        <v>0.9992668464618244</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6309,7 @@
         <v>99.923</v>
       </c>
       <c r="C5" t="n">
-        <v>964.896273246979</v>
+        <v>99.923</v>
       </c>
       <c r="D5" t="n">
         <v>1.34813e-07</v>
@@ -6561,11 +6341,10 @@
       <c r="X5" t="n">
         <v>-14629.67131829655</v>
       </c>
-      <c r="Y5" t="n">
-        <v>431.8986589084778</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>31910299.39771348</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.700756659347028e-07</v>
@@ -6582,7 +6361,7 @@
         <v>91.04399999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>942.9364327278213</v>
+        <v>255.6927370205997</v>
       </c>
       <c r="D6" t="n">
         <v>1.34414e-07</v>
@@ -6615,16 +6394,13 @@
         <v>-14209.24727128199</v>
       </c>
       <c r="Y6" t="n">
-        <v>428.0160598089331</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>467629884.2441313</v>
+        <v>261.956667704895</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68002551100011e-07</v>
+        <v>9.214600821194664e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9655398689829168</v>
+        <v>0.9314323137555558</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6411,7 @@
         <v>85.00900000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>956.5271380866474</v>
+        <v>253.4126847116963</v>
       </c>
       <c r="D7" t="n">
         <v>1.34128e-07</v>
@@ -6668,16 +6444,13 @@
         <v>-13763.94748817758</v>
       </c>
       <c r="Y7" t="n">
-        <v>424.1785264245281</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>125545190.288765</v>
+        <v>229.1941463381632</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66198345384196e-07</v>
+        <v>2.904651164328515e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9668629723079419</v>
+        <v>0.9978693777275013</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6461,7 @@
         <v>91.34000000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>1196.886266794471</v>
+        <v>251.4777773657543</v>
       </c>
       <c r="D8" t="n">
         <v>1.33927e-07</v>
@@ -6721,16 +6494,13 @@
         <v>-15682.86009572078</v>
       </c>
       <c r="Y8" t="n">
-        <v>413.3510388804626</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>15685.6440730381</v>
+        <v>231.2689585296854</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77094109916298e-07</v>
+        <v>2.888079588338673e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9999999860989168</v>
+        <v>0.9998167654147081</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6511,7 @@
         <v>88.19399999999996</v>
       </c>
       <c r="C9" t="n">
-        <v>1190.220921449024</v>
+        <v>302.4900543516959</v>
       </c>
       <c r="D9" t="n">
         <v>1.33729e-07</v>
@@ -6774,16 +6544,13 @@
         <v>-15651.29473670315</v>
       </c>
       <c r="Y9" t="n">
-        <v>416.7702582982151</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>909589822.4757632</v>
+        <v>165.9119004196483</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.639971929839753e-07</v>
+        <v>1.958808534387946e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.968447875621587</v>
+        <v>0.9998292123906046</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6561,7 @@
         <v>86.22899999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>1128.509710844802</v>
+        <v>260.5354111560781</v>
       </c>
       <c r="D10" t="n">
         <v>1.33595e-07</v>
@@ -6827,16 +6594,13 @@
         <v>-15764.34154710978</v>
       </c>
       <c r="Y10" t="n">
-        <v>412.4253798300946</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7686.457886692357</v>
+        <v>221.6729228584302</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.662815190856792e-07</v>
+        <v>3.946225521568107e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8534223755056346</v>
+        <v>0.9768257594433111</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6611,7 @@
         <v>84.887</v>
       </c>
       <c r="C11" t="n">
-        <v>1142.898646326923</v>
+        <v>258.312394349725</v>
       </c>
       <c r="D11" t="n">
         <v>1.33485e-07</v>
@@ -6880,16 +6644,13 @@
         <v>-15934.39619045957</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.1903711043747</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3362.49531787377</v>
+        <v>208.6414680434051</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.561791301832183e-06</v>
+        <v>2.671600186441002e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7126031676005499</v>
+        <v>0.9981138690219217</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6661,7 @@
         <v>84.24399999999997</v>
       </c>
       <c r="C12" t="n">
-        <v>1247.375020500277</v>
+        <v>258.0487266149413</v>
       </c>
       <c r="D12" t="n">
         <v>1.33389e-07</v>
@@ -6933,16 +6694,13 @@
         <v>-16252.51595046164</v>
       </c>
       <c r="Y12" t="n">
-        <v>406.5696251295084</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7562.536343381692</v>
+        <v>202.2520148290152</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.033533860087458e-06</v>
+        <v>2.647463922517598e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8329837228778508</v>
+        <v>0.9960123890533075</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6711,7 @@
         <v>80.80599999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>1075.41726769733</v>
+        <v>80.80599999999998</v>
       </c>
       <c r="D13" t="n">
         <v>1.33293e-07</v>
@@ -6985,11 +6743,10 @@
       <c r="X13" t="n">
         <v>-16028.72150931268</v>
       </c>
-      <c r="Y13" t="n">
-        <v>403.8964437003165</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>220028077.1227835</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>1.609640843267215e-07</v>
@@ -7006,7 +6763,7 @@
         <v>80.16300000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>1057.674916194222</v>
+        <v>238.4628540344122</v>
       </c>
       <c r="D14" t="n">
         <v>1.33203e-07</v>
@@ -7039,16 +6796,13 @@
         <v>-16130.07587172526</v>
       </c>
       <c r="Y14" t="n">
-        <v>391.4139537918428</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6274.182893957601</v>
+        <v>215.0631429778591</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.838704087528576e-07</v>
+        <v>2.82062949476141e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8185845910639955</v>
+        <v>0.9981107744170539</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6813,7 @@
         <v>72.80300000000005</v>
       </c>
       <c r="C15" t="n">
-        <v>1073.914181366701</v>
+        <v>236.8293467416155</v>
       </c>
       <c r="D15" t="n">
         <v>1.33143e-07</v>
@@ -7092,16 +6846,13 @@
         <v>-14594.95151907926</v>
       </c>
       <c r="Y15" t="n">
-        <v>397.9808730092059</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>216786082.4330912</v>
+        <v>214.5494407783958</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.59908970498482e-07</v>
+        <v>2.927738991316743e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9716433820751113</v>
+        <v>0.9980667775757276</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6863,7 @@
         <v>79.13499999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1344.542937852518</v>
+        <v>229.4587798558131</v>
       </c>
       <c r="D16" t="n">
         <v>1.33054e-07</v>
@@ -7145,16 +6896,13 @@
         <v>-16806.83966202478</v>
       </c>
       <c r="Y16" t="n">
-        <v>386.1011873896881</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6152.843472120463</v>
+        <v>227.4093860881763</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.338106733968226e-06</v>
+        <v>3.320689123665889e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.7868989511233535</v>
+        <v>0.999897587602508</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6913,7 @@
         <v>77.017</v>
       </c>
       <c r="C17" t="n">
-        <v>1243.196112514063</v>
+        <v>227.0090815361379</v>
       </c>
       <c r="D17" t="n">
         <v>1.33038e-07</v>
@@ -7198,16 +6946,13 @@
         <v>-16665.98065748631</v>
       </c>
       <c r="Y17" t="n">
-        <v>392.1617665167183</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>108141571.6773528</v>
+        <v>225.2666992763086</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.588498537872321e-07</v>
+        <v>3.316986974632975e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9725387417697915</v>
+        <v>0.999791324536471</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6963,7 @@
         <v>78.03199999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>1180.872582257425</v>
+        <v>78.03199999999998</v>
       </c>
       <c r="D18" t="n">
         <v>1.32974e-07</v>
@@ -7250,11 +6995,10 @@
       <c r="X18" t="n">
         <v>-17201.66456970658</v>
       </c>
-      <c r="Y18" t="n">
-        <v>389.2228096335514</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>423823252.9383525</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.583740140481801e-07</v>
@@ -7271,7 +7015,7 @@
         <v>74.76599999999996</v>
       </c>
       <c r="C19" t="n">
-        <v>1321.017014404334</v>
+        <v>221.4349311421819</v>
       </c>
       <c r="D19" t="n">
         <v>1.32936e-07</v>
@@ -7304,16 +7048,13 @@
         <v>-16648.47850029673</v>
       </c>
       <c r="Y19" t="n">
-        <v>386.3321753760547</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>421642121.2288289</v>
+        <v>221.6101910815641</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.579302543440558e-07</v>
+        <v>3.493212044199326e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9733164792989136</v>
+        <v>0.9949017958490781</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7065,7 @@
         <v>81.35699999999997</v>
       </c>
       <c r="C20" t="n">
-        <v>1380.415501785433</v>
+        <v>219.3363077886187</v>
       </c>
       <c r="D20" t="n">
         <v>1.32884e-07</v>
@@ -7357,16 +7098,13 @@
         <v>-19179.41293714672</v>
       </c>
       <c r="Y20" t="n">
-        <v>372.524350903414</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3137.765914510968</v>
+        <v>218.8533017712282</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.80558198294671e-06</v>
+        <v>3.373145847949433e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.6814004971198239</v>
+        <v>0.9961888146378377</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7115,7 @@
         <v>67.51500000000004</v>
       </c>
       <c r="C21" t="n">
-        <v>1234.261565383726</v>
+        <v>67.51500000000004</v>
       </c>
       <c r="D21" t="n">
         <v>1.32834e-07</v>
@@ -7409,11 +7147,10 @@
       <c r="X21" t="n">
         <v>-15400.26373223274</v>
       </c>
-      <c r="Y21" t="n">
-        <v>370.3841944268697</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3110.482970582952</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>5.060048837761327e-06</v>
@@ -7430,7 +7167,7 @@
         <v>76.25200000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1447.475565144302</v>
+        <v>218.4613710634203</v>
       </c>
       <c r="D22" t="n">
         <v>1.32818e-07</v>
@@ -7463,16 +7200,13 @@
         <v>-18393.18569421029</v>
       </c>
       <c r="Y22" t="n">
-        <v>368.3066786447217</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3088.221134289601</v>
+        <v>221.0792775782005</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.946012337124171e-06</v>
+        <v>3.514208323216027e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.6733042551582672</v>
+        <v>0.9995503755085474</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7363,7 @@
         <v>134.256</v>
       </c>
       <c r="C2" t="n">
-        <v>1357.332671937825</v>
+        <v>344.8271343059443</v>
       </c>
       <c r="D2" t="n">
         <v>1.45121e-07</v>
@@ -7662,16 +7396,13 @@
         <v>-5250.953486006958</v>
       </c>
       <c r="Y2" t="n">
-        <v>428.2332462765251</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>176854762.310507</v>
+        <v>139.4489923581032</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.503146688684804e-07</v>
+        <v>1.539987100596939e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9172624204141567</v>
+        <v>0.9973872035437737</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7413,7 @@
         <v>82.05099999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>2576.242322725203</v>
+        <v>232.140385195269</v>
       </c>
       <c r="D3" t="n">
         <v>1.44345e-07</v>
@@ -7715,16 +7446,13 @@
         <v>-6428.417618295207</v>
       </c>
       <c r="Y3" t="n">
-        <v>378.5659046197014</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3251.976403630118</v>
+        <v>217.9219797836351</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.638314156025119e-06</v>
+        <v>2.793305124279454e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7310016366530891</v>
+        <v>0.9994717118838898</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7463,7 @@
         <v>72.76100000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>1729.448086621572</v>
+        <v>230.9881618802109</v>
       </c>
       <c r="D4" t="n">
         <v>1.41798e-07</v>
@@ -7768,16 +7496,13 @@
         <v>-7975.320502822983</v>
       </c>
       <c r="Y4" t="n">
-        <v>387.4135014371778</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5878.512002361233</v>
+        <v>206.8508987825704</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.027754898540164e-07</v>
+        <v>2.731651690589102e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9368114480869567</v>
+        <v>0.9993183421428584</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7513,7 @@
         <v>69.72300000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1557.670874235105</v>
+        <v>69.72300000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.39885e-07</v>
@@ -7820,11 +7545,10 @@
       <c r="X5" t="n">
         <v>-9362.084669412065</v>
       </c>
-      <c r="Y5" t="n">
-        <v>383.8299045016033</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>419254175.9051671</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.82381194019089e-07</v>
@@ -7841,7 +7565,7 @@
         <v>69.18100000000004</v>
       </c>
       <c r="C6" t="n">
-        <v>2728.311317800298</v>
+        <v>69.18100000000004</v>
       </c>
       <c r="D6" t="n">
         <v>1.38618e-07</v>
@@ -7873,11 +7597,10 @@
       <c r="X6" t="n">
         <v>-10601.21969535638</v>
       </c>
-      <c r="Y6" t="n">
-        <v>368.8728782930354</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3105.746169602751</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>3.379624438924234e-06</v>
@@ -7894,7 +7617,7 @@
         <v>70.18599999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>2699.881846719973</v>
+        <v>70.18599999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.37709e-07</v>
@@ -7926,11 +7649,10 @@
       <c r="X7" t="n">
         <v>-11797.63606719903</v>
       </c>
-      <c r="Y7" t="n">
-        <v>366.1889323686365</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3069.469555446921</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>4.354806899301846e-06</v>
@@ -7947,7 +7669,7 @@
         <v>63.12099999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>2191.806692688222</v>
+        <v>224.1837446285852</v>
       </c>
       <c r="D8" t="n">
         <v>1.37161e-07</v>
@@ -7980,16 +7702,13 @@
         <v>-11910.99916511957</v>
       </c>
       <c r="Y8" t="n">
-        <v>363.3927720476658</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3029.728417792315</v>
+        <v>198.7960623224378</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.595083832219959e-06</v>
+        <v>2.993754075627584e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6335036539685892</v>
+        <v>0.9983403714535143</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7719,7 @@
         <v>60.96899999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>2997.566226451623</v>
+        <v>60.96899999999999</v>
       </c>
       <c r="D9" t="n">
         <v>1.36684e-07</v>
@@ -8032,11 +7751,10 @@
       <c r="X9" t="n">
         <v>-12423.38149510681</v>
       </c>
-      <c r="Y9" t="n">
-        <v>365.6700232995036</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4894.766165784499</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.110762989935804e-06</v>
@@ -8053,7 +7771,7 @@
         <v>60.221</v>
       </c>
       <c r="C10" t="n">
-        <v>5984.979771433238</v>
+        <v>314.6530164753547</v>
       </c>
       <c r="D10" t="n">
         <v>1.36418e-07</v>
@@ -8086,16 +7804,13 @@
         <v>-12879.70078544074</v>
       </c>
       <c r="Y10" t="n">
-        <v>362.3122293056554</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>393741041.4451929</v>
+        <v>95.95032025661813</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.648926069873349e-07</v>
+        <v>1.790583607794887e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9707232710836597</v>
+        <v>0.9981518068203472</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7821,7 @@
         <v>58.30099999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>7700.796048501948</v>
+        <v>368.8360063945358</v>
       </c>
       <c r="D11" t="n">
         <v>1.36178e-07</v>
@@ -8139,16 +7854,13 @@
         <v>-13285.89821834282</v>
       </c>
       <c r="Y11" t="n">
-        <v>358.4391175287689</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>33422879.31864697</v>
+        <v>38.7085527339773</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.632150073337587e-07</v>
+        <v>1.385040067397342e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.972014366512766</v>
+        <v>0.9994294686443047</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +8017,7 @@
         <v>112.704</v>
       </c>
       <c r="C2" t="n">
-        <v>1193.055211275207</v>
+        <v>305.5525883610767</v>
       </c>
       <c r="D2" t="n">
         <v>1.43565e-07</v>
@@ -8338,16 +8050,13 @@
         <v>-8593.638004325428</v>
       </c>
       <c r="Y2" t="n">
-        <v>445.7947041603194</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>244050227.6888387</v>
+        <v>195.4399967472757</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.071748836608976e-07</v>
+        <v>2.019746967994297e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9437716666932277</v>
+        <v>0.9993308831626059</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8067,7 @@
         <v>106.277</v>
       </c>
       <c r="C3" t="n">
-        <v>961.4522379248406</v>
+        <v>304.3795159934789</v>
       </c>
       <c r="D3" t="n">
         <v>1.40363e-07</v>
@@ -8391,16 +8100,13 @@
         <v>-11840.64945193359</v>
       </c>
       <c r="Y3" t="n">
-        <v>436.9700326005391</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>341020120.6648586</v>
+        <v>194.4807704208527</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.865560298812348e-07</v>
+        <v>2.293231818435695e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9561961947193215</v>
+        <v>0.9967529726200738</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8117,7 @@
         <v>98.12400000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>985.494511659311</v>
+        <v>323.5425752078182</v>
       </c>
       <c r="D4" t="n">
         <v>1.39069e-07</v>
@@ -8444,16 +8150,13 @@
         <v>-13041.57198786413</v>
       </c>
       <c r="Y4" t="n">
-        <v>432.5868409983169</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>27750175.75858851</v>
+        <v>167.2624660435847</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.787540813147449e-07</v>
+        <v>1.95848250005153e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9612695288223025</v>
+        <v>0.9999064126906103</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8167,7 @@
         <v>96.012</v>
       </c>
       <c r="C5" t="n">
-        <v>1002.10624829965</v>
+        <v>309.0067075072034</v>
       </c>
       <c r="D5" t="n">
         <v>1.38452e-07</v>
@@ -8497,16 +8200,13 @@
         <v>-13975.83191713709</v>
       </c>
       <c r="Y5" t="n">
-        <v>428.6187214448487</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>234348620.6758281</v>
+        <v>169.2277603018833</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.752994282087224e-07</v>
+        <v>1.877728632504746e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9635642570370346</v>
+        <v>0.9998947746202564</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8217,7 @@
         <v>89.96599999999995</v>
       </c>
       <c r="C6" t="n">
-        <v>943.4716840086022</v>
+        <v>285.7065359113026</v>
       </c>
       <c r="D6" t="n">
         <v>1.38064e-07</v>
@@ -8550,16 +8250,13 @@
         <v>-13808.29235260107</v>
       </c>
       <c r="Y6" t="n">
-        <v>424.5595634917665</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>128756446.3089024</v>
+        <v>189.9863980247889</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.729583716904129e-07</v>
+        <v>2.159766810531195e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9651903461022434</v>
+        <v>0.999806608893253</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8267,7 @@
         <v>94.36799999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>957.796178747469</v>
+        <v>247.7761895840785</v>
       </c>
       <c r="D7" t="n">
         <v>1.37826e-07</v>
@@ -8603,16 +8300,13 @@
         <v>-15532.44254583502</v>
       </c>
       <c r="Y7" t="n">
-        <v>420.4315652067328</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>118615617.0548192</v>
+        <v>223.9977339649027</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.712206307714624e-07</v>
+        <v>2.696735453574901e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9664686563307822</v>
+        <v>0.9991417372695413</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8317,7 @@
         <v>88.21200000000005</v>
       </c>
       <c r="C8" t="n">
-        <v>961.9155868322862</v>
+        <v>88.21200000000005</v>
       </c>
       <c r="D8" t="n">
         <v>1.37642e-07</v>
@@ -8655,11 +8349,10 @@
       <c r="X8" t="n">
         <v>-15019.59746420028</v>
       </c>
-      <c r="Y8" t="n">
-        <v>416.3770116231983</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>454588972.0921235</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.699571050475663e-07</v>
@@ -8676,7 +8369,7 @@
         <v>86.52100000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1001.090225451148</v>
+        <v>86.52100000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.37501e-07</v>
@@ -8708,11 +8401,10 @@
       <c r="X9" t="n">
         <v>-15295.7998640503</v>
       </c>
-      <c r="Y9" t="n">
-        <v>393.7922482824788</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3380.332953377035</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>3.299760744514844e-06</v>
@@ -8729,7 +8421,7 @@
         <v>84.55599999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>993.1428419713969</v>
+        <v>244.133329412032</v>
       </c>
       <c r="D10" t="n">
         <v>1.37379e-07</v>
@@ -8762,16 +8454,13 @@
         <v>-15496.52076257386</v>
       </c>
       <c r="Y10" t="n">
-        <v>393.3558551742232</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3350.947418589739</v>
+        <v>225.0475612431466</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.133772204584533e-06</v>
+        <v>2.952358883584935e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7969682207860459</v>
+        <v>0.9998366309771888</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8471,7 @@
         <v>85.34500000000003</v>
       </c>
       <c r="C11" t="n">
-        <v>1014.198733875123</v>
+        <v>241.5502183797672</v>
       </c>
       <c r="D11" t="n">
         <v>1.37277e-07</v>
@@ -8815,16 +8504,13 @@
         <v>-16136.33295058607</v>
       </c>
       <c r="Y11" t="n">
-        <v>405.6987242050351</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>223496760.40505</v>
+        <v>219.594437726525</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.671143237273648e-07</v>
+        <v>3.107345193227281e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9695690665259259</v>
+        <v>0.9961586536350435</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8521,7 @@
         <v>77.20300000000003</v>
       </c>
       <c r="C12" t="n">
-        <v>1010.515173696825</v>
+        <v>253.0569208937246</v>
       </c>
       <c r="D12" t="n">
         <v>1.37214e-07</v>
@@ -8868,16 +8554,13 @@
         <v>-14647.01905829087</v>
       </c>
       <c r="Y12" t="n">
-        <v>406.6718598625063</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>10426.34676195086</v>
+        <v>213.6637292518529</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.626741760332304e-07</v>
+        <v>3.937269341668482e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9983495940900967</v>
+        <v>0.9800345757141827</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8571,7 @@
         <v>80.02299999999997</v>
       </c>
       <c r="C13" t="n">
-        <v>1043.592620797343</v>
+        <v>80.02299999999997</v>
       </c>
       <c r="D13" t="n">
         <v>1.37122e-07</v>
@@ -8920,11 +8603,10 @@
       <c r="X13" t="n">
         <v>-15797.92056487545</v>
       </c>
-      <c r="Y13" t="n">
-        <v>399.4162991703378</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>123994034.9297559</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>1.657267705748101e-07</v>
@@ -8941,7 +8623,7 @@
         <v>75.322</v>
       </c>
       <c r="C14" t="n">
-        <v>1035.771274177843</v>
+        <v>75.322</v>
       </c>
       <c r="D14" t="n">
         <v>1.3706e-07</v>
@@ -8973,11 +8655,10 @@
       <c r="X14" t="n">
         <v>-15094.6284375091</v>
       </c>
-      <c r="Y14" t="n">
-        <v>400.2324335157696</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>10470.88867216568</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.269943740968406e-07</v>
@@ -8994,7 +8675,7 @@
         <v>78.28199999999998</v>
       </c>
       <c r="C15" t="n">
-        <v>1147.580437365002</v>
+        <v>252.3961907310332</v>
       </c>
       <c r="D15" t="n">
         <v>1.36985e-07</v>
@@ -9027,16 +8708,13 @@
         <v>-16328.45434062075</v>
       </c>
       <c r="Y15" t="n">
-        <v>393.4107771894506</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>107723215.7499345</v>
+        <v>191.3585133297507</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.645584611816782e-07</v>
+        <v>2.498527913586906e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9716049016418253</v>
+        <v>0.9999035199301276</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8725,7 @@
         <v>76.464</v>
       </c>
       <c r="C16" t="n">
-        <v>1175.301653432448</v>
+        <v>230.98111221652</v>
       </c>
       <c r="D16" t="n">
         <v>1.36958e-07</v>
@@ -9080,16 +8758,13 @@
         <v>-16298.55191694088</v>
       </c>
       <c r="Y16" t="n">
-        <v>390.4918075518529</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>217876328.0257168</v>
+        <v>210.7101508867933</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.640303864404856e-07</v>
+        <v>2.948716844737031e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9720715638424783</v>
+        <v>0.998253239832757</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8775,7 @@
         <v>72.988</v>
       </c>
       <c r="C17" t="n">
-        <v>1089.703197627686</v>
+        <v>223.6044205631403</v>
       </c>
       <c r="D17" t="n">
         <v>1.36887e-07</v>
@@ -9133,16 +8808,13 @@
         <v>-15585.79937136267</v>
       </c>
       <c r="Y17" t="n">
-        <v>375.5062330050512</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3172.946271935872</v>
+        <v>241.2719355365649</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.241315651755685e-06</v>
+        <v>6.887145220096756e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.6669372147365985</v>
+        <v>0.9605701039230062</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8825,7 @@
         <v>74.37799999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>1237.866964721545</v>
+        <v>221.3021694905316</v>
       </c>
       <c r="D18" t="n">
         <v>1.36843e-07</v>
@@ -9186,16 +8858,13 @@
         <v>-16502.58576815755</v>
       </c>
       <c r="Y18" t="n">
-        <v>373.3998191523149</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3149.076553888359</v>
+        <v>219.0282824615442</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.07087961023799e-06</v>
+        <v>3.155020356931639e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7032503934952897</v>
+        <v>0.9999747663909812</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8875,7 @@
         <v>73.68599999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>1374.122971297147</v>
+        <v>217.610299488288</v>
       </c>
       <c r="D19" t="n">
         <v>1.36822e-07</v>
@@ -9239,16 +8908,13 @@
         <v>-16651.58944383805</v>
       </c>
       <c r="Y19" t="n">
-        <v>371.3188852355273</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3123.663719967379</v>
+        <v>220.3154807684579</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.18720346893616e-06</v>
+        <v>3.766759833520993e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.6730752126117748</v>
+        <v>0.9948819408296141</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8925,7 @@
         <v>73.13099999999997</v>
       </c>
       <c r="C20" t="n">
-        <v>1219.265013511809</v>
+        <v>215.6329842508293</v>
       </c>
       <c r="D20" t="n">
         <v>1.36795e-07</v>
@@ -9292,16 +8958,13 @@
         <v>-16851.46139508637</v>
       </c>
       <c r="Y20" t="n">
-        <v>369.2982471975364</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3099.302276693664</v>
+        <v>217.9359637850355</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.942202739543038e-06</v>
+        <v>3.536249875474661e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.6557105089339925</v>
+        <v>0.9951334387587625</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8975,7 @@
         <v>71.46600000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>1425.72425234788</v>
+        <v>213.3616990321525</v>
       </c>
       <c r="D21" t="n">
         <v>1.36769e-07</v>
@@ -9345,16 +9008,13 @@
         <v>-16913.70999556211</v>
       </c>
       <c r="Y21" t="n">
-        <v>367.1860219749532</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3075.127425408357</v>
+        <v>215.1302710915043</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.907859228920702e-06</v>
+        <v>3.401973392876289e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.6277294533940498</v>
+        <v>0.9965270671834375</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +9025,7 @@
         <v>70.26300000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>1582.263100357433</v>
+        <v>211.3075754157582</v>
       </c>
       <c r="D22" t="n">
         <v>1.36741e-07</v>
@@ -9398,16 +9058,13 @@
         <v>-16789.93781409243</v>
       </c>
       <c r="Y22" t="n">
-        <v>365.2080411536498</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3048.036387501885</v>
+        <v>212.3721379263784</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.649870250503162e-06</v>
+        <v>3.275904155095662e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.6333881973766845</v>
+        <v>0.9975436089829007</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9221,7 @@
         <v>100.56</v>
       </c>
       <c r="C2" t="n">
-        <v>1212.64855539107</v>
+        <v>454.5897309367172</v>
       </c>
       <c r="D2" t="n">
         <v>1.47798e-07</v>
@@ -9597,16 +9254,13 @@
         <v>-5304.874138784559</v>
       </c>
       <c r="Y2" t="n">
-        <v>401.1043403775762</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>108907247.952289</v>
+        <v>0.2051128665565436</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.373384584861524e-07</v>
+        <v>1.124253487797941e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.927957716770761</v>
+        <v>0.9910397036434576</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9271,7 @@
         <v>70.649</v>
       </c>
       <c r="C3" t="n">
-        <v>2680.169616607989</v>
+        <v>220.3890627258374</v>
       </c>
       <c r="D3" t="n">
         <v>1.43856e-07</v>
@@ -9650,16 +9304,13 @@
         <v>-8006.074614647086</v>
       </c>
       <c r="Y3" t="n">
-        <v>381.3629202390516</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9439.87884057199</v>
+        <v>218.2742308179068</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.658933688911196e-07</v>
+        <v>3.198521157350651e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9982084002033405</v>
+        <v>0.9993248394189505</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9321,7 @@
         <v>65.30499999999995</v>
       </c>
       <c r="C4" t="n">
-        <v>2772.353020694173</v>
+        <v>293.3361362611387</v>
       </c>
       <c r="D4" t="n">
         <v>1.41636e-07</v>
@@ -9703,16 +9354,13 @@
         <v>-10066.13555488129</v>
       </c>
       <c r="Y4" t="n">
-        <v>364.5311168886443</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3058.22627779957</v>
+        <v>130.2662706679455</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.609211404066198e-06</v>
+        <v>1.963707764111064e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6804409056036921</v>
+        <v>0.9995388469200124</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9371,7 @@
         <v>68.39299999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>3936.753456025812</v>
+        <v>377.3782457533134</v>
       </c>
       <c r="D5" t="n">
         <v>1.40476e-07</v>
@@ -9756,16 +9404,13 @@
         <v>-12164.62309624022</v>
       </c>
       <c r="Y5" t="n">
-        <v>361.9718251685001</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3015.894685735782</v>
+        <v>39.16178378638405</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.520239378837497e-06</v>
+        <v>1.305650472509922e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6358179121648219</v>
+        <v>0.9999954920299587</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9421,7 @@
         <v>60.45499999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>3800.93210713362</v>
+        <v>60.45499999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.39867e-07</v>
@@ -9808,11 +9453,10 @@
       <c r="X6" t="n">
         <v>-12301.63704658648</v>
       </c>
-      <c r="Y6" t="n">
-        <v>364.3538657862861</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>105464050.9517256</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.705058324283315e-07</v>
@@ -9829,7 +9473,7 @@
         <v>57.06100000000004</v>
       </c>
       <c r="C7" t="n">
-        <v>10932.94245709177</v>
+        <v>295.8024498701705</v>
       </c>
       <c r="D7" t="n">
         <v>1.39524e-07</v>
@@ -9862,16 +9506,13 @@
         <v>-12591.55523584506</v>
       </c>
       <c r="Y7" t="n">
-        <v>359.2365938796329</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>30867463.59770979</v>
+        <v>117.720160713178</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.680696565424466e-07</v>
+        <v>2.109920437275224e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9712306144011446</v>
+        <v>0.9992231242068638</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9523,7 @@
         <v>55.97399999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>5691.992514653214</v>
+        <v>182.4132752263546</v>
       </c>
       <c r="D8" t="n">
         <v>1.39352e-07</v>
@@ -9915,16 +9556,13 @@
         <v>-13108.61851085418</v>
       </c>
       <c r="Y8" t="n">
-        <v>354.16747354124</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>289119563.5671461</v>
+        <v>233.8761783754527</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.667270538946964e-07</v>
+        <v>4.528409896661844e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9722673321817167</v>
+        <v>0.9993788528685684</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9573,7 @@
         <v>54.41900000000004</v>
       </c>
       <c r="C9" t="n">
-        <v>80690.26115623501</v>
+        <v>179.9192104091418</v>
       </c>
       <c r="D9" t="n">
         <v>1.39268e-07</v>
@@ -9968,16 +9606,13 @@
         <v>-13545.50494930807</v>
       </c>
       <c r="Y9" t="n">
-        <v>349.3739113736689</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>474103179.0063043</v>
+        <v>220.4748179153826</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.655311809901298e-07</v>
+        <v>3.966650188535112e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9732739305007284</v>
+        <v>0.9986108725435486</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9623,7 @@
         <v>52.26300000000003</v>
       </c>
       <c r="C10" t="n">
-        <v>137086.1988007794</v>
+        <v>52.26300000000003</v>
       </c>
       <c r="D10" t="n">
         <v>1.39238e-07</v>
@@ -10020,11 +9655,10 @@
       <c r="X10" t="n">
         <v>-13638.58811045589</v>
       </c>
-      <c r="Y10" t="n">
-        <v>345.0101471185797</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>187649832.029548</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.646770464454235e-07</v>
@@ -10041,7 +9675,7 @@
         <v>48.93799999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>5218.273174827402</v>
+        <v>48.93799999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.39217e-07</v>
@@ -10073,11 +9707,10 @@
       <c r="X11" t="n">
         <v>-13312.56357781967</v>
       </c>
-      <c r="Y11" t="n">
-        <v>333.1721359161679</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5602.47840505856</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.840085250934307e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 23.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>2.782526557021624e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9993444902882843</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>126.462</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1122.837618073158</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.31074e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-85.252</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1778819964779912</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.089293153795504</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.104313179905942</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.644722639784622</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27.16490610903331</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.53951509543693</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>23.27206089065146</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-12344.37768874648</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-496.6623560577252</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.765856924959165e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9540645597205092</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>120.127</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9499059005867376</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1170.06875982411</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.042064089224231</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.30011e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-85.554</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2434583226533332</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.18347198914152</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.30569155616504</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.145201308606906</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.66138098204909</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.78614871101689</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>25.8677099484165</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-13489.03786423497</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-548.0819950358172</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.708017582691505e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9578916680277162</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>113.013</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8936518479859562</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1221.082900450581</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.087497320000747</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.29335e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.758</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04569425672340185</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8119325738219176</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.926368514225424</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.58083555817284</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.93832620350692</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.89029421361499</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>27.14590986891531</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-13863.96538051371</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-601.6464087412255</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.661877335263083e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9997456135185345</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111.574</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8822729357435437</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1324.696258481078</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.179775452085689</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.28864e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.914</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4123040942772812</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.360741545056794</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.649670122709811</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.992624364730559</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.19159774703152</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.05805267390988</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.49299259925347</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14903.05133271452</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-699.4579102193015</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.642305570667434e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9625287614976732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104.864</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8292135186854548</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1271.422875137458</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.132330138100717</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.28581e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.015</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2810135135290894</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9020318354828287</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.155598522010069</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.892903409406919</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36.536222586957</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.07866841055484</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>29.80969128565701</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14783.95811005138</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-662.4058941713713</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.624525978720059e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9638636810929061</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100.478</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7945311635115688</v>
+      </c>
+      <c r="D17" t="n">
+        <v>279.6211029875773</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2490307578645436</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.28356e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.111</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7510205601316173</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.82519493579781</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.647561951245311</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37.73494990865267</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.10811613630992</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>30.27403320798036</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-14768.77376278749</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>224.5901466005297</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.803919173082032e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9943017056898975</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99.42899999999997</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7862361816197749</v>
+      </c>
+      <c r="D18" t="n">
+        <v>258.2593503850659</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2300059654469461</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.28196e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.19199999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3635042131552154</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.086408653935847</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.399689138944258</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.154290207897681</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39.26199052860405</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.20335717492929</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>31.88001430985865</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-15407.87487417757</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>242.4975014458217</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.995261903214791e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9802154211008546</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97.62399999999997</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7719631193560119</v>
+      </c>
+      <c r="D19" t="n">
+        <v>272.4940011150844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2426833557488901</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.27971e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.279</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.379843483238768</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.076706323494596</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.368862333224177</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.995516242664121</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.48026260911331</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.27073029357051</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>33.12287317267284</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-15823.33750516756</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>217.7810283576211</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.817194370839032e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9901845443776265</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90.94600000000003</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.719156742736949</v>
+      </c>
+      <c r="D20" t="n">
+        <v>270.464489143676</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2408758709098167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.27854e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.349</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1190157201801389</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4004532187446726</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.803182124567867</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.468701286382921</v>
+      </c>
+      <c r="L20" t="n">
+        <v>41.22627154855961</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.22851940606468</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>32.33313509996982</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-15136.25084606659</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>216.4949910995768</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.596509624283394e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9992307438145945</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>89.99900000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.711668327244548</v>
+      </c>
+      <c r="D21" t="n">
+        <v>271.653225451993</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2419345603313174</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2773e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.407</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.08883564878249696</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7851116347003053</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.926636331827337</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.508426057602019</v>
+      </c>
+      <c r="L21" t="n">
+        <v>42.23913891192351</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.29013535664943</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>33.49900806166463</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-15531.25305697876</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>215.1335023312679</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.782526557021624e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9993444902882843</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>2.905504970398272e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9981994650833986</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>115.611</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>432.9188242283471</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.4007e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.575</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.06951318462215825</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5363639417591418</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.685119683448859</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.017854888966721</v>
+      </c>
+      <c r="L23" t="n">
+        <v>33.26870929552174</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.7226039646996</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>25.14521032911586</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-12822.02778880958</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>60.87000534837613</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.064323391996013e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9999668573480585</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97.70499999999998</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8451185440831754</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1315.436488819968</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.038529200398384</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.39345e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.97499999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1857790428966435</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.403151162066192</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.306504634640369</v>
+      </c>
+      <c r="L24" t="n">
+        <v>39.39030896110042</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.94837269523504</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>27.91505518640042</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-13557.94999070565</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-708.6432888438155</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.763430389738114e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9635870822507515</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97.13600000000002</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8401968670801224</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1264.712381294312</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.921361489763326</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.38986e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.126</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1204578768004475</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8531209395630199</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.409483768391679</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.991770979476339</v>
+      </c>
+      <c r="L25" t="n">
+        <v>43.17298880949703</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.17854880117901</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>31.44551813616913</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15147.33515707951</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-675.7610854529307</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.732865694075292e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9658671588310183</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90.66300000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7842073851104135</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1341.02687446506</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.097640479956869</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.38786e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.22199999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2926918352227469</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.574525573621481</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.376592971047289</v>
+      </c>
+      <c r="L26" t="n">
+        <v>44.50083534249696</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.16927968497635</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>31.2861988063765</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-14808.5196472664</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-748.9172740480922</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.718479741523072e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9669316818352978</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8070166333653374</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1481.937328603784</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.423129800939592</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.38667e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.29300000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2932953736593257</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.129286132015484</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.335199387803538</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.158662694983656</v>
+      </c>
+      <c r="L27" t="n">
+        <v>47.07913007936292</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.32880186537525</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>34.27452972360252</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16171.68798660787</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-877.6405682184695</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6.919311721271531e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8718001307299609</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.84399999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7684735881533764</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1425.350679408188</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.292420194360441</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.38581e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.366</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2266073247084026</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.048968602297025</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.19063086677084</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.030853283879326</v>
+      </c>
+      <c r="L28" t="n">
+        <v>48.58405553382573</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.33883013400482</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>34.48155769680275</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-16045.38937363871</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-835.0136036987415</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.692610012807808e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9690307847277694</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88.85899999999998</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7686033335928241</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1549.749199337736</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.579768567698747</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.38516e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.405</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4764653158754314</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.365963224073554</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.44405821296238</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.214491632564211</v>
+      </c>
+      <c r="L29" t="n">
+        <v>49.08386415821636</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.41648753791699</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>36.17350164897743</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16726.77627878552</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-949.1038584269372</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.318479908176496e-06</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.7233618543659136</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>85.46800000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7392722145816577</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1673.573129399404</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.865789694828937</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.38474e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.447</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2613070317529992</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.019715664328673</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.383543495839679</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.151513710767172</v>
+      </c>
+      <c r="L30" t="n">
+        <v>49.76593931152152</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.38809614662625</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>35.53602944907729</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-16205.02873704155</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-1062.092286662245</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.679114916044387e-06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.7403640421130188</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86.26900000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7462006210481703</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1524.059991998209</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.520429019723866</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.38429e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.489</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8044593626129941</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.492624284211407</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.713240074058787</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.169981521747506</v>
+      </c>
+      <c r="L31" t="n">
+        <v>50.31281525164443</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.48458316352</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>37.79977698829273</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-17172.75378590349</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-936.7640077280334</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.676641170578329e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9703243491872734</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83.37299999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7211511015387809</v>
+      </c>
+      <c r="D32" t="n">
+        <v>274.730591488999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6346007059838307</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.38354e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.532</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5791586716262803</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.440439675494955</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.373385300900581</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.003763990569142</v>
+      </c>
+      <c r="L32" t="n">
+        <v>50.96133026838996</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.4780430744419</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>37.63726944066112</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16898.73726182367</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>185.9623079727016</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.438468089028628e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.998719115684059</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.09399999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6927887484754911</v>
+      </c>
+      <c r="D33" t="n">
+        <v>272.9577811281451</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6305056880228681</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.38316e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.56399999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2497183156415834</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9244531947223121</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.118351436617805</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.680211136750347</v>
+      </c>
+      <c r="L33" t="n">
+        <v>51.05797370567237</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.43660816401631</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>36.63928501116852</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-16228.82403837326</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>183.2363048643726</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.418732902253571e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9991202805606091</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77.12099999999998</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6670732023769363</v>
+      </c>
+      <c r="D34" t="n">
+        <v>271.3942577503896</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6268941024547368</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.38329e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1119905121092186</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6749111709089382</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.868492427981709</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.527776893446886</v>
+      </c>
+      <c r="L34" t="n">
+        <v>51.54947364743479</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.42629967368011</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>36.39916059435038</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15942.18692873509</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>180.8074417378887</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.409270555259314e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9993451830201321</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79.024</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6835335737948812</v>
+      </c>
+      <c r="D35" t="n">
+        <v>231.171530875439</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5339835505824653</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.38237e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.639</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5666007078452291</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.368839178456682</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.575457526474617</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.179732958503439</v>
+      </c>
+      <c r="L35" t="n">
+        <v>53.3794124102861</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.52159239249009</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>38.74646128319421</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16936.36643620468</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>211.6828465587813</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.751417442834842e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9996087324300101</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>76.39699999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6608108224995891</v>
+      </c>
+      <c r="D36" t="n">
+        <v>229.2730070242341</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5295981467955337</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.38212e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2858519373528463</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.341616894250423</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.328221694878474</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.035690631854864</v>
+      </c>
+      <c r="L36" t="n">
+        <v>53.94822747558594</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.51125202708421</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>38.47722089551421</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-16643.30296134172</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>218.0679127214798</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.029233658340091e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9994263817253142</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>76.05099999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6578180276963265</v>
+      </c>
+      <c r="D37" t="n">
+        <v>227.3590949716157</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.52517719777344</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.38169e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.705</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5598743303363515</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.271683280521099</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.460845748870019</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.356380541812865</v>
+      </c>
+      <c r="L37" t="n">
+        <v>55.1614172491581</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.53887902477388</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>39.20507593103612</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16846.48349964605</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>219.2073914470069</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.425261291322662e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9961716704977077</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>74.41500000000002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6436671251005529</v>
+      </c>
+      <c r="D38" t="n">
+        <v>224.8053977943077</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5192784078978555</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.38151e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.73399999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4036996126499637</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.141671879699344</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.706236060701364</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.220401319932065</v>
+      </c>
+      <c r="L38" t="n">
+        <v>55.39694693217127</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.55207436504415</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>39.56251670272344</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-16857.01893624054</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>215.365619841092</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.026180329335461e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9995291605925954</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>75.26500000000004</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.651019366669262</v>
+      </c>
+      <c r="D39" t="n">
+        <v>223.7890633677353</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5169307751092282</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.38102e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.759</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6923233787622027</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.724408025851523</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.950560058139958</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.887422707736175</v>
+      </c>
+      <c r="L39" t="n">
+        <v>56.29815725534894</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.60092914736765</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>40.94459638364689</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-17362.76992330362</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>216.2720785789252</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.339379047266922e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9984957090615103</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72.649</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6283917620295647</v>
+      </c>
+      <c r="D40" t="n">
+        <v>221.8603830450188</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5124757128324742</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.38053e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.78100000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4171271437730372</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.219041978718328</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.567569745415884</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.343598890053027</v>
+      </c>
+      <c r="L40" t="n">
+        <v>56.03853610797679</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.57576865845618</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.22097843238722</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-16876.74777693363</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>211.9662784744332</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.053481358964374e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9999613105289092</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>70.15699999999998</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6068367196893029</v>
+      </c>
+      <c r="D41" t="n">
+        <v>225.5904785067302</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5210918673006014</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.38014e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.80800000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5137708234577403</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.079343671455127</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.418460919227589</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.9658695451593</v>
+      </c>
+      <c r="L41" t="n">
+        <v>56.30510536327489</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.55961358739191</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>39.76968146326256</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16516.71193339312</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>222.7690568473654</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.649573060902027e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8905240182391647</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>69.86399999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.604302358772089</v>
+      </c>
+      <c r="D42" t="n">
+        <v>218.7677593021465</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5053320554773459</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.38002e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.84099999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2807535285702525</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.141952169131998</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.160260717261922</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.291795020231753</v>
+      </c>
+      <c r="L42" t="n">
+        <v>56.89884287006748</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.59781360725368</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.85358472405958</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16857.07896105192</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>218.7000535759879</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.605950951908154e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9967716024051789</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.46100000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5835171393725512</v>
+      </c>
+      <c r="D43" t="n">
+        <v>241.4594621157134</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.557747662153756</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.37988e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.86499999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1969564037566486</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9283398958539635</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.190472682701644</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.716488146449735</v>
+      </c>
+      <c r="L43" t="n">
+        <v>56.54821189176041</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.57623627401499</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>40.23419390030874</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-16423.9140367922</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>189.3419740583748</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.905504970398272e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9981994650833986</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>3.317399563027327e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9999981803798014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>128.455</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>309.090945875449</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.31411e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.224</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2961497334859802</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.07438005711279</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.054143240335374</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.670752362614413</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.84920750777166</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.50473203768817</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22.94725548113249</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-12123.84202056224</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>218.5960779723586</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.506183856205819e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9904481954231168</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>111.482</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8678681250243274</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1299.262109442114</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.203494559706912</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.29962e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.854</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3309961804814279</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.039111332003842</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.229773506922785</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.920709881674654</v>
+      </c>
+      <c r="L24" t="n">
+        <v>34.750027546527</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.99565485570862</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>28.57412331729682</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-14481.42614730383</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-675.7693372279103</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.664567588103265e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9617656197504765</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105.075</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8179907360554279</v>
+      </c>
+      <c r="D25" t="n">
+        <v>272.1599975378653</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8805175343037536</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.29233e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.074</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1543690342366548</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9733287695844106</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.208858162951442</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.91952451678127</v>
+      </c>
+      <c r="L25" t="n">
+        <v>38.57456074028052</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.1359397460767</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>30.72624013131347</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15304.82075703165</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>238.3786308458622</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.658020476123133e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9996729774001459</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102.436</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7974465766221638</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1357.517366827745</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.391967428818732</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.28793e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.202</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1946287545114478</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.274834238332939</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.583886807502353</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.269524906896642</v>
+      </c>
+      <c r="L26" t="n">
+        <v>41.34846520139183</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.24226566809949</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>32.5861551470263</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-16064.31660664211</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-742.7003003856094</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.603182105650482e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9661200428420953</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97.84100000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7616752948503368</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1478.225775612409</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.782494587234119</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.28431e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09234270436945416</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8258924627126107</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.130121393416192</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.680446529196132</v>
+      </c>
+      <c r="L27" t="n">
+        <v>42.938189124065</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.2628309136518</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>32.97216275140337</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16013.82608106867</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-853.0285735656098</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.834295378082544e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9992569699770993</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96.60300000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.752037678564478</v>
+      </c>
+      <c r="D28" t="n">
+        <v>276.4563527064457</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8944175052537653</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.28143e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.373</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1967073806402147</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.815595440953068</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.198568194472012</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.961068635430331</v>
+      </c>
+      <c r="L28" t="n">
+        <v>44.41427469034488</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.31719934723067</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>34.03808028109797</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-16357.28705731489</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>213.5683248966414</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.470797542756943e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9992737909397531</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95.69100000000003</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.744937916001713</v>
+      </c>
+      <c r="D29" t="n">
+        <v>273.9546872138348</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8863238825644131</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.27985e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.42700000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3298480835679606</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.06503664367744</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.526562412118118</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.271625341513504</v>
+      </c>
+      <c r="L29" t="n">
+        <v>45.41190804409871</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.3812777923025</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>35.38626601000009</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16865.19531556046</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>210.9820685970585</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.428441608749769e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9984887231390577</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92.08800000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7168891829823676</v>
+      </c>
+      <c r="D30" t="n">
+        <v>272.5038323262236</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8816299408395856</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.27862e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.491</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2213273545414763</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.12739830906719</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.237339269896657</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.794782410509471</v>
+      </c>
+      <c r="L30" t="n">
+        <v>46.34316522544032</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.40152683659176</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>35.83476719408563</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-16874.71697691734</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>208.1546335846111</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.442357276260284e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9985147960848259</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90.72899999999998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7063096025845627</v>
+      </c>
+      <c r="D31" t="n">
+        <v>274.9046951061026</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8893974371442052</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.27761e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.539</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3705906724996814</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.245483978466519</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.314626774374533</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.486040202824595</v>
+      </c>
+      <c r="L31" t="n">
+        <v>47.67165537552716</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.44911893954631</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>36.93499599502281</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-17247.43865135637</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>206.7994771969636</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.451633736877475e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9999535935978776</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>89.14699999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.693994005682924</v>
+      </c>
+      <c r="D32" t="n">
+        <v>251.5490738405515</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8138351420423539</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.2767e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.571</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3248178927093877</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.078967413326492</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.199718146763056</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.867271217500068</v>
+      </c>
+      <c r="L32" t="n">
+        <v>47.50616115459507</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.44835247916954</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>36.91674246362543</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-17040.17357784339</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>213.4479109632603</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.494282660667083e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9995595965316134</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86.73400000000004</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6752092172356082</v>
+      </c>
+      <c r="D33" t="n">
+        <v>243.1357328093168</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7866155125336169</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.27615e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.61799999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4218268456143988</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.322658430585799</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.386570487346716</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.321862086952069</v>
+      </c>
+      <c r="L33" t="n">
+        <v>48.99489222910123</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.47074562688456</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>37.45758347364621</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-17120.1256064699</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>218.0337664543482</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.65953005182518e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9992595384576498</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87.87199999999996</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6840683507843212</v>
+      </c>
+      <c r="D34" t="n">
+        <v>241.0072999985011</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7797294072004851</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.27526e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.66500000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6978565979983411</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.726468905081745</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.90767348351091</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.741659562188315</v>
+      </c>
+      <c r="L34" t="n">
+        <v>50.16899455770158</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.55210595611571</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>39.56338027044617</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-18003.73978618631</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>229.6951345985137</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.945624195718024e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.999962499917411</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>85.00900000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6617803900198514</v>
+      </c>
+      <c r="D35" t="n">
+        <v>239.1248549653668</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7736391445827866</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.27443e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.699</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3415276741666914</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.329998498487884</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.649623799320877</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.381282807868472</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50.41225208985558</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.53771951488943</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>39.17397492422733</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-17610.9871134212</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>227.3938993653259</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.975471881381715e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9999866947802626</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>81.565</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6349694445525671</v>
+      </c>
+      <c r="D36" t="n">
+        <v>236.1541328777196</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.76402798603127</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.27374e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.73399999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3862141369690649</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.06533420302879</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.211085945044229</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.899309230510733</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50.74319243120775</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.52154558342484</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>38.74523399413439</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-17208.48884818449</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>235.6568344820595</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.430751734684615e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.99951517383604</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80.928</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6300105095169515</v>
+      </c>
+      <c r="D37" t="n">
+        <v>232.7146077793028</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7529001120371779</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.27307e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.774</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5381187430298392</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.131387712789768</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.34469632957035</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.071291082847563</v>
+      </c>
+      <c r="L37" t="n">
+        <v>51.80401881796762</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.55344098214188</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>39.59990876630123</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17441.15762665463</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>232.0383683266263</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.496266441345273e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9992220583353456</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6125102175859252</v>
+      </c>
+      <c r="D38" t="n">
+        <v>230.0824630859932</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7443843508075678</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.27252e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.80500000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2647621442549637</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.184836442130321</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.262599557443147</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.214651173076095</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.26071364266095</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.55258391024402</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>39.57645013509659</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-17243.04685903747</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>213.8263170288621</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.868538484210145e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9992800698387687</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79.79400000000004</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6211825152777241</v>
+      </c>
+      <c r="D39" t="n">
+        <v>227.4035159567835</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7357171699504191</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.27191e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.833</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7661997557540706</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.326766979481069</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.564710195922419</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.529908175628724</v>
+      </c>
+      <c r="L39" t="n">
+        <v>52.74241802735012</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.6153973402204</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>41.37260989341588</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-17944.37131442848</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>221.6490058493261</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.210796750464919e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9967116446696979</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6077614728893387</v>
+      </c>
+      <c r="D40" t="n">
+        <v>225.2728379747509</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7288238008289206</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.27144e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.878</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7546145028248559</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.356954440799032</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.478819333185493</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.499086673610129</v>
+      </c>
+      <c r="L40" t="n">
+        <v>53.99092940782302</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.64204818525057</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>42.18489223197854</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-18135.46509163999</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>217.8833178602723</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.014317417191389e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9979532296584781</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>76.40500000000003</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5947997353158697</v>
+      </c>
+      <c r="D41" t="n">
+        <v>226.6062768689688</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7331378673262138</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.27113e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.90000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6706463919858338</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.422353147362363</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.632001414651894</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.179724261530192</v>
+      </c>
+      <c r="L41" t="n">
+        <v>53.83046628810909</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.64241017521204</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>42.19614469315525</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-17958.52544821114</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>211.296924098891</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.857972871790189e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.999552870680942</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>74.73899999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5818302129150285</v>
+      </c>
+      <c r="D42" t="n">
+        <v>224.2146908442899</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7254003840495519</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.2708e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.94</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5683809482985607</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.369701716363486</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.687698510528306</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.507433663685586</v>
+      </c>
+      <c r="L42" t="n">
+        <v>55.17276114244543</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.65490644638726</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>42.58830400864934</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-17946.06409079452</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>217.2527845608556</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.446115217376509e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9982915768328794</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>72.61700000000002</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5653108092328055</v>
+      </c>
+      <c r="D43" t="n">
+        <v>221.2493184731169</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7158065334022155</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.27013e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.96299999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3873089029219532</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.124209568982395</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.409891270046687</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.160184330058309</v>
+      </c>
+      <c r="L43" t="n">
+        <v>54.91244908678262</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.65396118956778</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>42.55838534295848</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-17744.21970502623</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>220.31982799243</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.317399563027327e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9999981803798014</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.307388778844133e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9999546695617846</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>130.234</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>492.2811540955083</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.37996e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.717</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07202664845586355</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3407518282098369</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.057552668873019</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.207857261436747</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.53329474445022</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.00061494428905</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.43146540766853</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5808.302779513925</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.195972326343027</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.09149498252307e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9875348917133651</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>85.577</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6571018320868588</v>
+      </c>
+      <c r="D13" t="n">
+        <v>234.8483986639029</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.477061526142314</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.39236e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.15000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.325413406432366</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9309109630611319</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.165840018206571</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.704236939535567</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.32678534541973</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.2671391483667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.32730328211609</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6796.953724562959</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>238.7307453422851</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.560917345551804e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9809900783642836</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>76.524</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.587588494555953</v>
+      </c>
+      <c r="D14" t="n">
+        <v>232.8792445915996</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4730614663067485</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.37508e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.934</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5546009352384351</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.376137804329235</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.32355230040416</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.144426345681668</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.24050676807615</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.95152604535487</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.77716672359222</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8069.112609432689</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>208.0564861196497</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.684395215091432e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9994109649278061</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>73.04199999999997</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5608520048528031</v>
+      </c>
+      <c r="D15" t="n">
+        <v>232.8677398586217</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4730380960580967</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.35982e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.404</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5035980585291561</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.209575112493277</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.467511956597355</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.727991680058426</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23.61596604441922</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.35950003177355</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.68347343646544</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9173.939713338897</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>202.084635118898</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.756018177647602e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9992629479487498</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>67.81400000000002</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5207088778659951</v>
+      </c>
+      <c r="D16" t="n">
+        <v>354.2043990623885</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7195164716658413</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.34835e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.71599999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1670621641700335</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.025381259487446</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.247211907482951</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.035977715278665</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.5414218030699</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.58101973264372</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23.67184792422899</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9838.252048670225</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80.95406291231197</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.594604097086345e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9993845287170436</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>68.13100000000003</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5231429580601072</v>
+      </c>
+      <c r="D17" t="n">
+        <v>324.1995677169077</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6585658724079637</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.33972e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.934</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6360304182257815</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.559712439582444</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.726317347346814</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.325319664595901</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.92231094358374</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.80078017159987</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.03997926821781</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10743.07042555574</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>102.6237146869881</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.695112329369602e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9990980818427974</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>63.90199999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4906706390036394</v>
+      </c>
+      <c r="D18" t="n">
+        <v>315.8948134903686</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6416959309985718</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.33379e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.107</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3494459330198162</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.143709976938647</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.247426052613434</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.970932618799004</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30.97096447634449</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.90012402087255</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>27.27309825683981</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-11053.07098521811</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>105.5784319624963</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.748258608957187e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9994234701546042</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>60.459</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4642336102707433</v>
+      </c>
+      <c r="D19" t="n">
+        <v>388.7748303033882</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.789741445653557</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.32873e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.24299999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2441439194917761</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9203981111752455</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.139796798558371</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.847991671378964</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32.66946247606383</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.97993307133902</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>28.35155427519584</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11312.33455660986</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>27.72185781669272</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.257772642469243e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999955845973827</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>61.10899999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4692246264416355</v>
+      </c>
+      <c r="D20" t="n">
+        <v>398.4005048317425</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8092946510693523</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3251e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.348</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5438541769385348</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.395037510540678</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.669971821702061</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.555414939046712</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.30801522795542</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.09190839973874</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>30.01669130786157</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-11874.33313082993</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>14.72619832578306</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.235045468630468e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9999156660069122</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56.19099999999997</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.431461830244022</v>
+      </c>
+      <c r="D21" t="n">
+        <v>388.7978229911109</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7897881520682377</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.3222e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.438</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.08604405244194629</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9206334549081292</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.02555026674533</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.992569253427723</v>
+      </c>
+      <c r="L21" t="n">
+        <v>35.50439815262592</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.1037037525636</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>30.20353899602047</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11736.96339846924</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>20.79965479585404</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.307388778844133e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9999546695617846</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>3.327877936435559e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9997574737254421</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>113.145</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>357.0406866607453</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.35036e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.182</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1505760818234145</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7731531203910154</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.003276334300212</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.426320137566016</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.32937160508418</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.40998884539238</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22.10675719047645</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11058.03164845512</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>138.7483403789973</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.574338419642469e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9992769428408949</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104.525</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9238145742189221</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1215.448793025685</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.404230493710052</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.33679e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.688</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2668031236871934</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.036357425760383</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.260546567795348</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.132888692699387</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.31094508839436</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.82907848491389</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>26.37974608869155</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-12887.85470734534</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-621.7085793202859</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.731094755667596e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9601272681503946</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101.551</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8975297185028057</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1361.702609770905</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.81385836585278</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.32952e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.928</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4074312951661168</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.166027180025574</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.297374894743989</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.103697649702061</v>
+      </c>
+      <c r="L25" t="n">
+        <v>34.88634803430541</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.03561727392091</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>29.15589075786477</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-14096.6253668565</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-754.7846960494028</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.853974146356537e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9999894978399823</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98.47399999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8703345264925534</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1401.777718388601</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.926100779994715</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.32425e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.074</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3703446100547459</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.151329383402778</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.262260490881905</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.127728620695996</v>
+      </c>
+      <c r="L26" t="n">
+        <v>37.50820903873145</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.12590844652591</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30.56165782648232</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-14593.08078356724</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-794.7228358993502</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.659933458259396e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9650895641874155</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96.40899999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.852083609527597</v>
+      </c>
+      <c r="D27" t="n">
+        <v>256.0109878035566</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.717035893578186</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.32104e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.20699999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5392592258844723</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.216380074690692</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.582132698625078</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.068490608082332</v>
+      </c>
+      <c r="L27" t="n">
+        <v>39.92667146314594</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.23523104501101</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>32.45618034320421</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-15346.34184152871</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>231.7433062945591</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.848809245381501e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9998068553984095</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93.51799999999997</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8265323257766577</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1517.948884153545</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.25147312579498</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.31841e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.26900000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3302634351417134</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.056692112141867</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.248625915727059</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.195651648485865</v>
+      </c>
+      <c r="L28" t="n">
+        <v>41.02196851584197</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.26574326382118</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.02756706761961</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-15431.40644278099</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-907.45809915876</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.6255153529867e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9676225195725283</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92.80500000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8202306774492906</v>
+      </c>
+      <c r="D29" t="n">
+        <v>264.207426986884</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.739992490653957</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.31663e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.35299999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.523344728445956</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.395018904351595</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.641916884218028</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.484531077848667</v>
+      </c>
+      <c r="L29" t="n">
+        <v>42.75112478166474</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.34692519291823</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>34.65050730635799</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16062.70326834718</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>219.5398450126584</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.775301442959909e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9795553396058071</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90.05799999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.795952096866852</v>
+      </c>
+      <c r="D30" t="n">
+        <v>262.6383216864274</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7355977385736499</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3149e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.41800000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4395876874386115</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.125274954028687</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.622288051572982</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.223500220678886</v>
+      </c>
+      <c r="L30" t="n">
+        <v>44.01821102558331</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.36326173207384</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>34.99655046162921</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-16030.59039215619</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>206.9145829262023</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.623853272567415e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9992988041667972</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83.95999999999998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7420566529674307</v>
+      </c>
+      <c r="D31" t="n">
+        <v>261.9993710065137</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7338081647133442</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.31353e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.477</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.602417523596386</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.758099486164819</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.732414377827308</v>
+      </c>
+      <c r="L31" t="n">
+        <v>44.73671880310231</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.3117973395633</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>33.92910051832172</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15278.70072850319</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>201.7827677252746</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.61683885930695e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9958587714030758</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>85.44400000000002</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7551725661761456</v>
+      </c>
+      <c r="D32" t="n">
+        <v>264.4213758382353</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7405917188633589</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.31225e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.524</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3112519479575973</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.025498442330901</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.282487752170091</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.140815682987528</v>
+      </c>
+      <c r="L32" t="n">
+        <v>46.01200420898316</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.40333634760319</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>35.87540007591397</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16101.64984084333</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>200.8568937967151</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.632875497945146e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9976457976696619</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83.76499999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7403332007600862</v>
+      </c>
+      <c r="D33" t="n">
+        <v>241.7371284043806</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6770576503906278</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.31102e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.56999999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7196881972102216</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.063632674220548</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.56447398656038</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.499453464676784</v>
+      </c>
+      <c r="L33" t="n">
+        <v>47.05323594021765</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.43765963813895</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>36.66395593673482</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-16319.70746934681</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>214.7450050896306</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.794818689721383e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9980643042087907</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>84.488</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7467232312519331</v>
+      </c>
+      <c r="D34" t="n">
+        <v>233.2266873216683</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6532215964038763</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.30994e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.616</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6110153446980167</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.447276985514313</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.601835562909352</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.565616618225262</v>
+      </c>
+      <c r="L34" t="n">
+        <v>47.99606500840096</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.48952368140284</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>37.92347138357046</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16775.68393520089</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>218.3747213558041</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.894966549636697e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9979024144424037</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79.09700000000004</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6990764063811924</v>
+      </c>
+      <c r="D35" t="n">
+        <v>232.6442919141273</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6515904226208884</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.30901e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.661</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7264555301297773</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.954872516341676</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.974146109871869</v>
+      </c>
+      <c r="L35" t="n">
+        <v>48.74698283605987</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.43843403923236</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>36.68214708828121</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15978.47705867695</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>226.7225121151572</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.216928298958019e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9998933240711612</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>77.55600000000004</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6854567148349464</v>
+      </c>
+      <c r="D36" t="n">
+        <v>228.7526972579346</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6406908394596831</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.30828e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.685</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3734413719913721</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8495422301089434</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.105468811064588</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.137639649043462</v>
+      </c>
+      <c r="L36" t="n">
+        <v>48.92735939463357</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.4520607038823</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>37.00522296977935</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-15986.14978403234</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>212.8787575204846</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.918715015026392e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9989942531731318</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>77.27599999999995</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6829820142295279</v>
+      </c>
+      <c r="D37" t="n">
+        <v>226.7130750809242</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6349782631253551</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.30739e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1985363731329773</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8775760946296537</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.177528453694789</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.029089573463846</v>
+      </c>
+      <c r="L37" t="n">
+        <v>49.85561175722484</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.50172950716394</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>38.23256173726999</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16410.35807759123</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>227.6405702061418</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.597525324439303e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9991496440311213</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>76.57900000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6768217773653276</v>
+      </c>
+      <c r="D38" t="n">
+        <v>224.3014833739286</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6282238740680456</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.30682e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.76300000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3370459563957311</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9745183409478436</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.284271464930761</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.910655098021333</v>
+      </c>
+      <c r="L38" t="n">
+        <v>50.35514553467614</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.53229054254551</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>39.02900960042764</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-16628.03869600047</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>209.8739459890468</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.958447196195316e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9992431696190411</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>76.11499999999995</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6727208449334918</v>
+      </c>
+      <c r="D39" t="n">
+        <v>221.9669927437048</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6216854298026109</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.30609e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.79600000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2820905077459882</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.068162640978397</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.485315090007098</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.29380758574157</v>
+      </c>
+      <c r="L39" t="n">
+        <v>51.20198023007158</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.56643024143784</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>39.95886663715626</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16898.86726804942</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>217.7835419356093</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.334081727124552e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9963871348094269</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>74.577</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.65912766803659</v>
+      </c>
+      <c r="D40" t="n">
+        <v>219.881514773832</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6158444205065069</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.30585e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.84</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2720796036774977</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.135012512533163</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.499184462509821</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.536873695252218</v>
+      </c>
+      <c r="L40" t="n">
+        <v>52.47150482237888</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.5755622336933</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.21514734066275</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-16834.99572961427</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>214.8147510476772</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.207116811534443e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9974095421104726</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>73.88200000000001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6529851076052851</v>
+      </c>
+      <c r="D41" t="n">
+        <v>221.1968475042425</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6195284060564794</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.30541e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.87</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6979595335423836</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.015345194688437</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.342801621416547</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.151741334015781</v>
+      </c>
+      <c r="L41" t="n">
+        <v>52.77130604888472</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.60138341235772</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>40.95790030923192</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-17014.7453676991</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>219.1984453351588</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.39001293472796e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9999723027827738</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.15800000000002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6023951566573865</v>
+      </c>
+      <c r="D42" t="n">
+        <v>219.1383865423527</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6137630660299919</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.30485e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.896</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6572037844327163</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.723410416429102</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.808567272961701</v>
+      </c>
+      <c r="L42" t="n">
+        <v>52.85430080487623</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.52127905446127</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>38.73824733928092</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15826.61462063316</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>211.0848938209815</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.138904427055603e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9999888794924949</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>73.74900000000002</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6518096248177118</v>
+      </c>
+      <c r="D43" t="n">
+        <v>216.6645480753944</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6068343361698322</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.30452e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.934</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.8279753148514126</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.718800916485976</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.789910803388504</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.094896364935551</v>
+      </c>
+      <c r="L43" t="n">
+        <v>54.40523652964323</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.67967253573478</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>43.387446525239</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-17783.62994468227</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>210.9395793547784</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.327877936435559e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9997574737254421</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>4.711154342875005e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9844700846400498</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>124.007</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>377.1986485961716</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.42364e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.172</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1475317172455076</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5491065251219244</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.299768982330636</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.490451348572728</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.23641004851777</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.5734836262973</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.52689366006718</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5264.72458753714</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>106.1328657442626</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.288734449132212e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9989342332759684</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83.63200000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6744135411710629</v>
+      </c>
+      <c r="D13" t="n">
+        <v>234.7414298331167</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6223283956789319</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.42039e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.833</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3951801674856225</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.004075919106236</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.028514809940817</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.629600561539606</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.17888372248058</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.0032009398027</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.31215659855639</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6368.238706289995</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>227.0477299226874</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.089800078248353e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9978623643395942</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79.17600000000004</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6384800858016083</v>
+      </c>
+      <c r="D14" t="n">
+        <v>238.7608751817361</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6329844395528395</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.39813e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.73399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.244805505050918</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.778309896176582</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.875108049534948</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.231455458527977</v>
+      </c>
+      <c r="L14" t="n">
+        <v>19.29681133932474</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.84456018329087</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.13941789571864</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7917.759453026883</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>206.9449467062814</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.6287256339928e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9994832596885793</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5820639157466917</v>
+      </c>
+      <c r="D15" t="n">
+        <v>233.5702075834454</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6192233414746547</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.37992e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.26300000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5304552065887045</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.234395001242919</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.347352391313667</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.164562404650361</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.89828902638913</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.2567462518365</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20.87010420282448</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8929.433037612014</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>212.6941255730871</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.929332133305095e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9986058894156015</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>70.00899999999996</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5645568395332518</v>
+      </c>
+      <c r="D16" t="n">
+        <v>328.8894945728115</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8719264923054384</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.36703e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.622</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5904198919995903</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.151603432549296</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.358905446866916</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.064990056643957</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.14229911344584</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.55762539885507</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23.44483569035805</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9911.451398944964</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>111.9193884551673</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.912842229381056e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.992063009943382</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>65.73400000000004</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5300829791866591</v>
+      </c>
+      <c r="D17" t="n">
+        <v>327.1044915943984</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8671942299151664</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.3576e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.85599999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1796670358858117</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.142429341888751</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.150578729279332</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.837279147388965</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.52055018265381</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.71961191690619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>25.11218304492023</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10457.32644871787</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>107.6448616650236</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.752909804369162e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9964524197215489</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>65.70699999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5298652495423645</v>
+      </c>
+      <c r="D18" t="n">
+        <v>315.0342460614964</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8351945247788302</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.35109e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.051</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7027325452828443</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.463907646666737</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.440647435841053</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.178167468120908</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.0887744243484</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.89886347394258</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>27.25672148466398</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-11245.43405165313</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>114.5326330015931</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.798702133260367e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9983456045523751</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>59.49400000000003</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4797632391719824</v>
+      </c>
+      <c r="D19" t="n">
+        <v>388.3644729518133</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.029601973382455</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.34609e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.187</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1546566482363866</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6326767915943524</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.905116921374161</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.402519992793956</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32.6449759772661</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.9207469114542</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>27.54384529644544</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11125.36763713648</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>33.81805713029578</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.26060767062711e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999898475104083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>60.26400000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.485972566064819</v>
+      </c>
+      <c r="D20" t="n">
+        <v>285.7224593983365</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7574853739845463</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3425e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.31399999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5001385020331462</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.185976331440435</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.510807797859341</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.154664958529194</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.8906087303131</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.06866440834293</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>29.65516584665808</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-11897.30801714758</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>134.0890254746868</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.004135561621898e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9998882337304682</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>60.077</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4844645866765586</v>
+      </c>
+      <c r="D21" t="n">
+        <v>218.9600702858357</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.58049007095</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.33984e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.413</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9346006582115417</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.422164254515464</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.724357026499066</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.066108846378718</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36.31008441041866</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.1680233395651</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>31.26472852899871</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-12434.17226967321</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>217.5833856088824</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.711154342875005e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9844700846400498</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>3.514208323216027e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9995503755085474</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>120.405</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>297.8238852640771</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.4003e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.227</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1904481742290459</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.854818698938966</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.871087436611262</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.448882625495529</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.96094924565681</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.61199063625102</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.89162513017471</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8686.133135867789</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>210.9188048562233</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.137940533595913e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9989564695668066</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106.272</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8826211536065776</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1301.81522299347</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.371090726451187</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.36711e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.384</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2287152286706374</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.299399411249475</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.317115546426677</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.043411297611991</v>
+      </c>
+      <c r="L24" t="n">
+        <v>27.91021216558055</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.61820935853832</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24.04189980595649</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-11896.57602459269</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-691.1064304548198</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.809083805034442e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9568502772434311</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100.224</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8323906814501056</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1329.973789258696</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.465638436216837</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.35447e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.762</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2740149499731916</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.030147439665586</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.379578587893013</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.098711081818809</v>
+      </c>
+      <c r="L25" t="n">
+        <v>33.047796442997</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.90968108703846</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>27.39790400897862</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-13325.24316002457</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-727.1069165212596</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.738985204231838e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9614436847749341</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99.923</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8298907852663924</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1319.075342238137</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.429044839934607</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.34813e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.95999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8424748988119065</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.41646158147149</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.665065823210168</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.581421301036349</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.30255578874856</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.10998604028869</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30.30400689299799</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-14629.67131829655</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-725.544088079002</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.700756659347028e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9641181272402682</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91.04399999999998</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7561480004983179</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1378.272176065052</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.627809400991977</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.34414e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.09099999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.08693528301623969</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6254812080830131</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.053056163950485</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.571902884236613</v>
+      </c>
+      <c r="L27" t="n">
+        <v>38.16372192538996</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.09375167779901</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>30.04573790057623</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-14209.24727128199</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-782.5083849143859</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.68002551100011e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9655398689829168</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>85.00900000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7060254972800132</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1439.64122536074</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.833867586154906</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.34128e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.19799999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.04398044082441644</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.090750417036863</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.940398891385464</v>
+      </c>
+      <c r="L28" t="n">
+        <v>39.47167640342165</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.06670532332714</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>29.62509229111804</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-13763.94748817758</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-841.3443499207954</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.66198345384196e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9668629723079419</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91.34000000000003</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7586063701673519</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1564.427449152797</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.252860924051261</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.33927e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.264</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.510513439407238</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.368924675205588</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.545661225637498</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.17491193090753</v>
+      </c>
+      <c r="L29" t="n">
+        <v>41.65046854068598</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.29492502434373</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>33.59316479265556</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-15682.86009572078</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-955.0668534855909</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.77094109916298e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9999999860989168</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>88.19399999999996</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7324778871309325</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1664.144061884236</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.587678303265228</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.33729e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.334</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4587350122262122</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.053150148941244</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.191575198893802</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.969298016130145</v>
+      </c>
+      <c r="L30" t="n">
+        <v>42.90602094757921</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.31178839547577</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>33.92892065902269</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15651.29473670315</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-1046.930113745831</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.639971929839753e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.968447875621587</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86.22899999999998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.716157966861841</v>
+      </c>
+      <c r="D31" t="n">
+        <v>260.5354111560781</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8747968985934902</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.33595e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.220447407081307</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.372259963094892</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.782693991537857</v>
+      </c>
+      <c r="L31" t="n">
+        <v>43.76940997105598</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.33982469682809</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>34.50222617392208</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15764.34154710978</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>221.6729228584302</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.946225521568107e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9768257594433111</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>84.887</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7050122503218303</v>
+      </c>
+      <c r="D32" t="n">
+        <v>258.312394349725</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8673326993927377</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.33485e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.437</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1778411172250179</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.037918207206718</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.317968621508405</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.924217298201902</v>
+      </c>
+      <c r="L32" t="n">
+        <v>44.64645579013533</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.37191918054657</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>35.18274839827001</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15934.39619045957</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>208.6414680434051</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.671600186441002e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9981138690219217</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>84.24399999999997</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6996719405340306</v>
+      </c>
+      <c r="D33" t="n">
+        <v>258.0487266149413</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8664473851253818</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.33389e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.482</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4390828994100324</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.296116317949674</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.516227724758624</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.497620027677549</v>
+      </c>
+      <c r="L33" t="n">
+        <v>46.02124065458372</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.41432945599126</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>36.12424477514838</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-16252.51595046164</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>202.2520148290152</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.647463922517598e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9960123890533075</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80.80599999999998</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.671118309040322</v>
+      </c>
+      <c r="D34" t="n">
+        <v>260.376226508733</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8742624060453054</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.33293e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.535</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1981368519938238</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8998556832980953</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.304146116114672</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.947471979252967</v>
+      </c>
+      <c r="L34" t="n">
+        <v>46.74603020550754</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.41061103453872</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>36.03968784011037</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16028.72150931268</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>203.8126047979085</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.72884822694767e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9974476830022549</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80.16300000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6657779992525227</v>
+      </c>
+      <c r="D35" t="n">
+        <v>238.4628540344122</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8006841151204842</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.33203e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.57299999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2867986388771034</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.069348375307753</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.125654236682709</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.900370958588094</v>
+      </c>
+      <c r="L35" t="n">
+        <v>47.47885178218676</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.43327254477968</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>36.56123987820738</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16130.07587172526</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>215.0631429778591</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.82062949476141e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9981107744170539</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>72.80300000000005</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.604650969644118</v>
+      </c>
+      <c r="D36" t="n">
+        <v>236.8293467416155</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7951993055614783</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.33143e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1084767012000819</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.187834329476276</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.156482962352657</v>
+      </c>
+      <c r="L36" t="n">
+        <v>46.93553120817976</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.30164900253993</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>33.72624261967252</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14594.95151907926</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>214.5494407783958</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.927738991316743e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9980667775757276</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79.13499999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.657240147834392</v>
+      </c>
+      <c r="D37" t="n">
+        <v>229.4587798558131</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7704512337966264</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.33054e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.655</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5561334322968206</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.379764212327423</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.554965450624795</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.157139765297166</v>
+      </c>
+      <c r="L37" t="n">
+        <v>49.63030921717826</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.51491342104781</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>38.57212688822576</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16806.83966202478</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>227.4093860881763</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.320689123665889e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.999897587602508</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>77.017</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6396495162161038</v>
+      </c>
+      <c r="D38" t="n">
+        <v>227.0090815361379</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7622259085595215</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.33038e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.68300000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4350936473064957</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.280935521500277</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.56340135305993</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.666020172977758</v>
+      </c>
+      <c r="L38" t="n">
+        <v>50.19868416358441</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.5165870612917</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>38.61566484624898</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-16665.98065748631</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>225.2666992763086</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.316986974632975e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.999791324536471</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78.03199999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6480793986960671</v>
+      </c>
+      <c r="D39" t="n">
+        <v>223.318284780645</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7498333606877474</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.32974e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.72199999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9344358162724209</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.57352195341097</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.653464789645653</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.168356644033553</v>
+      </c>
+      <c r="L39" t="n">
+        <v>50.78203327005826</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.56988028413464</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>40.05530421361483</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-17201.66456970658</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>223.736925621368</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.675124400442101e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9948869104919874</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>74.76599999999996</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6209542793073373</v>
+      </c>
+      <c r="D40" t="n">
+        <v>221.4349311421819</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7435096447883556</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.32936e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.754</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4581996164536785</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.081457603830237</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.059235308547056</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.950474385472732</v>
+      </c>
+      <c r="L40" t="n">
+        <v>51.08267860844081</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.54107988918297</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>39.26424465960307</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-16648.47850029673</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>221.6101910815641</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.493212044199326e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9949017958490781</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>81.35699999999997</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6756945309580162</v>
+      </c>
+      <c r="D41" t="n">
+        <v>219.3363077886187</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7364631201226043</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.32884e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.78700000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.724817634640487</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.782594133650997</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.000965509988829</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5.864705141533984</v>
+      </c>
+      <c r="L41" t="n">
+        <v>52.5309502095397</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.7222515776574</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>44.83377155936709</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-19179.41293714672</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>218.8533017712282</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.373145847949433e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9961888146378377</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>67.51500000000004</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5607325277189488</v>
+      </c>
+      <c r="D42" t="n">
+        <v>217.2125788377318</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7293322986674889</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.32834e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.821</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3518807705337629</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.587347054985503</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.304062021941724</v>
+      </c>
+      <c r="L42" t="n">
+        <v>51.7077246709522</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.46246401890861</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>37.25573011912314</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15400.26373223274</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>215.9163131663147</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.240486504944793e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9973085938364602</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>76.25200000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6332959594701216</v>
+      </c>
+      <c r="D43" t="n">
+        <v>218.4613710634203</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7335253546562024</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.32818e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.851</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.640291974051946</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.129090198646517</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.335943161282973</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.084502388976164</v>
+      </c>
+      <c r="L43" t="n">
+        <v>53.63909919572608</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.69849085206897</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>44.01499935883474</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-18393.18569421029</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>221.0792775782005</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.514208323216027e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9995503755085474</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.385040067397342e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9994294686443047</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>134.256</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>344.8271343059443</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.45121e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.01300000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2875363148956713</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7839386182584485</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.526556016009936</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.882158004050137</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.08523423968417</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.49918395916609</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.3838469103033</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5250.953486006958</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>139.4489923581032</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.539987100596939e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9973872035437737</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82.05099999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6111533190322963</v>
+      </c>
+      <c r="D13" t="n">
+        <v>232.140385195269</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6732079993139543</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44345e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.952</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2273951028380678</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8561023301699239</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.078115871711116</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.770837372650904</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.70977465012022</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.10331232512375</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.68103658445144</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6428.417618295207</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>217.9219797836351</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.793305124279454e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9994717118838898</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>72.76100000000002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.541957156477178</v>
+      </c>
+      <c r="D14" t="n">
+        <v>230.9881618802109</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6698665473212703</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.41798e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.92100000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.432100356170089</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.15918510012084</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.292750016909542</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.918568256018977</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.49111343701817</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.95039915777241</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.770215076152</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7975.320502822983</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>206.8508987825704</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.731651690589102e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9993183421428584</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>69.72300000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5193287450840186</v>
+      </c>
+      <c r="D15" t="n">
+        <v>235.6044113410417</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6832536883016989</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.39885e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.47199999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4695339054831082</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.179566746522168</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.276852005340013</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.735652831965993</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.75600408426212</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.43536910256242</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>22.32582828733286</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9362.084669412065</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>217.5022764762756</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.298657407732259e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9817781056717075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>69.18100000000004</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5152916815635802</v>
+      </c>
+      <c r="D16" t="n">
+        <v>324.0627111194066</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9397830938440168</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.38618e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.825</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8368184598070096</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.434652697637291</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.530023157173491</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.152210999246645</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.62084430887329</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.7556883062751</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25.51627431049239</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10601.21969535638</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>111.5542954684589</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.060783038861011e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9899277629228933</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>70.18599999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5227773805267546</v>
+      </c>
+      <c r="D17" t="n">
+        <v>306.5772836847627</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8890752878303226</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.37709e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.06100000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.689863731115181</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.046000611455014</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.454590031108722</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.244487200646617</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.92102320706093</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.99494859295974</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>28.56405010142371</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11797.63606719903</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>123.8372678086702</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.114229879522614e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9964388354463364</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>63.12099999999998</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4701540340841375</v>
+      </c>
+      <c r="D18" t="n">
+        <v>224.1837446285852</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6501337114314225</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.37161e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.25700000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4290091167837713</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.187548516452249</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.116201812707581</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.880991108345968</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.70392156141912</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.06013333914801</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>29.52465046603283</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-11910.99916511957</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>198.7960623224378</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.993754075627584e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9983403714535143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>60.96899999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4541249553092598</v>
+      </c>
+      <c r="D19" t="n">
+        <v>286.8248152862473</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.83179305440553</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.36684e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.39100000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2734043755488413</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.345784003941734</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.459635923457063</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.182853234655018</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36.99664937929808</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.16340468963088</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>31.1860506491509</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12423.38149510681</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>125.4105420348018</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.895453233581109e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.999893604003559</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>60.221</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4485535097127875</v>
+      </c>
+      <c r="D20" t="n">
+        <v>314.6530164753547</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.912494943614797</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.36418e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.488</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9045724190484686</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.465495990064886</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.597983352973499</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.178081958715279</v>
+      </c>
+      <c r="L20" t="n">
+        <v>38.6125616181471</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.24712784817928</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>32.67660046061189</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-12879.70078544074</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>95.95032025661813</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.790583607794887e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9981518068203472</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58.30099999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4342524728876175</v>
+      </c>
+      <c r="D21" t="n">
+        <v>368.8360063945358</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.069625820302442</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.36178e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.587</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7892208974391008</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.370849447281564</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.386909576465692</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.15630253813424</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40.54521353049856</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.32050250286623</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>34.10506323137476</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-13285.89821834282</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>38.7085527339773</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.385040067397342e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9994294686443047</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>3.275904155095662e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9975436089829007</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>112.704</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>305.5525883610767</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.43565e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.29300000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4959055670420575</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.586756815320366</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.150004120034919</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.34016829248513</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.65441705284117</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.10633029014837</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8593.638004325428</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>195.4399967472757</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.019746967994297e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9993308831626059</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106.277</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9429745173197051</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1286.458599278832</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.210269028251863</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.40363e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.313</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8280253555913717</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.617647183996894</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.399626816114479</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.950347170866386</v>
+      </c>
+      <c r="L24" t="n">
+        <v>27.48379038793594</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.62321067557258</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24.09254781736517</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-11840.64945193359</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-685.0594560954437</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.865560298812348e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9561961947193215</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98.12400000000002</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8706345826235096</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1228.839148084151</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.021694447673966</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.39069e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.717</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2116383013726481</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9582943207768206</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.227577819866553</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.913504955135797</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.9633118811969</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.88393660932623</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>27.06427749399874</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-13041.57198786413</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-644.3422125294036</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.787540813147449e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9612695288223025</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96.012</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8518952299829642</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1280.664726304585</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.191307078018275</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.38452e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.922</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2189114680642494</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.180223357025625</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.304662586000497</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.011265600275663</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.4376246988161</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.04612989654245</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29.312884077808</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-13975.83191713709</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-695.6018167050154</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.752994282087224e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9635642570370346</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>89.96599999999995</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.798250283929585</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1377.07197414185</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.506824771238855</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.38064e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.051</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5022086359909113</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.73828235454599</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.661496002131329</v>
+      </c>
+      <c r="L27" t="n">
+        <v>38.48364080755779</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.05673054153104</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>29.47291122073068</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-13808.29235260107</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-784.7664209405373</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.729583716904129e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9651903461022434</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94.36799999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8373083475298125</v>
+      </c>
+      <c r="D28" t="n">
+        <v>247.7761895840785</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8109117678010866</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.37826e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.15600000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7874010170535384</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.631564961163769</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.663010046563074</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.460722732002552</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40.93285349340482</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.27044688663949</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.11744231579915</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-15532.44254583502</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>223.9977339649027</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.696735453574901e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9991417372695413</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88.21200000000005</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7826873935264058</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1399.616440110153</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.580607376351864</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.37642e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.235</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6242231188623198</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9676343193172794</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.442593355943094</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.007705508736649</v>
+      </c>
+      <c r="L29" t="n">
+        <v>42.31264864052041</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.24290423031162</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>32.59800501140025</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-15019.59746420028</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-815.6111957146711</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.699571050475663e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9673986967322421</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>86.52100000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7676834894946054</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1510.465711895646</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.943390334205588</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.37501e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.306</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4620594521889791</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.068804789065058</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.312750144623849</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.036746361847698</v>
+      </c>
+      <c r="L30" t="n">
+        <v>43.69460385081167</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.29186155096993</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>33.53288126858914</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15295.7998640503</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-917.8686634096027</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.299760744514844e-06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.7206784422406334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84.55599999999998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7502484383872797</v>
+      </c>
+      <c r="D31" t="n">
+        <v>244.133329412032</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7989895641909454</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.37379e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.36799999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.354721607336536</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.19145251376467</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.204583051530835</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.22585319527408</v>
+      </c>
+      <c r="L31" t="n">
+        <v>44.96742248647183</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.33010779802876</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>34.30134918815782</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15496.52076257386</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>225.0475612431466</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.952358883584935e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9998366309771888</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>85.34500000000003</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7572490772288475</v>
+      </c>
+      <c r="D32" t="n">
+        <v>241.5502183797672</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7905356641728825</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.37277e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.416</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9147051797277438</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.428852187994655</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.618215573143581</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.167444174510042</v>
+      </c>
+      <c r="L32" t="n">
+        <v>45.64887252385711</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.40474625744268</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>35.90712372131114</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16136.33295058607</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>219.594437726525</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.107345193227281e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9961586536350435</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>77.20300000000003</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.685006743327655</v>
+      </c>
+      <c r="D33" t="n">
+        <v>253.0569208937246</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8281943290059217</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.37214e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.462</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3598668737548246</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.411012730276602</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.128593992565151</v>
+      </c>
+      <c r="L33" t="n">
+        <v>45.40441804939214</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.2793501247301</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>33.28890730102925</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14647.01905829087</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>213.6637292518529</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.937269341668482e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9800345757141827</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80.02299999999997</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7100280380465641</v>
+      </c>
+      <c r="D34" t="n">
+        <v>251.0433145577155</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8216042806387661</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.37122e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.508</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1209527387684319</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.010424950348922</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.248906958226849</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.814085383256018</v>
+      </c>
+      <c r="L34" t="n">
+        <v>47.14611154018428</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.40617885970838</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>35.93941543066358</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15797.92056487545</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>204.0799017147456</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.804022997411781e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9987813511608479</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75.322</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6683170073821691</v>
+      </c>
+      <c r="D35" t="n">
+        <v>254.2156022041721</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8319864137552686</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3706e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.545</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4638370498212119</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.910052324553353</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.75981163317594</v>
+      </c>
+      <c r="L35" t="n">
+        <v>47.84135482975276</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.35504712138336</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>34.8216883773384</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15094.6284375091</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>208.3974991826625</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.245702527674403e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9943399452122906</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78.28199999999998</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6945804940374785</v>
+      </c>
+      <c r="D36" t="n">
+        <v>252.3961907310332</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8260319183837916</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.36985e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.587</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5052179703890171</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.019529494491963</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.334090789504904</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.088039535229215</v>
+      </c>
+      <c r="L36" t="n">
+        <v>48.96615506324409</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.47903605119467</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>37.66185287272612</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-16328.45434062075</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>191.3585133297507</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.498527913586906e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9999035199301276</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>76.464</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.678449744463373</v>
+      </c>
+      <c r="D37" t="n">
+        <v>230.98111221652</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7559455262855297</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.36958e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.63</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3247480507861498</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.142872454857702</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.521556784898553</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.382739632121032</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50.20702195728759</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.49065533624402</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>37.95191827476459</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16298.55191694088</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>210.7101508867933</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.948716844737031e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.998253239832757</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>72.988</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6476078932424758</v>
+      </c>
+      <c r="D38" t="n">
+        <v>223.6044205631403</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7318033918891341</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.36887e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.65300000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07873981263444427</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.749340141456708</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.050301209771286</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.894760236396851</v>
+      </c>
+      <c r="L38" t="n">
+        <v>49.89027451049957</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.44194140277973</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>36.76476354958777</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-15585.79937136267</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>241.2719355365649</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.887145220096756e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9605701039230062</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>74.37799999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6599410846110163</v>
+      </c>
+      <c r="D39" t="n">
+        <v>221.3021694905316</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7242686788469126</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.36843e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.694</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3920910056521773</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.352871154610726</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.582126968586413</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.541963158896137</v>
+      </c>
+      <c r="L39" t="n">
+        <v>51.44471404856569</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.53242985999732</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>39.03271627264386</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16502.58576815755</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>219.0282824615442</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.155020356931639e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9999747663909812</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>73.68599999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6538011073253831</v>
+      </c>
+      <c r="D40" t="n">
+        <v>217.610299488288</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7121860778712639</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.36822e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.726</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4164622445740868</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.336789869355909</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.314026562672537</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.071243381509586</v>
+      </c>
+      <c r="L40" t="n">
+        <v>51.5547216193296</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.55674945260151</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>39.69072512253167</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-16651.58944383805</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>220.3154807684579</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.766759833520993e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9948819408296141</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>73.13099999999997</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6488767035775125</v>
+      </c>
+      <c r="D41" t="n">
+        <v>215.6329842508293</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7057148015254647</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.36795e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.762</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8120121246553947</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.33117745829463</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.674237639603463</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.263904964532949</v>
+      </c>
+      <c r="L41" t="n">
+        <v>52.58921192846201</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.58473711769085</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>40.4759617126121</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16851.46139508637</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>217.9359637850355</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.536249875474661e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9951334387587625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>71.46600000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6341034923339012</v>
+      </c>
+      <c r="D42" t="n">
+        <v>213.3616990321525</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6982814322620606</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.36769e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.78400000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5884355961336842</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.31437535523234</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.607131094079043</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.48620913669718</v>
+      </c>
+      <c r="L42" t="n">
+        <v>52.84353422473711</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.60130208001813</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.95551771787612</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16913.70999556211</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>215.1302710915043</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.401973392876289e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9965270671834375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>70.26300000000003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6234295144804091</v>
+      </c>
+      <c r="D43" t="n">
+        <v>211.3075754157582</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.691558780598685</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.36741e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.816</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5711502675243449</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.452995813698131</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.593207236360604</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.732259849175275</v>
+      </c>
+      <c r="L43" t="n">
+        <v>53.64127473272201</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.60453112993389</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>41.05032449489355</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-16789.93781409243</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>212.3721379263784</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.275904155095662e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9975436089829007</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8663187546127861</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>454.5897309367172</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.47798e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.81100000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1858786897697501</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5761232361937542</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.529415065979131</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.823728616810431</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.4743140759348</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.07196918455699</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.5978216620827</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5304.874138784559</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.2051128665565436</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.124253487797941e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9910397036434576</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>70.649</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7025556881463803</v>
+      </c>
+      <c r="D13" t="n">
+        <v>220.3890627258374</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4848087137201906</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.43856e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-85.01900000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2573476385916386</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9328062405032042</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.977705808995471</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.714843158946661</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.23427694191831</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.01464537540696</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.17491468162689</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8006.074614647086</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>218.2742308179068</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.198521157350651e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9993248394189505</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>65.30499999999995</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6494132856006359</v>
+      </c>
+      <c r="D14" t="n">
+        <v>293.3361362611387</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6452766446278868</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.41636e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.785</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5806117957601437</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.080142564586975</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.424196426777212</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2015206332408</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28.40958958227861</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.67743692957593</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24.65568924399423</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10066.13555488129</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>130.2662706679455</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.963707764111064e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9995388469200124</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>68.39299999999997</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6801213206046138</v>
+      </c>
+      <c r="D15" t="n">
+        <v>377.3782457533134</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8301512772312222</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.40476e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-86.152</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.058351096808554</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.293269559505159</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.386080398305476</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.336142077774697</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.92955917781334</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.08235552617823</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.86705027022585</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-12164.62309624022</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>39.16178378638405</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.305650472509922e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9999954920299587</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>60.45499999999998</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6011833731105806</v>
+      </c>
+      <c r="D16" t="n">
+        <v>386.9930152201104</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8513017098355508</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.39867e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.372</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5934631493476684</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.309336792618772</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.649505525886763</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.341852520538622</v>
+      </c>
+      <c r="L16" t="n">
+        <v>37.71109840772913</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.1532222126736</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>31.01398367139811</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-12301.63704658648</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>24.3418422203439</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.260194803460469e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9999375245747943</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57.06100000000004</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5674323786793958</v>
+      </c>
+      <c r="D17" t="n">
+        <v>295.8024498701705</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6507020060938172</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.39524e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.52</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.57956578892743</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.051516293240645</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.410154555136514</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.870976057397392</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40.33624523028612</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.22827363210166</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>32.32864698610952</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-12591.55523584506</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>117.720160713178</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.109920437275224e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9992231242068638</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>55.97399999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5566229116945106</v>
+      </c>
+      <c r="D18" t="n">
+        <v>182.4132752263546</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4012701185538838</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.39352e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.397431760239812</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.135820687024798</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.395714627381376</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.932596252622725</v>
+      </c>
+      <c r="L18" t="n">
+        <v>42.43705322646479</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.32155903305907</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>34.12654368386422</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-13108.61851085418</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>233.8761783754527</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.528409896661844e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9993788528685684</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>54.41900000000004</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5411595067621324</v>
+      </c>
+      <c r="D19" t="n">
+        <v>179.9192104091418</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3957837103763968</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.39268e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.721</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6985055427113006</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.364938252202912</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.608947491879248</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.494867310999511</v>
+      </c>
+      <c r="L19" t="n">
+        <v>44.86456903002861</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.39740103072994</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>35.74246454158065</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-13545.50494930807</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>220.4748179153826</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.966650188535112e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9986108725435486</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>52.26300000000003</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5197195704057282</v>
+      </c>
+      <c r="D20" t="n">
+        <v>177.5706237159228</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3906173228991004</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.39238e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.786</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5014500573245739</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.282092939337125</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.393934140188522</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.2465681211706</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45.94419276144426</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.4311182282699</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>36.51101060817594</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-13638.58811045589</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>226.6713948754433</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.133665939312221e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9551062298125889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>48.93799999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4866547334924422</v>
+      </c>
+      <c r="D21" t="n">
+        <v>179.9442203184309</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3958387268177879</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.39217e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.843</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2567589030461178</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.04250996156246</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.315056953784954</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.802228242451729</v>
+      </c>
+      <c r="L21" t="n">
+        <v>46.79584937436223</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.41999804012282</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>36.25391406392725</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-13312.56357781967</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>223.7539094805443</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.201122768536637e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8663187546127861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
